--- a/Base_RAs/022__alunos_com_informacao_de_parceria_2026-07-27T16_00_39.4344432-04_00.xlsx
+++ b/Base_RAs/022__alunos_com_informacao_de_parceria_2026-07-27T16_00_39.4344432-04_00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senaimt-my.sharepoint.com/personal/manoel_campos_sfiemt_ind_br/Documents/Área de Trabalho/AutomatizacaoERP/Base_RAs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{707DEA74-B68B-4E6A-B857-F924FB2D3DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4134AC5-0D29-48A5-88E9-FBC8F26C7CC1}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{707DEA74-B68B-4E6A-B857-F924FB2D3DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5877BEBF-4739-45F3-88E6-2F67B9C4A0D6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2685" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2685" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultado da consulta" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8698" uniqueCount="3527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8711" uniqueCount="3527">
   <si>
     <t>CodFilialSGE</t>
   </si>
@@ -12835,7 +12835,7 @@
       <c r="H45" t="s">
         <v>1386</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="3" t="s">
         <v>1387</v>
       </c>
       <c r="J45" s="1">
@@ -46500,48 +46500,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36902C53-BC33-4603-BFD3-82F285A025AB}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>306</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>307</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J1" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -46555,22 +46570,22 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>829</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>830</v>
+        <v>306</v>
       </c>
       <c r="H2" t="s">
-        <v>831</v>
+        <v>307</v>
       </c>
       <c r="I2" t="s">
-        <v>832</v>
+        <v>308</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
@@ -46579,7 +46594,7 @@
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>833</v>
+        <v>115</v>
       </c>
       <c r="M2" t="s">
         <v>22</v>
@@ -46596,22 +46611,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>828</v>
       </c>
       <c r="E3" t="s">
-        <v>3208</v>
+        <v>829</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>3209</v>
+        <v>830</v>
       </c>
       <c r="H3" t="s">
-        <v>3210</v>
+        <v>831</v>
       </c>
       <c r="I3" t="s">
-        <v>3211</v>
+        <v>832</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
@@ -46620,7 +46635,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>115</v>
+        <v>833</v>
       </c>
       <c r="M3" t="s">
         <v>22</v>
@@ -46637,22 +46652,22 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>3400</v>
+        <v>3208</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>3401</v>
+        <v>3209</v>
       </c>
       <c r="H4" t="s">
-        <v>3402</v>
+        <v>3210</v>
       </c>
       <c r="I4" t="s">
-        <v>3403</v>
+        <v>3211</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
@@ -46661,7 +46676,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>833</v>
+        <v>115</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
@@ -46678,22 +46693,22 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>3505</v>
+        <v>828</v>
       </c>
       <c r="E5" t="s">
-        <v>3506</v>
+        <v>3400</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>3507</v>
+        <v>3401</v>
       </c>
       <c r="H5" t="s">
-        <v>3508</v>
+        <v>3402</v>
       </c>
       <c r="I5" t="s">
-        <v>3509</v>
+        <v>3403</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -46702,9 +46717,50 @@
         <v>2</v>
       </c>
       <c r="L5" t="s">
+        <v>833</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3505</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3506</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3507</v>
+      </c>
+      <c r="H6" t="s">
+        <v>3508</v>
+      </c>
+      <c r="I6" t="s">
+        <v>3509</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
         <v>3510</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M6" t="s">
         <v>22</v>
       </c>
     </row>

--- a/Base_RAs/022__alunos_com_informacao_de_parceria_2026-07-27T16_00_39.4344432-04_00.xlsx
+++ b/Base_RAs/022__alunos_com_informacao_de_parceria_2026-07-27T16_00_39.4344432-04_00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoel.campos\Desktop\AutomatizacaoERP\totvs_sge_bot\Base_RAs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FA8790-6CD4-4ACE-99CF-7ACE10E7BBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E70C2C-06D4-4CB1-9971-7F151EAE9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8698" uniqueCount="3527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8724" uniqueCount="3527">
   <si>
     <t>CodFilialSGE</t>
   </si>
@@ -10663,14 +10663,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -11131,7 +11129,7 @@
       <c r="H3" t="s">
         <v>2918</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="5" t="s">
         <v>2919</v>
       </c>
       <c r="J3" s="1">
@@ -12879,7 +12877,7 @@
       <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="5" t="s">
         <v>165</v>
       </c>
       <c r="E46" t="s">
@@ -14740,44 +14738,44 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" t="s">
         <v>418</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
         <v>419</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" t="s">
         <v>420</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" t="s">
         <v>421</v>
       </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -14788,80 +14786,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC188AFD-1D7F-4882-984E-029AE543C45A}">
-  <dimension ref="A1:M262"/>
+  <dimension ref="A1:M273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>3</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
         <v>2169</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>2170</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" t="s">
         <v>2171</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G2" t="s">
         <v>2172</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H2" t="s">
         <v>2173</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I2" t="s">
         <v>2174</v>
-      </c>
-      <c r="J1" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2175</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2176</v>
-      </c>
-      <c r="H2" t="s">
-        <v>2177</v>
-      </c>
-      <c r="I2" t="s">
-        <v>2178</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
@@ -14887,22 +14897,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>2180</v>
+        <v>2176</v>
       </c>
       <c r="H3" t="s">
-        <v>2181</v>
+        <v>2177</v>
       </c>
       <c r="I3" t="s">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
@@ -14931,19 +14941,19 @@
         <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>2183</v>
+        <v>2179</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>2184</v>
+        <v>2180</v>
       </c>
       <c r="H4" t="s">
-        <v>2185</v>
+        <v>2181</v>
       </c>
       <c r="I4" t="s">
-        <v>2186</v>
+        <v>2182</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
@@ -14972,19 +14982,19 @@
         <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>2188</v>
+        <v>2184</v>
       </c>
       <c r="H5" t="s">
-        <v>2189</v>
+        <v>2185</v>
       </c>
       <c r="I5" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -15010,104 +15020,104 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2187</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2188</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2190</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
         <v>300</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>2191</v>
       </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
         <v>2192</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H7" t="s">
         <v>2193</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I7" t="s">
         <v>2194</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
         <v>2195</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>2196</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>2171</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>2197</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H8" t="s">
         <v>2198</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I8" t="s">
         <v>2199</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2208</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2209</v>
-      </c>
-      <c r="H8" t="s">
-        <v>2210</v>
-      </c>
-      <c r="I8" t="s">
-        <v>2211</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -15133,22 +15143,22 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>2212</v>
+        <v>2208</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>2213</v>
+        <v>2209</v>
       </c>
       <c r="H9" t="s">
-        <v>2214</v>
+        <v>2210</v>
       </c>
       <c r="I9" t="s">
-        <v>2215</v>
+        <v>2211</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -15177,19 +15187,19 @@
         <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="H10" t="s">
-        <v>2218</v>
+        <v>2214</v>
       </c>
       <c r="I10" t="s">
-        <v>2219</v>
+        <v>2215</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -15215,22 +15225,22 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>432</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>2232</v>
+        <v>2216</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>2233</v>
+        <v>2217</v>
       </c>
       <c r="H11" t="s">
-        <v>2234</v>
+        <v>2218</v>
       </c>
       <c r="I11" t="s">
-        <v>2235</v>
+        <v>2219</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -15256,22 +15266,22 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>300</v>
+        <v>432</v>
       </c>
       <c r="E12" t="s">
-        <v>2236</v>
+        <v>2232</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
       <c r="H12" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="I12" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -15300,19 +15310,19 @@
         <v>300</v>
       </c>
       <c r="E13" t="s">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="H13" t="s">
-        <v>2242</v>
+        <v>2238</v>
       </c>
       <c r="I13" t="s">
-        <v>2243</v>
+        <v>2239</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -15338,22 +15348,22 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>300</v>
       </c>
       <c r="E14" t="s">
-        <v>2244</v>
+        <v>2240</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="H14" t="s">
-        <v>2246</v>
+        <v>2242</v>
       </c>
       <c r="I14" t="s">
-        <v>2247</v>
+        <v>2243</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -15382,19 +15392,19 @@
         <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>2249</v>
+        <v>2245</v>
       </c>
       <c r="H15" t="s">
-        <v>2250</v>
+        <v>2246</v>
       </c>
       <c r="I15" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
@@ -15420,22 +15430,22 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>2252</v>
+        <v>2248</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="H16" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="I16" t="s">
-        <v>2255</v>
+        <v>2251</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
@@ -15464,19 +15474,19 @@
         <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>2256</v>
+        <v>2252</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>2257</v>
+        <v>2253</v>
       </c>
       <c r="H17" t="s">
-        <v>2258</v>
+        <v>2254</v>
       </c>
       <c r="I17" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
@@ -15505,19 +15515,19 @@
         <v>179</v>
       </c>
       <c r="E18" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>2261</v>
+        <v>2257</v>
       </c>
       <c r="H18" t="s">
-        <v>2262</v>
+        <v>2258</v>
       </c>
       <c r="I18" t="s">
-        <v>2263</v>
+        <v>2259</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
@@ -15546,19 +15556,19 @@
         <v>179</v>
       </c>
       <c r="E19" t="s">
-        <v>2264</v>
+        <v>2260</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>2265</v>
+        <v>2261</v>
       </c>
       <c r="H19" t="s">
-        <v>2266</v>
+        <v>2262</v>
       </c>
       <c r="I19" t="s">
-        <v>2267</v>
+        <v>2263</v>
       </c>
       <c r="J19" s="1">
         <v>1</v>
@@ -15584,22 +15594,22 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="E20" t="s">
-        <v>2268</v>
+        <v>2264</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>2269</v>
+        <v>2265</v>
       </c>
       <c r="H20" t="s">
-        <v>2270</v>
+        <v>2266</v>
       </c>
       <c r="I20" t="s">
-        <v>2271</v>
+        <v>2267</v>
       </c>
       <c r="J20" s="1">
         <v>1</v>
@@ -15625,22 +15635,22 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>432</v>
+        <v>300</v>
       </c>
       <c r="E21" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
       <c r="H21" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="I21" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="J21" s="1">
         <v>1</v>
@@ -15669,19 +15679,19 @@
         <v>432</v>
       </c>
       <c r="E22" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="H22" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="I22" t="s">
-        <v>2279</v>
+        <v>2275</v>
       </c>
       <c r="J22" s="1">
         <v>1</v>
@@ -15707,22 +15717,22 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>432</v>
       </c>
       <c r="E23" t="s">
-        <v>2284</v>
+        <v>2276</v>
       </c>
       <c r="F23" t="s">
         <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>2285</v>
+        <v>2277</v>
       </c>
       <c r="H23" t="s">
-        <v>2286</v>
+        <v>2278</v>
       </c>
       <c r="I23" t="s">
-        <v>2287</v>
+        <v>2279</v>
       </c>
       <c r="J23" s="1">
         <v>1</v>
@@ -15748,22 +15758,22 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>2288</v>
+        <v>2284</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="H24" t="s">
-        <v>2290</v>
+        <v>2286</v>
       </c>
       <c r="I24" t="s">
-        <v>2291</v>
+        <v>2287</v>
       </c>
       <c r="J24" s="1">
         <v>1</v>
@@ -15789,22 +15799,22 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>2293</v>
+        <v>2289</v>
       </c>
       <c r="H25" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
       <c r="I25" t="s">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
@@ -15833,19 +15843,19 @@
         <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>2296</v>
+        <v>2292</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>2297</v>
+        <v>2293</v>
       </c>
       <c r="H26" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="I26" t="s">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="J26" s="1">
         <v>1</v>
@@ -15874,19 +15884,19 @@
         <v>27</v>
       </c>
       <c r="E27" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>2301</v>
+        <v>2297</v>
       </c>
       <c r="H27" t="s">
-        <v>2302</v>
+        <v>2298</v>
       </c>
       <c r="I27" t="s">
-        <v>2303</v>
+        <v>2299</v>
       </c>
       <c r="J27" s="1">
         <v>1</v>
@@ -15912,22 +15922,22 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>507</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>2304</v>
+        <v>2300</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>2305</v>
+        <v>2301</v>
       </c>
       <c r="H28" t="s">
-        <v>2306</v>
+        <v>2302</v>
       </c>
       <c r="I28" t="s">
-        <v>2307</v>
+        <v>2303</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
@@ -15953,22 +15963,22 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E29" t="s">
-        <v>2308</v>
+        <v>2304</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>2309</v>
+        <v>2305</v>
       </c>
       <c r="H29" t="s">
-        <v>2310</v>
+        <v>2306</v>
       </c>
       <c r="I29" t="s">
-        <v>2311</v>
+        <v>2307</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
@@ -15997,19 +16007,19 @@
         <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>2312</v>
+        <v>2308</v>
       </c>
       <c r="F30" t="s">
         <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>2313</v>
+        <v>2309</v>
       </c>
       <c r="H30" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
       <c r="I30" t="s">
-        <v>2315</v>
+        <v>2311</v>
       </c>
       <c r="J30" s="1">
         <v>1</v>
@@ -16038,19 +16048,19 @@
         <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>2316</v>
+        <v>2312</v>
       </c>
       <c r="F31" t="s">
         <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>2317</v>
+        <v>2313</v>
       </c>
       <c r="H31" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
       <c r="I31" t="s">
-        <v>2319</v>
+        <v>2315</v>
       </c>
       <c r="J31" s="1">
         <v>1</v>
@@ -16076,22 +16086,22 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>2328</v>
+        <v>2316</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>2329</v>
+        <v>2317</v>
       </c>
       <c r="H32" t="s">
-        <v>2330</v>
+        <v>2318</v>
       </c>
       <c r="I32" t="s">
-        <v>2331</v>
+        <v>2319</v>
       </c>
       <c r="J32" s="1">
         <v>1</v>
@@ -16117,22 +16127,22 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
-        <v>2340</v>
+        <v>2328</v>
       </c>
       <c r="F33" t="s">
         <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>2341</v>
+        <v>2329</v>
       </c>
       <c r="H33" t="s">
-        <v>2342</v>
+        <v>2330</v>
       </c>
       <c r="I33" t="s">
-        <v>2343</v>
+        <v>2331</v>
       </c>
       <c r="J33" s="1">
         <v>1</v>
@@ -16158,22 +16168,22 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>432</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>2348</v>
+        <v>2340</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>2349</v>
+        <v>2341</v>
       </c>
       <c r="H34" t="s">
-        <v>2350</v>
+        <v>2342</v>
       </c>
       <c r="I34" t="s">
-        <v>2351</v>
+        <v>2343</v>
       </c>
       <c r="J34" s="1">
         <v>1</v>
@@ -16202,19 +16212,19 @@
         <v>432</v>
       </c>
       <c r="E35" t="s">
-        <v>2352</v>
+        <v>2348</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
       <c r="H35" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
       <c r="I35" t="s">
-        <v>2355</v>
+        <v>2351</v>
       </c>
       <c r="J35" s="1">
         <v>1</v>
@@ -16243,19 +16253,19 @@
         <v>432</v>
       </c>
       <c r="E36" t="s">
-        <v>2356</v>
+        <v>2352</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>2357</v>
+        <v>2353</v>
       </c>
       <c r="H36" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
       <c r="I36" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
@@ -16281,22 +16291,22 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>507</v>
+        <v>432</v>
       </c>
       <c r="E37" t="s">
-        <v>2360</v>
+        <v>2356</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>2361</v>
+        <v>2357</v>
       </c>
       <c r="H37" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
       <c r="I37" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="J37" s="1">
         <v>1</v>
@@ -16322,22 +16332,22 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>507</v>
       </c>
       <c r="E38" t="s">
-        <v>2364</v>
+        <v>2360</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
       <c r="H38" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
       <c r="I38" t="s">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="J38" s="1">
         <v>1</v>
@@ -16363,22 +16373,22 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
       <c r="F39" t="s">
         <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>2369</v>
+        <v>2365</v>
       </c>
       <c r="H39" t="s">
-        <v>2370</v>
+        <v>2366</v>
       </c>
       <c r="I39" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="J39" s="1">
         <v>1</v>
@@ -16407,19 +16417,19 @@
         <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>2380</v>
+        <v>2368</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>2381</v>
+        <v>2369</v>
       </c>
       <c r="H40" t="s">
-        <v>2382</v>
+        <v>2370</v>
       </c>
       <c r="I40" t="s">
-        <v>2383</v>
+        <v>2371</v>
       </c>
       <c r="J40" s="1">
         <v>1</v>
@@ -16448,19 +16458,19 @@
         <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
       <c r="H41" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
       <c r="I41" t="s">
-        <v>2387</v>
+        <v>2383</v>
       </c>
       <c r="J41" s="1">
         <v>1</v>
@@ -16486,22 +16496,22 @@
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>466</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>2388</v>
+        <v>2384</v>
       </c>
       <c r="F42" t="s">
         <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>2389</v>
+        <v>2385</v>
       </c>
       <c r="H42" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
       <c r="I42" t="s">
-        <v>2391</v>
+        <v>2387</v>
       </c>
       <c r="J42" s="1">
         <v>1</v>
@@ -16530,19 +16540,19 @@
         <v>466</v>
       </c>
       <c r="E43" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>2393</v>
+        <v>2389</v>
       </c>
       <c r="H43" t="s">
-        <v>2394</v>
+        <v>2390</v>
       </c>
       <c r="I43" t="s">
-        <v>2395</v>
+        <v>2391</v>
       </c>
       <c r="J43" s="1">
         <v>1</v>
@@ -16571,19 +16581,19 @@
         <v>466</v>
       </c>
       <c r="E44" t="s">
-        <v>2396</v>
+        <v>2392</v>
       </c>
       <c r="F44" t="s">
         <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>2397</v>
+        <v>2393</v>
       </c>
       <c r="H44" t="s">
-        <v>2398</v>
+        <v>2394</v>
       </c>
       <c r="I44" t="s">
-        <v>2399</v>
+        <v>2395</v>
       </c>
       <c r="J44" s="1">
         <v>1</v>
@@ -16609,22 +16619,22 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>507</v>
+        <v>466</v>
       </c>
       <c r="E45" t="s">
-        <v>2400</v>
+        <v>2396</v>
       </c>
       <c r="F45" t="s">
         <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>2401</v>
+        <v>2397</v>
       </c>
       <c r="H45" t="s">
-        <v>2402</v>
+        <v>2398</v>
       </c>
       <c r="I45" t="s">
-        <v>2403</v>
+        <v>2399</v>
       </c>
       <c r="J45" s="1">
         <v>1</v>
@@ -16650,22 +16660,22 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>507</v>
       </c>
       <c r="E46" t="s">
-        <v>2404</v>
+        <v>2400</v>
       </c>
       <c r="F46" t="s">
         <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>2405</v>
+        <v>2401</v>
       </c>
       <c r="H46" t="s">
-        <v>2406</v>
+        <v>2402</v>
       </c>
       <c r="I46" t="s">
-        <v>2407</v>
+        <v>2403</v>
       </c>
       <c r="J46" s="1">
         <v>1</v>
@@ -16694,19 +16704,19 @@
         <v>124</v>
       </c>
       <c r="E47" t="s">
-        <v>2408</v>
+        <v>2404</v>
       </c>
       <c r="F47" t="s">
         <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>2409</v>
+        <v>2405</v>
       </c>
       <c r="H47" t="s">
-        <v>2410</v>
+        <v>2406</v>
       </c>
       <c r="I47" t="s">
-        <v>2411</v>
+        <v>2407</v>
       </c>
       <c r="J47" s="1">
         <v>1</v>
@@ -16732,22 +16742,22 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s">
-        <v>2412</v>
+        <v>2408</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>2413</v>
+        <v>2409</v>
       </c>
       <c r="H48" t="s">
-        <v>2414</v>
+        <v>2410</v>
       </c>
       <c r="I48" t="s">
-        <v>2415</v>
+        <v>2411</v>
       </c>
       <c r="J48" s="1">
         <v>1</v>
@@ -16773,22 +16783,22 @@
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>2416</v>
+        <v>2412</v>
       </c>
       <c r="F49" t="s">
         <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>2417</v>
+        <v>2413</v>
       </c>
       <c r="H49" t="s">
-        <v>2418</v>
+        <v>2414</v>
       </c>
       <c r="I49" t="s">
-        <v>2419</v>
+        <v>2415</v>
       </c>
       <c r="J49" s="1">
         <v>1</v>
@@ -16814,22 +16824,22 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="E50" t="s">
-        <v>2420</v>
+        <v>2416</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>2421</v>
+        <v>2417</v>
       </c>
       <c r="H50" t="s">
-        <v>2422</v>
+        <v>2418</v>
       </c>
       <c r="I50" t="s">
-        <v>2423</v>
+        <v>2419</v>
       </c>
       <c r="J50" s="1">
         <v>1</v>
@@ -16855,22 +16865,22 @@
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>2428</v>
+        <v>2420</v>
       </c>
       <c r="F51" t="s">
         <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>2429</v>
+        <v>2421</v>
       </c>
       <c r="H51" t="s">
-        <v>2430</v>
+        <v>2422</v>
       </c>
       <c r="I51" t="s">
-        <v>2431</v>
+        <v>2423</v>
       </c>
       <c r="J51" s="1">
         <v>1</v>
@@ -16896,22 +16906,22 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>622</v>
+        <v>124</v>
       </c>
       <c r="E52" t="s">
-        <v>2432</v>
+        <v>2428</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
       <c r="H52" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
       <c r="I52" t="s">
-        <v>2435</v>
+        <v>2431</v>
       </c>
       <c r="J52" s="1">
         <v>1</v>
@@ -16937,22 +16947,22 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
+        <v>622</v>
       </c>
       <c r="E53" t="s">
-        <v>2436</v>
+        <v>2432</v>
       </c>
       <c r="F53" t="s">
         <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>2437</v>
+        <v>2433</v>
       </c>
       <c r="H53" t="s">
-        <v>2438</v>
+        <v>2434</v>
       </c>
       <c r="I53" t="s">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="J53" s="1">
         <v>1</v>
@@ -16978,22 +16988,22 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>580</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
-        <v>2440</v>
+        <v>2436</v>
       </c>
       <c r="F54" t="s">
         <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
       <c r="H54" t="s">
-        <v>2442</v>
+        <v>2438</v>
       </c>
       <c r="I54" t="s">
-        <v>2443</v>
+        <v>2439</v>
       </c>
       <c r="J54" s="1">
         <v>1</v>
@@ -17019,22 +17029,22 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="E55" t="s">
-        <v>2444</v>
+        <v>2440</v>
       </c>
       <c r="F55" t="s">
         <v>17</v>
       </c>
       <c r="G55" t="s">
-        <v>2445</v>
+        <v>2441</v>
       </c>
       <c r="H55" t="s">
-        <v>2446</v>
+        <v>2442</v>
       </c>
       <c r="I55" t="s">
-        <v>2447</v>
+        <v>2443</v>
       </c>
       <c r="J55" s="1">
         <v>1</v>
@@ -17060,22 +17070,22 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="E56" t="s">
-        <v>2448</v>
+        <v>2444</v>
       </c>
       <c r="F56" t="s">
         <v>17</v>
       </c>
       <c r="G56" t="s">
-        <v>2449</v>
+        <v>2445</v>
       </c>
       <c r="H56" t="s">
-        <v>2450</v>
+        <v>2446</v>
       </c>
       <c r="I56" t="s">
-        <v>2451</v>
+        <v>2447</v>
       </c>
       <c r="J56" s="1">
         <v>1</v>
@@ -17101,22 +17111,22 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>580</v>
       </c>
       <c r="E57" t="s">
-        <v>2452</v>
+        <v>2448</v>
       </c>
       <c r="F57" t="s">
         <v>17</v>
       </c>
       <c r="G57" t="s">
-        <v>2453</v>
+        <v>2449</v>
       </c>
       <c r="H57" t="s">
-        <v>2454</v>
+        <v>2450</v>
       </c>
       <c r="I57" t="s">
-        <v>2455</v>
+        <v>2451</v>
       </c>
       <c r="J57" s="1">
         <v>1</v>
@@ -17142,22 +17152,22 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>605</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>2456</v>
+        <v>2452</v>
       </c>
       <c r="F58" t="s">
         <v>17</v>
       </c>
       <c r="G58" t="s">
-        <v>2457</v>
+        <v>2453</v>
       </c>
       <c r="H58" t="s">
-        <v>2458</v>
+        <v>2454</v>
       </c>
       <c r="I58" t="s">
-        <v>2459</v>
+        <v>2455</v>
       </c>
       <c r="J58" s="1">
         <v>1</v>
@@ -17183,22 +17193,22 @@
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>605</v>
       </c>
       <c r="E59" t="s">
-        <v>2460</v>
+        <v>2456</v>
       </c>
       <c r="F59" t="s">
         <v>17</v>
       </c>
       <c r="G59" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
       <c r="H59" t="s">
-        <v>2462</v>
+        <v>2458</v>
       </c>
       <c r="I59" t="s">
-        <v>2463</v>
+        <v>2459</v>
       </c>
       <c r="J59" s="1">
         <v>1</v>
@@ -17224,22 +17234,22 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>605</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s">
-        <v>2464</v>
+        <v>2460</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="H60" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
       <c r="I60" t="s">
-        <v>2467</v>
+        <v>2463</v>
       </c>
       <c r="J60" s="1">
         <v>1</v>
@@ -17268,19 +17278,19 @@
         <v>605</v>
       </c>
       <c r="E61" t="s">
-        <v>2468</v>
+        <v>2464</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>2469</v>
+        <v>2465</v>
       </c>
       <c r="H61" t="s">
-        <v>2470</v>
+        <v>2466</v>
       </c>
       <c r="I61" t="s">
-        <v>2471</v>
+        <v>2467</v>
       </c>
       <c r="J61" s="1">
         <v>1</v>
@@ -17306,31 +17316,31 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>461</v>
+        <v>605</v>
       </c>
       <c r="E62" t="s">
-        <v>2472</v>
+        <v>2468</v>
       </c>
       <c r="F62" t="s">
         <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>2473</v>
+        <v>2469</v>
       </c>
       <c r="H62" t="s">
-        <v>2474</v>
+        <v>2470</v>
       </c>
       <c r="I62" t="s">
-        <v>2475</v>
+        <v>2471</v>
       </c>
       <c r="J62" s="1">
         <v>1</v>
       </c>
       <c r="K62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M62" t="s">
         <v>22</v>
@@ -17350,28 +17360,28 @@
         <v>461</v>
       </c>
       <c r="E63" t="s">
-        <v>2476</v>
+        <v>2472</v>
       </c>
       <c r="F63" t="s">
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>2477</v>
+        <v>2473</v>
       </c>
       <c r="H63" t="s">
-        <v>2478</v>
+        <v>2474</v>
       </c>
       <c r="I63" t="s">
-        <v>2479</v>
+        <v>2475</v>
       </c>
       <c r="J63" s="1">
         <v>1</v>
       </c>
       <c r="K63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M63" t="s">
         <v>22</v>
@@ -17388,22 +17398,22 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>622</v>
+        <v>461</v>
       </c>
       <c r="E64" t="s">
-        <v>2480</v>
+        <v>2476</v>
       </c>
       <c r="F64" t="s">
         <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="H64" t="s">
-        <v>2482</v>
+        <v>2478</v>
       </c>
       <c r="I64" t="s">
-        <v>2483</v>
+        <v>2479</v>
       </c>
       <c r="J64" s="1">
         <v>1</v>
@@ -17429,22 +17439,22 @@
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
+        <v>622</v>
       </c>
       <c r="E65" t="s">
-        <v>2492</v>
+        <v>2480</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>2493</v>
+        <v>2481</v>
       </c>
       <c r="H65" t="s">
-        <v>2494</v>
+        <v>2482</v>
       </c>
       <c r="I65" t="s">
-        <v>2495</v>
+        <v>2483</v>
       </c>
       <c r="J65" s="1">
         <v>1</v>
@@ -17470,22 +17480,22 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E66" t="s">
-        <v>2496</v>
+        <v>2492</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="H66" t="s">
-        <v>2498</v>
+        <v>2494</v>
       </c>
       <c r="I66" t="s">
-        <v>2499</v>
+        <v>2495</v>
       </c>
       <c r="J66" s="1">
         <v>1</v>
@@ -17511,22 +17521,22 @@
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>2500</v>
+        <v>2496</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>2501</v>
+        <v>2497</v>
       </c>
       <c r="H67" t="s">
-        <v>2502</v>
+        <v>2498</v>
       </c>
       <c r="I67" t="s">
-        <v>2503</v>
+        <v>2499</v>
       </c>
       <c r="J67" s="1">
         <v>1</v>
@@ -17552,22 +17562,22 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="E68" t="s">
-        <v>2504</v>
+        <v>2500</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
       <c r="H68" t="s">
-        <v>2506</v>
+        <v>2502</v>
       </c>
       <c r="I68" t="s">
-        <v>2507</v>
+        <v>2503</v>
       </c>
       <c r="J68" s="1">
         <v>1</v>
@@ -17593,22 +17603,22 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="E69" t="s">
-        <v>2508</v>
+        <v>2504</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="H69" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
       <c r="I69" t="s">
-        <v>2511</v>
+        <v>2507</v>
       </c>
       <c r="J69" s="1">
         <v>1</v>
@@ -17634,22 +17644,22 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E70" t="s">
-        <v>2512</v>
+        <v>2508</v>
       </c>
       <c r="F70" t="s">
         <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>2513</v>
+        <v>2509</v>
       </c>
       <c r="H70" t="s">
-        <v>2514</v>
+        <v>2510</v>
       </c>
       <c r="I70" t="s">
-        <v>2515</v>
+        <v>2511</v>
       </c>
       <c r="J70" s="1">
         <v>1</v>
@@ -17675,22 +17685,22 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="E71" t="s">
-        <v>2516</v>
+        <v>2512</v>
       </c>
       <c r="F71" t="s">
         <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>2517</v>
+        <v>2513</v>
       </c>
       <c r="H71" t="s">
-        <v>2518</v>
+        <v>2514</v>
       </c>
       <c r="I71" t="s">
-        <v>2519</v>
+        <v>2515</v>
       </c>
       <c r="J71" s="1">
         <v>1</v>
@@ -17716,31 +17726,31 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>461</v>
+        <v>156</v>
       </c>
       <c r="E72" t="s">
-        <v>2520</v>
+        <v>2516</v>
       </c>
       <c r="F72" t="s">
         <v>17</v>
       </c>
       <c r="G72" t="s">
-        <v>2521</v>
+        <v>2517</v>
       </c>
       <c r="H72" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
       <c r="I72" t="s">
-        <v>2523</v>
+        <v>2519</v>
       </c>
       <c r="J72" s="1">
         <v>1</v>
       </c>
       <c r="K72" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M72" t="s">
         <v>22</v>
@@ -17757,31 +17767,31 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>622</v>
+        <v>461</v>
       </c>
       <c r="E73" t="s">
-        <v>2524</v>
+        <v>2520</v>
       </c>
       <c r="F73" t="s">
         <v>17</v>
       </c>
       <c r="G73" t="s">
-        <v>2525</v>
+        <v>2521</v>
       </c>
       <c r="H73" t="s">
-        <v>2526</v>
+        <v>2522</v>
       </c>
       <c r="I73" t="s">
-        <v>2527</v>
+        <v>2523</v>
       </c>
       <c r="J73" s="1">
         <v>1</v>
       </c>
       <c r="K73" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M73" t="s">
         <v>22</v>
@@ -17798,31 +17808,31 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>461</v>
+        <v>622</v>
       </c>
       <c r="E74" t="s">
-        <v>2528</v>
+        <v>2524</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>2529</v>
+        <v>2525</v>
       </c>
       <c r="H74" t="s">
-        <v>2530</v>
+        <v>2526</v>
       </c>
       <c r="I74" t="s">
-        <v>2531</v>
+        <v>2527</v>
       </c>
       <c r="J74" s="1">
         <v>1</v>
       </c>
       <c r="K74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M74" t="s">
         <v>22</v>
@@ -17839,31 +17849,31 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>147</v>
+        <v>461</v>
       </c>
       <c r="E75" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="F75" t="s">
         <v>17</v>
       </c>
       <c r="G75" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="H75" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="I75" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="J75" s="1">
         <v>1</v>
       </c>
       <c r="K75" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M75" t="s">
         <v>22</v>
@@ -17880,22 +17890,22 @@
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
-        <v>2536</v>
+        <v>2532</v>
       </c>
       <c r="F76" t="s">
         <v>17</v>
       </c>
       <c r="G76" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="H76" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
       <c r="I76" t="s">
-        <v>2539</v>
+        <v>2535</v>
       </c>
       <c r="J76" s="1">
         <v>1</v>
@@ -17921,22 +17931,22 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="E77" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="F77" t="s">
         <v>17</v>
       </c>
       <c r="G77" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="H77" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="I77" t="s">
-        <v>2543</v>
+        <v>2539</v>
       </c>
       <c r="J77" s="1">
         <v>1</v>
@@ -17962,22 +17972,22 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="E78" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="F78" t="s">
         <v>17</v>
       </c>
       <c r="G78" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="H78" t="s">
-        <v>2546</v>
+        <v>2542</v>
       </c>
       <c r="I78" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="J78" s="1">
         <v>1</v>
@@ -18003,22 +18013,22 @@
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="E79" t="s">
-        <v>2548</v>
+        <v>2544</v>
       </c>
       <c r="F79" t="s">
         <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>2549</v>
+        <v>2545</v>
       </c>
       <c r="H79" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="I79" t="s">
-        <v>2551</v>
+        <v>2547</v>
       </c>
       <c r="J79" s="1">
         <v>1</v>
@@ -18047,19 +18057,19 @@
         <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>2552</v>
+        <v>2548</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>2553</v>
+        <v>2549</v>
       </c>
       <c r="H80" t="s">
-        <v>2554</v>
+        <v>2550</v>
       </c>
       <c r="I80" t="s">
-        <v>2555</v>
+        <v>2551</v>
       </c>
       <c r="J80" s="1">
         <v>1</v>
@@ -18085,22 +18095,22 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E81" t="s">
-        <v>2556</v>
+        <v>2552</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>2557</v>
+        <v>2553</v>
       </c>
       <c r="H81" t="s">
-        <v>2558</v>
+        <v>2554</v>
       </c>
       <c r="I81" t="s">
-        <v>2559</v>
+        <v>2555</v>
       </c>
       <c r="J81" s="1">
         <v>1</v>
@@ -18126,22 +18136,22 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E82" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="F82" t="s">
         <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>2561</v>
+        <v>2557</v>
       </c>
       <c r="H82" t="s">
-        <v>2562</v>
+        <v>2558</v>
       </c>
       <c r="I82" t="s">
-        <v>2563</v>
+        <v>2559</v>
       </c>
       <c r="J82" s="1">
         <v>1</v>
@@ -18170,19 +18180,19 @@
         <v>15</v>
       </c>
       <c r="E83" t="s">
-        <v>2564</v>
+        <v>2560</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
       </c>
       <c r="G83" t="s">
-        <v>2565</v>
+        <v>2561</v>
       </c>
       <c r="H83" t="s">
-        <v>2566</v>
+        <v>2562</v>
       </c>
       <c r="I83" t="s">
-        <v>2567</v>
+        <v>2563</v>
       </c>
       <c r="J83" s="1">
         <v>1</v>
@@ -18208,22 +18218,22 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>605</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>2576</v>
+        <v>2564</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
       </c>
       <c r="G84" t="s">
-        <v>2577</v>
+        <v>2565</v>
       </c>
       <c r="H84" t="s">
-        <v>2578</v>
+        <v>2566</v>
       </c>
       <c r="I84" t="s">
-        <v>2579</v>
+        <v>2567</v>
       </c>
       <c r="J84" s="1">
         <v>1</v>
@@ -18252,19 +18262,19 @@
         <v>605</v>
       </c>
       <c r="E85" t="s">
-        <v>2580</v>
+        <v>2576</v>
       </c>
       <c r="F85" t="s">
         <v>17</v>
       </c>
       <c r="G85" t="s">
-        <v>2581</v>
+        <v>2577</v>
       </c>
       <c r="H85" t="s">
-        <v>2582</v>
+        <v>2578</v>
       </c>
       <c r="I85" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
       <c r="J85" s="1">
         <v>1</v>
@@ -18293,19 +18303,19 @@
         <v>605</v>
       </c>
       <c r="E86" t="s">
-        <v>2584</v>
+        <v>2580</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
       </c>
       <c r="G86" t="s">
-        <v>2585</v>
+        <v>2581</v>
       </c>
       <c r="H86" t="s">
-        <v>2586</v>
+        <v>2582</v>
       </c>
       <c r="I86" t="s">
-        <v>2587</v>
+        <v>2583</v>
       </c>
       <c r="J86" s="1">
         <v>1</v>
@@ -18334,19 +18344,19 @@
         <v>605</v>
       </c>
       <c r="E87" t="s">
-        <v>2588</v>
+        <v>2584</v>
       </c>
       <c r="F87" t="s">
         <v>17</v>
       </c>
       <c r="G87" t="s">
-        <v>2589</v>
+        <v>2585</v>
       </c>
       <c r="H87" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="I87" t="s">
-        <v>2591</v>
+        <v>2587</v>
       </c>
       <c r="J87" s="1">
         <v>1</v>
@@ -18372,22 +18382,22 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>116</v>
+        <v>605</v>
       </c>
       <c r="E88" t="s">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="F88" t="s">
         <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>2593</v>
+        <v>2589</v>
       </c>
       <c r="H88" t="s">
-        <v>2594</v>
+        <v>2590</v>
       </c>
       <c r="I88" t="s">
-        <v>2595</v>
+        <v>2591</v>
       </c>
       <c r="J88" s="1">
         <v>1</v>
@@ -18413,22 +18423,22 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>627</v>
+        <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="F89" t="s">
         <v>17</v>
       </c>
       <c r="G89" t="s">
-        <v>2597</v>
+        <v>2593</v>
       </c>
       <c r="H89" t="s">
-        <v>2598</v>
+        <v>2594</v>
       </c>
       <c r="I89" t="s">
-        <v>2599</v>
+        <v>2595</v>
       </c>
       <c r="J89" s="1">
         <v>1</v>
@@ -18454,22 +18464,22 @@
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E90" t="s">
-        <v>2600</v>
+        <v>2596</v>
       </c>
       <c r="F90" t="s">
         <v>17</v>
       </c>
       <c r="G90" t="s">
-        <v>2601</v>
+        <v>2597</v>
       </c>
       <c r="H90" t="s">
-        <v>2602</v>
+        <v>2598</v>
       </c>
       <c r="I90" t="s">
-        <v>2603</v>
+        <v>2599</v>
       </c>
       <c r="J90" s="1">
         <v>1</v>
@@ -18495,22 +18505,22 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>622</v>
       </c>
       <c r="E91" t="s">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="F91" t="s">
         <v>17</v>
       </c>
       <c r="G91" t="s">
-        <v>2609</v>
+        <v>2601</v>
       </c>
       <c r="H91" t="s">
-        <v>2610</v>
+        <v>2602</v>
       </c>
       <c r="I91" t="s">
-        <v>2611</v>
+        <v>2603</v>
       </c>
       <c r="J91" s="1">
         <v>1</v>
@@ -18536,22 +18546,22 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E92" t="s">
-        <v>2620</v>
+        <v>2608</v>
       </c>
       <c r="F92" t="s">
         <v>17</v>
       </c>
       <c r="G92" t="s">
-        <v>2621</v>
+        <v>2609</v>
       </c>
       <c r="H92" t="s">
-        <v>2622</v>
+        <v>2610</v>
       </c>
       <c r="I92" t="s">
-        <v>2623</v>
+        <v>2611</v>
       </c>
       <c r="J92" s="1">
         <v>1</v>
@@ -18577,22 +18587,22 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="E93" t="s">
-        <v>2624</v>
+        <v>2620</v>
       </c>
       <c r="F93" t="s">
         <v>17</v>
       </c>
       <c r="G93" t="s">
-        <v>2625</v>
+        <v>2621</v>
       </c>
       <c r="H93" t="s">
-        <v>2626</v>
+        <v>2622</v>
       </c>
       <c r="I93" t="s">
-        <v>2627</v>
+        <v>2623</v>
       </c>
       <c r="J93" s="1">
         <v>1</v>
@@ -18621,19 +18631,19 @@
         <v>124</v>
       </c>
       <c r="E94" t="s">
-        <v>2628</v>
+        <v>2624</v>
       </c>
       <c r="F94" t="s">
         <v>17</v>
       </c>
       <c r="G94" t="s">
-        <v>2629</v>
+        <v>2625</v>
       </c>
       <c r="H94" t="s">
-        <v>2630</v>
+        <v>2626</v>
       </c>
       <c r="I94" t="s">
-        <v>2631</v>
+        <v>2627</v>
       </c>
       <c r="J94" s="1">
         <v>1</v>
@@ -18662,19 +18672,19 @@
         <v>124</v>
       </c>
       <c r="E95" t="s">
-        <v>2632</v>
+        <v>2628</v>
       </c>
       <c r="F95" t="s">
         <v>17</v>
       </c>
       <c r="G95" t="s">
-        <v>2633</v>
+        <v>2629</v>
       </c>
       <c r="H95" t="s">
-        <v>2634</v>
+        <v>2630</v>
       </c>
       <c r="I95" t="s">
-        <v>2635</v>
+        <v>2631</v>
       </c>
       <c r="J95" s="1">
         <v>1</v>
@@ -18700,22 +18710,22 @@
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="E96" t="s">
-        <v>2636</v>
+        <v>2632</v>
       </c>
       <c r="F96" t="s">
         <v>17</v>
       </c>
       <c r="G96" t="s">
-        <v>2637</v>
+        <v>2633</v>
       </c>
       <c r="H96" t="s">
-        <v>2638</v>
+        <v>2634</v>
       </c>
       <c r="I96" t="s">
-        <v>2639</v>
+        <v>2635</v>
       </c>
       <c r="J96" s="1">
         <v>1</v>
@@ -18741,31 +18751,31 @@
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>461</v>
+        <v>147</v>
       </c>
       <c r="E97" t="s">
-        <v>2640</v>
+        <v>2636</v>
       </c>
       <c r="F97" t="s">
         <v>17</v>
       </c>
       <c r="G97" t="s">
-        <v>2641</v>
+        <v>2637</v>
       </c>
       <c r="H97" t="s">
-        <v>2642</v>
+        <v>2638</v>
       </c>
       <c r="I97" t="s">
-        <v>2643</v>
+        <v>2639</v>
       </c>
       <c r="J97" s="1">
         <v>1</v>
       </c>
       <c r="K97" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M97" t="s">
         <v>22</v>
@@ -18785,19 +18795,19 @@
         <v>461</v>
       </c>
       <c r="E98" t="s">
-        <v>2644</v>
+        <v>2640</v>
       </c>
       <c r="F98" t="s">
         <v>17</v>
       </c>
       <c r="G98" t="s">
-        <v>2645</v>
+        <v>2641</v>
       </c>
       <c r="H98" t="s">
-        <v>2646</v>
+        <v>2642</v>
       </c>
       <c r="I98" t="s">
-        <v>2647</v>
+        <v>2643</v>
       </c>
       <c r="J98" s="1">
         <v>1</v>
@@ -18823,31 +18833,31 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>461</v>
       </c>
       <c r="E99" t="s">
-        <v>2648</v>
+        <v>2644</v>
       </c>
       <c r="F99" t="s">
         <v>17</v>
       </c>
       <c r="G99" t="s">
-        <v>2649</v>
+        <v>2645</v>
       </c>
       <c r="H99" t="s">
-        <v>2650</v>
+        <v>2646</v>
       </c>
       <c r="I99" t="s">
-        <v>2651</v>
+        <v>2647</v>
       </c>
       <c r="J99" s="1">
         <v>1</v>
       </c>
       <c r="K99" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M99" t="s">
         <v>22</v>
@@ -18864,22 +18874,22 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="E100" t="s">
-        <v>2652</v>
+        <v>2648</v>
       </c>
       <c r="F100" t="s">
         <v>17</v>
       </c>
       <c r="G100" t="s">
-        <v>2653</v>
+        <v>2649</v>
       </c>
       <c r="H100" t="s">
-        <v>2654</v>
+        <v>2650</v>
       </c>
       <c r="I100" t="s">
-        <v>2655</v>
+        <v>2651</v>
       </c>
       <c r="J100" s="1">
         <v>1</v>
@@ -18905,22 +18915,22 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>2656</v>
+        <v>2652</v>
       </c>
       <c r="F101" t="s">
         <v>17</v>
       </c>
       <c r="G101" t="s">
-        <v>2657</v>
+        <v>2653</v>
       </c>
       <c r="H101" t="s">
-        <v>2658</v>
+        <v>2654</v>
       </c>
       <c r="I101" t="s">
-        <v>2659</v>
+        <v>2655</v>
       </c>
       <c r="J101" s="1">
         <v>1</v>
@@ -18946,22 +18956,22 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>580</v>
+        <v>156</v>
       </c>
       <c r="E102" t="s">
-        <v>2660</v>
+        <v>2656</v>
       </c>
       <c r="F102" t="s">
         <v>17</v>
       </c>
       <c r="G102" t="s">
-        <v>2661</v>
+        <v>2657</v>
       </c>
       <c r="H102" t="s">
-        <v>2662</v>
+        <v>2658</v>
       </c>
       <c r="I102" t="s">
-        <v>2663</v>
+        <v>2659</v>
       </c>
       <c r="J102" s="1">
         <v>1</v>
@@ -18987,22 +18997,22 @@
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>116</v>
+        <v>580</v>
       </c>
       <c r="E103" t="s">
-        <v>2668</v>
+        <v>2660</v>
       </c>
       <c r="F103" t="s">
         <v>17</v>
       </c>
       <c r="G103" t="s">
-        <v>2669</v>
+        <v>2661</v>
       </c>
       <c r="H103" t="s">
-        <v>2670</v>
+        <v>2662</v>
       </c>
       <c r="I103" t="s">
-        <v>2671</v>
+        <v>2663</v>
       </c>
       <c r="J103" s="1">
         <v>1</v>
@@ -19031,19 +19041,19 @@
         <v>116</v>
       </c>
       <c r="E104" t="s">
-        <v>2676</v>
+        <v>2668</v>
       </c>
       <c r="F104" t="s">
         <v>17</v>
       </c>
       <c r="G104" t="s">
-        <v>2677</v>
+        <v>2669</v>
       </c>
       <c r="H104" t="s">
-        <v>2678</v>
+        <v>2670</v>
       </c>
       <c r="I104" t="s">
-        <v>2679</v>
+        <v>2671</v>
       </c>
       <c r="J104" s="1">
         <v>1</v>
@@ -19072,19 +19082,19 @@
         <v>116</v>
       </c>
       <c r="E105" t="s">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="F105" t="s">
         <v>17</v>
       </c>
       <c r="G105" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="H105" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="I105" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="J105" s="1">
         <v>1</v>
@@ -19113,19 +19123,19 @@
         <v>116</v>
       </c>
       <c r="E106" t="s">
-        <v>2684</v>
+        <v>2680</v>
       </c>
       <c r="F106" t="s">
         <v>17</v>
       </c>
       <c r="G106" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="H106" t="s">
-        <v>2686</v>
+        <v>2682</v>
       </c>
       <c r="I106" t="s">
-        <v>2687</v>
+        <v>2683</v>
       </c>
       <c r="J106" s="1">
         <v>1</v>
@@ -19151,22 +19161,22 @@
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="E107" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="F107" t="s">
         <v>17</v>
       </c>
       <c r="G107" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="H107" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="I107" t="s">
-        <v>2691</v>
+        <v>2687</v>
       </c>
       <c r="J107" s="1">
         <v>1</v>
@@ -19192,22 +19202,22 @@
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>580</v>
+        <v>41</v>
       </c>
       <c r="E108" t="s">
-        <v>2692</v>
+        <v>2688</v>
       </c>
       <c r="F108" t="s">
         <v>17</v>
       </c>
       <c r="G108" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="H108" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="I108" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="J108" s="1">
         <v>1</v>
@@ -19233,22 +19243,22 @@
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>156</v>
+        <v>580</v>
       </c>
       <c r="E109" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="F109" t="s">
         <v>17</v>
       </c>
       <c r="G109" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="H109" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
       <c r="I109" t="s">
-        <v>2699</v>
+        <v>2695</v>
       </c>
       <c r="J109" s="1">
         <v>1</v>
@@ -19274,22 +19284,22 @@
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="E110" t="s">
-        <v>2704</v>
+        <v>2696</v>
       </c>
       <c r="F110" t="s">
         <v>17</v>
       </c>
       <c r="G110" t="s">
-        <v>2705</v>
+        <v>2697</v>
       </c>
       <c r="H110" t="s">
-        <v>2706</v>
+        <v>2698</v>
       </c>
       <c r="I110" t="s">
-        <v>2707</v>
+        <v>2699</v>
       </c>
       <c r="J110" s="1">
         <v>1</v>
@@ -19315,22 +19325,22 @@
         <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="E111" t="s">
-        <v>2708</v>
+        <v>2704</v>
       </c>
       <c r="F111" t="s">
         <v>17</v>
       </c>
       <c r="G111" t="s">
-        <v>2709</v>
+        <v>2705</v>
       </c>
       <c r="H111" t="s">
-        <v>2710</v>
+        <v>2706</v>
       </c>
       <c r="I111" t="s">
-        <v>2711</v>
+        <v>2707</v>
       </c>
       <c r="J111" s="1">
         <v>1</v>
@@ -19356,22 +19366,22 @@
         <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E112" t="s">
-        <v>2720</v>
+        <v>2708</v>
       </c>
       <c r="F112" t="s">
         <v>17</v>
       </c>
       <c r="G112" t="s">
-        <v>2721</v>
+        <v>2709</v>
       </c>
       <c r="H112" t="s">
-        <v>2722</v>
+        <v>2710</v>
       </c>
       <c r="I112" t="s">
-        <v>2723</v>
+        <v>2711</v>
       </c>
       <c r="J112" s="1">
         <v>1</v>
@@ -19400,19 +19410,19 @@
         <v>41</v>
       </c>
       <c r="E113" t="s">
-        <v>2724</v>
+        <v>2720</v>
       </c>
       <c r="F113" t="s">
         <v>17</v>
       </c>
       <c r="G113" t="s">
-        <v>2725</v>
+        <v>2721</v>
       </c>
       <c r="H113" t="s">
-        <v>2726</v>
+        <v>2722</v>
       </c>
       <c r="I113" t="s">
-        <v>2727</v>
+        <v>2723</v>
       </c>
       <c r="J113" s="1">
         <v>1</v>
@@ -19438,31 +19448,31 @@
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>461</v>
+        <v>41</v>
       </c>
       <c r="E114" t="s">
-        <v>2728</v>
+        <v>2724</v>
       </c>
       <c r="F114" t="s">
         <v>17</v>
       </c>
       <c r="G114" t="s">
-        <v>2729</v>
+        <v>2725</v>
       </c>
       <c r="H114" t="s">
-        <v>2730</v>
+        <v>2726</v>
       </c>
       <c r="I114" t="s">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="J114" s="1">
         <v>1</v>
       </c>
       <c r="K114" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M114" t="s">
         <v>22</v>
@@ -19482,19 +19492,19 @@
         <v>461</v>
       </c>
       <c r="E115" t="s">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="F115" t="s">
         <v>17</v>
       </c>
       <c r="G115" t="s">
-        <v>2733</v>
+        <v>2729</v>
       </c>
       <c r="H115" t="s">
-        <v>2734</v>
+        <v>2730</v>
       </c>
       <c r="I115" t="s">
-        <v>2735</v>
+        <v>2731</v>
       </c>
       <c r="J115" s="1">
         <v>1</v>
@@ -19520,31 +19530,31 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>627</v>
+        <v>461</v>
       </c>
       <c r="E116" t="s">
-        <v>2736</v>
+        <v>2732</v>
       </c>
       <c r="F116" t="s">
         <v>17</v>
       </c>
       <c r="G116" t="s">
-        <v>2737</v>
+        <v>2733</v>
       </c>
       <c r="H116" t="s">
-        <v>2738</v>
+        <v>2734</v>
       </c>
       <c r="I116" t="s">
-        <v>2739</v>
+        <v>2735</v>
       </c>
       <c r="J116" s="1">
         <v>1</v>
       </c>
       <c r="K116" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M116" t="s">
         <v>22</v>
@@ -19561,22 +19571,22 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E117" t="s">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="F117" t="s">
         <v>17</v>
       </c>
       <c r="G117" t="s">
-        <v>2741</v>
+        <v>2737</v>
       </c>
       <c r="H117" t="s">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="I117" t="s">
-        <v>2743</v>
+        <v>2739</v>
       </c>
       <c r="J117" s="1">
         <v>1</v>
@@ -19602,22 +19612,22 @@
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>156</v>
+        <v>622</v>
       </c>
       <c r="E118" t="s">
-        <v>2744</v>
+        <v>2740</v>
       </c>
       <c r="F118" t="s">
         <v>17</v>
       </c>
       <c r="G118" t="s">
-        <v>2745</v>
+        <v>2741</v>
       </c>
       <c r="H118" t="s">
-        <v>2746</v>
+        <v>2742</v>
       </c>
       <c r="I118" t="s">
-        <v>2747</v>
+        <v>2743</v>
       </c>
       <c r="J118" s="1">
         <v>1</v>
@@ -19643,22 +19653,22 @@
         <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>432</v>
+        <v>156</v>
       </c>
       <c r="E119" t="s">
-        <v>2752</v>
+        <v>2744</v>
       </c>
       <c r="F119" t="s">
         <v>17</v>
       </c>
       <c r="G119" t="s">
-        <v>2753</v>
+        <v>2745</v>
       </c>
       <c r="H119" t="s">
-        <v>2754</v>
+        <v>2746</v>
       </c>
       <c r="I119" t="s">
-        <v>2755</v>
+        <v>2747</v>
       </c>
       <c r="J119" s="1">
         <v>1</v>
@@ -19684,22 +19694,22 @@
         <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>507</v>
+        <v>432</v>
       </c>
       <c r="E120" t="s">
-        <v>2756</v>
+        <v>2752</v>
       </c>
       <c r="F120" t="s">
         <v>17</v>
       </c>
       <c r="G120" t="s">
-        <v>2757</v>
+        <v>2753</v>
       </c>
       <c r="H120" t="s">
-        <v>2758</v>
+        <v>2754</v>
       </c>
       <c r="I120" t="s">
-        <v>2759</v>
+        <v>2755</v>
       </c>
       <c r="J120" s="1">
         <v>1</v>
@@ -19728,19 +19738,19 @@
         <v>507</v>
       </c>
       <c r="E121" t="s">
-        <v>2760</v>
+        <v>2756</v>
       </c>
       <c r="F121" t="s">
         <v>17</v>
       </c>
       <c r="G121" t="s">
-        <v>2761</v>
+        <v>2757</v>
       </c>
       <c r="H121" t="s">
-        <v>2762</v>
+        <v>2758</v>
       </c>
       <c r="I121" t="s">
-        <v>2763</v>
+        <v>2759</v>
       </c>
       <c r="J121" s="1">
         <v>1</v>
@@ -19766,22 +19776,22 @@
         <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>300</v>
+        <v>507</v>
       </c>
       <c r="E122" t="s">
-        <v>2764</v>
+        <v>2760</v>
       </c>
       <c r="F122" t="s">
         <v>17</v>
       </c>
       <c r="G122" t="s">
-        <v>2765</v>
+        <v>2761</v>
       </c>
       <c r="H122" t="s">
-        <v>2766</v>
+        <v>2762</v>
       </c>
       <c r="I122" t="s">
-        <v>2767</v>
+        <v>2763</v>
       </c>
       <c r="J122" s="1">
         <v>1</v>
@@ -19807,22 +19817,22 @@
         <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="E123" t="s">
-        <v>2768</v>
+        <v>2764</v>
       </c>
       <c r="F123" t="s">
         <v>17</v>
       </c>
       <c r="G123" t="s">
-        <v>2769</v>
+        <v>2765</v>
       </c>
       <c r="H123" t="s">
-        <v>2770</v>
+        <v>2766</v>
       </c>
       <c r="I123" t="s">
-        <v>2771</v>
+        <v>2767</v>
       </c>
       <c r="J123" s="1">
         <v>1</v>
@@ -19851,19 +19861,19 @@
         <v>56</v>
       </c>
       <c r="E124" t="s">
-        <v>2772</v>
+        <v>2768</v>
       </c>
       <c r="F124" t="s">
         <v>17</v>
       </c>
       <c r="G124" t="s">
-        <v>2773</v>
+        <v>2769</v>
       </c>
       <c r="H124" t="s">
-        <v>2774</v>
+        <v>2770</v>
       </c>
       <c r="I124" t="s">
-        <v>2775</v>
+        <v>2771</v>
       </c>
       <c r="J124" s="1">
         <v>1</v>
@@ -19889,22 +19899,22 @@
         <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E125" t="s">
-        <v>2780</v>
+        <v>2772</v>
       </c>
       <c r="F125" t="s">
         <v>17</v>
       </c>
       <c r="G125" t="s">
-        <v>2781</v>
+        <v>2773</v>
       </c>
       <c r="H125" t="s">
-        <v>2782</v>
+        <v>2774</v>
       </c>
       <c r="I125" t="s">
-        <v>2783</v>
+        <v>2775</v>
       </c>
       <c r="J125" s="1">
         <v>1</v>
@@ -19930,22 +19940,22 @@
         <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="E126" t="s">
-        <v>2784</v>
+        <v>2780</v>
       </c>
       <c r="F126" t="s">
         <v>17</v>
       </c>
       <c r="G126" t="s">
-        <v>2785</v>
+        <v>2781</v>
       </c>
       <c r="H126" t="s">
-        <v>2786</v>
+        <v>2782</v>
       </c>
       <c r="I126" t="s">
-        <v>2787</v>
+        <v>2783</v>
       </c>
       <c r="J126" s="1">
         <v>1</v>
@@ -19971,22 +19981,22 @@
         <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E127" t="s">
-        <v>2788</v>
+        <v>2784</v>
       </c>
       <c r="F127" t="s">
         <v>17</v>
       </c>
       <c r="G127" t="s">
-        <v>2789</v>
+        <v>2785</v>
       </c>
       <c r="H127" t="s">
-        <v>2790</v>
+        <v>2786</v>
       </c>
       <c r="I127" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
       <c r="J127" s="1">
         <v>1</v>
@@ -20012,22 +20022,22 @@
         <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="E128" t="s">
-        <v>2792</v>
+        <v>2788</v>
       </c>
       <c r="F128" t="s">
         <v>17</v>
       </c>
       <c r="G128" t="s">
-        <v>2793</v>
+        <v>2789</v>
       </c>
       <c r="H128" t="s">
-        <v>2794</v>
+        <v>2790</v>
       </c>
       <c r="I128" t="s">
-        <v>2795</v>
+        <v>2791</v>
       </c>
       <c r="J128" s="1">
         <v>1</v>
@@ -20053,22 +20063,22 @@
         <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="E129" t="s">
-        <v>2796</v>
+        <v>2792</v>
       </c>
       <c r="F129" t="s">
         <v>17</v>
       </c>
       <c r="G129" t="s">
-        <v>2797</v>
+        <v>2793</v>
       </c>
       <c r="H129" t="s">
-        <v>2798</v>
+        <v>2794</v>
       </c>
       <c r="I129" t="s">
-        <v>2799</v>
+        <v>2795</v>
       </c>
       <c r="J129" s="1">
         <v>1</v>
@@ -20094,22 +20104,22 @@
         <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>432</v>
+        <v>41</v>
       </c>
       <c r="E130" t="s">
-        <v>2800</v>
+        <v>2796</v>
       </c>
       <c r="F130" t="s">
         <v>17</v>
       </c>
       <c r="G130" t="s">
-        <v>2801</v>
+        <v>2797</v>
       </c>
       <c r="H130" t="s">
-        <v>2802</v>
+        <v>2798</v>
       </c>
       <c r="I130" t="s">
-        <v>2803</v>
+        <v>2799</v>
       </c>
       <c r="J130" s="1">
         <v>1</v>
@@ -20138,19 +20148,19 @@
         <v>432</v>
       </c>
       <c r="E131" t="s">
-        <v>2804</v>
+        <v>2800</v>
       </c>
       <c r="F131" t="s">
         <v>17</v>
       </c>
       <c r="G131" t="s">
-        <v>2805</v>
+        <v>2801</v>
       </c>
       <c r="H131" t="s">
-        <v>2806</v>
+        <v>2802</v>
       </c>
       <c r="I131" t="s">
-        <v>2807</v>
+        <v>2803</v>
       </c>
       <c r="J131" s="1">
         <v>1</v>
@@ -20179,19 +20189,19 @@
         <v>432</v>
       </c>
       <c r="E132" t="s">
-        <v>2808</v>
+        <v>2804</v>
       </c>
       <c r="F132" t="s">
         <v>17</v>
       </c>
       <c r="G132" t="s">
-        <v>2809</v>
+        <v>2805</v>
       </c>
       <c r="H132" t="s">
-        <v>2810</v>
+        <v>2806</v>
       </c>
       <c r="I132" t="s">
-        <v>2811</v>
+        <v>2807</v>
       </c>
       <c r="J132" s="1">
         <v>1</v>
@@ -20217,22 +20227,22 @@
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>41</v>
+        <v>432</v>
       </c>
       <c r="E133" t="s">
-        <v>2812</v>
+        <v>2808</v>
       </c>
       <c r="F133" t="s">
         <v>17</v>
       </c>
       <c r="G133" t="s">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="H133" t="s">
-        <v>2814</v>
+        <v>2810</v>
       </c>
       <c r="I133" t="s">
-        <v>2815</v>
+        <v>2811</v>
       </c>
       <c r="J133" s="1">
         <v>1</v>
@@ -20258,22 +20268,22 @@
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E134" t="s">
-        <v>2816</v>
+        <v>2812</v>
       </c>
       <c r="F134" t="s">
         <v>17</v>
       </c>
       <c r="G134" t="s">
-        <v>2817</v>
+        <v>2813</v>
       </c>
       <c r="H134" t="s">
-        <v>2818</v>
+        <v>2814</v>
       </c>
       <c r="I134" t="s">
-        <v>2819</v>
+        <v>2815</v>
       </c>
       <c r="J134" s="1">
         <v>1</v>
@@ -20299,22 +20309,22 @@
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="E135" t="s">
-        <v>2820</v>
+        <v>2816</v>
       </c>
       <c r="F135" t="s">
         <v>17</v>
       </c>
       <c r="G135" t="s">
-        <v>2821</v>
+        <v>2817</v>
       </c>
       <c r="H135" t="s">
-        <v>2822</v>
+        <v>2818</v>
       </c>
       <c r="I135" t="s">
-        <v>2823</v>
+        <v>2819</v>
       </c>
       <c r="J135" s="1">
         <v>1</v>
@@ -20340,22 +20350,22 @@
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>627</v>
+        <v>300</v>
       </c>
       <c r="E136" t="s">
-        <v>2824</v>
+        <v>2820</v>
       </c>
       <c r="F136" t="s">
         <v>17</v>
       </c>
       <c r="G136" t="s">
-        <v>2825</v>
+        <v>2821</v>
       </c>
       <c r="H136" t="s">
-        <v>2826</v>
+        <v>2822</v>
       </c>
       <c r="I136" t="s">
-        <v>2827</v>
+        <v>2823</v>
       </c>
       <c r="J136" s="1">
         <v>1</v>
@@ -20381,22 +20391,22 @@
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>124</v>
+        <v>627</v>
       </c>
       <c r="E137" t="s">
-        <v>2832</v>
+        <v>2824</v>
       </c>
       <c r="F137" t="s">
         <v>17</v>
       </c>
       <c r="G137" t="s">
-        <v>2833</v>
+        <v>2825</v>
       </c>
       <c r="H137" t="s">
-        <v>2834</v>
+        <v>2826</v>
       </c>
       <c r="I137" t="s">
-        <v>2835</v>
+        <v>2827</v>
       </c>
       <c r="J137" s="1">
         <v>1</v>
@@ -20422,31 +20432,31 @@
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>461</v>
+        <v>124</v>
       </c>
       <c r="E138" t="s">
-        <v>2836</v>
+        <v>2832</v>
       </c>
       <c r="F138" t="s">
         <v>17</v>
       </c>
       <c r="G138" t="s">
-        <v>2837</v>
+        <v>2833</v>
       </c>
       <c r="H138" t="s">
-        <v>2838</v>
+        <v>2834</v>
       </c>
       <c r="I138" t="s">
-        <v>2839</v>
+        <v>2835</v>
       </c>
       <c r="J138" s="1">
         <v>1</v>
       </c>
       <c r="K138" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L138" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M138" t="s">
         <v>22</v>
@@ -20463,31 +20473,31 @@
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>622</v>
+        <v>461</v>
       </c>
       <c r="E139" t="s">
-        <v>2840</v>
+        <v>2836</v>
       </c>
       <c r="F139" t="s">
         <v>17</v>
       </c>
       <c r="G139" t="s">
-        <v>2841</v>
+        <v>2837</v>
       </c>
       <c r="H139" t="s">
-        <v>2842</v>
+        <v>2838</v>
       </c>
       <c r="I139" t="s">
-        <v>2843</v>
+        <v>2839</v>
       </c>
       <c r="J139" s="1">
         <v>1</v>
       </c>
       <c r="K139" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M139" t="s">
         <v>22</v>
@@ -20504,31 +20514,31 @@
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>461</v>
+        <v>622</v>
       </c>
       <c r="E140" t="s">
-        <v>2844</v>
+        <v>2840</v>
       </c>
       <c r="F140" t="s">
         <v>17</v>
       </c>
       <c r="G140" t="s">
-        <v>2845</v>
+        <v>2841</v>
       </c>
       <c r="H140" t="s">
-        <v>2846</v>
+        <v>2842</v>
       </c>
       <c r="I140" t="s">
-        <v>2847</v>
+        <v>2843</v>
       </c>
       <c r="J140" s="1">
         <v>1</v>
       </c>
       <c r="K140" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L140" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M140" t="s">
         <v>22</v>
@@ -20545,31 +20555,31 @@
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>138</v>
+        <v>461</v>
       </c>
       <c r="E141" t="s">
-        <v>2848</v>
+        <v>2844</v>
       </c>
       <c r="F141" t="s">
         <v>17</v>
       </c>
       <c r="G141" t="s">
-        <v>2849</v>
+        <v>2845</v>
       </c>
       <c r="H141" t="s">
-        <v>2850</v>
+        <v>2846</v>
       </c>
       <c r="I141" t="s">
-        <v>2851</v>
+        <v>2847</v>
       </c>
       <c r="J141" s="1">
         <v>1</v>
       </c>
       <c r="K141" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L141" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M141" t="s">
         <v>22</v>
@@ -20586,22 +20596,22 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="E142" t="s">
-        <v>2852</v>
+        <v>2848</v>
       </c>
       <c r="F142" t="s">
         <v>17</v>
       </c>
       <c r="G142" t="s">
-        <v>2853</v>
+        <v>2849</v>
       </c>
       <c r="H142" t="s">
-        <v>2854</v>
+        <v>2850</v>
       </c>
       <c r="I142" t="s">
-        <v>2855</v>
+        <v>2851</v>
       </c>
       <c r="J142" s="1">
         <v>1</v>
@@ -20627,22 +20637,22 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E143" t="s">
-        <v>2860</v>
+        <v>2852</v>
       </c>
       <c r="F143" t="s">
         <v>17</v>
       </c>
       <c r="G143" t="s">
-        <v>2861</v>
+        <v>2853</v>
       </c>
       <c r="H143" t="s">
-        <v>2862</v>
+        <v>2854</v>
       </c>
       <c r="I143" t="s">
-        <v>2863</v>
+        <v>2855</v>
       </c>
       <c r="J143" s="1">
         <v>1</v>
@@ -20671,19 +20681,19 @@
         <v>27</v>
       </c>
       <c r="E144" t="s">
-        <v>2864</v>
+        <v>2860</v>
       </c>
       <c r="F144" t="s">
         <v>17</v>
       </c>
       <c r="G144" t="s">
-        <v>2865</v>
+        <v>2861</v>
       </c>
       <c r="H144" t="s">
-        <v>2866</v>
+        <v>2862</v>
       </c>
       <c r="I144" t="s">
-        <v>2867</v>
+        <v>2863</v>
       </c>
       <c r="J144" s="1">
         <v>1</v>
@@ -20712,19 +20722,19 @@
         <v>27</v>
       </c>
       <c r="E145" t="s">
-        <v>2868</v>
+        <v>2864</v>
       </c>
       <c r="F145" t="s">
         <v>17</v>
       </c>
       <c r="G145" t="s">
-        <v>2869</v>
+        <v>2865</v>
       </c>
       <c r="H145" t="s">
-        <v>2870</v>
+        <v>2866</v>
       </c>
       <c r="I145" t="s">
-        <v>2871</v>
+        <v>2867</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -20750,22 +20760,22 @@
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="E146" t="s">
-        <v>2872</v>
+        <v>2868</v>
       </c>
       <c r="F146" t="s">
         <v>17</v>
       </c>
       <c r="G146" t="s">
-        <v>2873</v>
+        <v>2869</v>
       </c>
       <c r="H146" t="s">
-        <v>2874</v>
+        <v>2870</v>
       </c>
       <c r="I146" t="s">
-        <v>2875</v>
+        <v>2871</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -20791,22 +20801,22 @@
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>466</v>
+        <v>179</v>
       </c>
       <c r="E147" t="s">
-        <v>2876</v>
+        <v>2872</v>
       </c>
       <c r="F147" t="s">
         <v>17</v>
       </c>
       <c r="G147" t="s">
-        <v>2877</v>
+        <v>2873</v>
       </c>
       <c r="H147" t="s">
-        <v>2878</v>
+        <v>2874</v>
       </c>
       <c r="I147" t="s">
-        <v>2879</v>
+        <v>2875</v>
       </c>
       <c r="J147" s="1">
         <v>1</v>
@@ -20832,22 +20842,22 @@
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>605</v>
+        <v>466</v>
       </c>
       <c r="E148" t="s">
-        <v>2884</v>
+        <v>2876</v>
       </c>
       <c r="F148" t="s">
         <v>17</v>
       </c>
       <c r="G148" t="s">
-        <v>2885</v>
+        <v>2877</v>
       </c>
       <c r="H148" t="s">
-        <v>2886</v>
+        <v>2878</v>
       </c>
       <c r="I148" t="s">
-        <v>2887</v>
+        <v>2879</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -20876,19 +20886,19 @@
         <v>605</v>
       </c>
       <c r="E149" t="s">
-        <v>2888</v>
+        <v>2884</v>
       </c>
       <c r="F149" t="s">
         <v>17</v>
       </c>
       <c r="G149" t="s">
-        <v>2889</v>
+        <v>2885</v>
       </c>
       <c r="H149" t="s">
-        <v>2890</v>
+        <v>2886</v>
       </c>
       <c r="I149" t="s">
-        <v>2891</v>
+        <v>2887</v>
       </c>
       <c r="J149" s="1">
         <v>1</v>
@@ -20914,31 +20924,31 @@
         <v>14</v>
       </c>
       <c r="D150" t="s">
-        <v>461</v>
+        <v>605</v>
       </c>
       <c r="E150" t="s">
-        <v>2896</v>
+        <v>2888</v>
       </c>
       <c r="F150" t="s">
         <v>17</v>
       </c>
       <c r="G150" t="s">
-        <v>2897</v>
+        <v>2889</v>
       </c>
       <c r="H150" t="s">
-        <v>2898</v>
+        <v>2890</v>
       </c>
       <c r="I150" t="s">
-        <v>2899</v>
+        <v>2891</v>
       </c>
       <c r="J150" s="1">
         <v>1</v>
       </c>
       <c r="K150" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L150" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M150" t="s">
         <v>22</v>
@@ -20955,31 +20965,31 @@
         <v>14</v>
       </c>
       <c r="D151" t="s">
-        <v>300</v>
+        <v>461</v>
       </c>
       <c r="E151" t="s">
-        <v>2900</v>
+        <v>2896</v>
       </c>
       <c r="F151" t="s">
         <v>17</v>
       </c>
       <c r="G151" t="s">
-        <v>2901</v>
+        <v>2897</v>
       </c>
       <c r="H151" t="s">
-        <v>2902</v>
+        <v>2898</v>
       </c>
       <c r="I151" t="s">
-        <v>2903</v>
+        <v>2899</v>
       </c>
       <c r="J151" s="1">
         <v>1</v>
       </c>
       <c r="K151" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L151" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M151" t="s">
         <v>22</v>
@@ -20996,22 +21006,22 @@
         <v>14</v>
       </c>
       <c r="D152" t="s">
-        <v>507</v>
+        <v>300</v>
       </c>
       <c r="E152" t="s">
-        <v>2904</v>
+        <v>2900</v>
       </c>
       <c r="F152" t="s">
         <v>17</v>
       </c>
       <c r="G152" t="s">
-        <v>2905</v>
+        <v>2901</v>
       </c>
       <c r="H152" t="s">
-        <v>2906</v>
+        <v>2902</v>
       </c>
       <c r="I152" t="s">
-        <v>2907</v>
+        <v>2903</v>
       </c>
       <c r="J152" s="1">
         <v>1</v>
@@ -21037,22 +21047,22 @@
         <v>14</v>
       </c>
       <c r="D153" t="s">
-        <v>605</v>
+        <v>507</v>
       </c>
       <c r="E153" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="F153" t="s">
         <v>17</v>
       </c>
       <c r="G153" t="s">
-        <v>2909</v>
+        <v>2905</v>
       </c>
       <c r="H153" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
       <c r="I153" t="s">
-        <v>2911</v>
+        <v>2907</v>
       </c>
       <c r="J153" s="1">
         <v>1</v>
@@ -21078,22 +21088,22 @@
         <v>14</v>
       </c>
       <c r="D154" t="s">
-        <v>147</v>
+        <v>605</v>
       </c>
       <c r="E154" t="s">
-        <v>2912</v>
+        <v>2908</v>
       </c>
       <c r="F154" t="s">
         <v>17</v>
       </c>
       <c r="G154" t="s">
-        <v>2913</v>
+        <v>2909</v>
       </c>
       <c r="H154" t="s">
-        <v>2914</v>
+        <v>2910</v>
       </c>
       <c r="I154" t="s">
-        <v>2915</v>
+        <v>2911</v>
       </c>
       <c r="J154" s="1">
         <v>1</v>
@@ -21122,19 +21132,19 @@
         <v>147</v>
       </c>
       <c r="E155" t="s">
-        <v>2920</v>
+        <v>2912</v>
       </c>
       <c r="F155" t="s">
         <v>17</v>
       </c>
       <c r="G155" t="s">
-        <v>2921</v>
+        <v>2913</v>
       </c>
       <c r="H155" t="s">
-        <v>2922</v>
+        <v>2914</v>
       </c>
       <c r="I155" t="s">
-        <v>2923</v>
+        <v>2915</v>
       </c>
       <c r="J155" s="1">
         <v>1</v>
@@ -21160,22 +21170,22 @@
         <v>14</v>
       </c>
       <c r="D156" t="s">
-        <v>300</v>
+        <v>147</v>
       </c>
       <c r="E156" t="s">
-        <v>2924</v>
+        <v>2920</v>
       </c>
       <c r="F156" t="s">
         <v>17</v>
       </c>
       <c r="G156" t="s">
-        <v>2925</v>
+        <v>2921</v>
       </c>
       <c r="H156" t="s">
-        <v>2926</v>
+        <v>2922</v>
       </c>
       <c r="I156" t="s">
-        <v>2927</v>
+        <v>2923</v>
       </c>
       <c r="J156" s="1">
         <v>1</v>
@@ -21204,19 +21214,19 @@
         <v>300</v>
       </c>
       <c r="E157" t="s">
-        <v>2928</v>
+        <v>2924</v>
       </c>
       <c r="F157" t="s">
         <v>17</v>
       </c>
       <c r="G157" t="s">
-        <v>2929</v>
+        <v>2925</v>
       </c>
       <c r="H157" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="I157" t="s">
-        <v>2931</v>
+        <v>2927</v>
       </c>
       <c r="J157" s="1">
         <v>1</v>
@@ -21245,19 +21255,19 @@
         <v>300</v>
       </c>
       <c r="E158" t="s">
-        <v>2932</v>
+        <v>2928</v>
       </c>
       <c r="F158" t="s">
         <v>17</v>
       </c>
       <c r="G158" t="s">
-        <v>2933</v>
+        <v>2929</v>
       </c>
       <c r="H158" t="s">
-        <v>2934</v>
+        <v>2930</v>
       </c>
       <c r="I158" t="s">
-        <v>2935</v>
+        <v>2931</v>
       </c>
       <c r="J158" s="1">
         <v>1</v>
@@ -21283,22 +21293,22 @@
         <v>14</v>
       </c>
       <c r="D159" t="s">
-        <v>116</v>
+        <v>300</v>
       </c>
       <c r="E159" t="s">
-        <v>2936</v>
+        <v>2932</v>
       </c>
       <c r="F159" t="s">
         <v>17</v>
       </c>
       <c r="G159" t="s">
-        <v>2937</v>
+        <v>2933</v>
       </c>
       <c r="H159" t="s">
-        <v>2938</v>
+        <v>2934</v>
       </c>
       <c r="I159" t="s">
-        <v>2939</v>
+        <v>2935</v>
       </c>
       <c r="J159" s="1">
         <v>1</v>
@@ -21324,22 +21334,22 @@
         <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="E160" t="s">
-        <v>2940</v>
+        <v>2936</v>
       </c>
       <c r="F160" t="s">
         <v>17</v>
       </c>
       <c r="G160" t="s">
-        <v>2941</v>
+        <v>2937</v>
       </c>
       <c r="H160" t="s">
-        <v>2942</v>
+        <v>2938</v>
       </c>
       <c r="I160" t="s">
-        <v>2943</v>
+        <v>2939</v>
       </c>
       <c r="J160" s="1">
         <v>1</v>
@@ -21365,22 +21375,22 @@
         <v>14</v>
       </c>
       <c r="D161" t="s">
-        <v>36</v>
+        <v>300</v>
       </c>
       <c r="E161" t="s">
-        <v>2944</v>
+        <v>2940</v>
       </c>
       <c r="F161" t="s">
         <v>17</v>
       </c>
       <c r="G161" t="s">
-        <v>2945</v>
+        <v>2941</v>
       </c>
       <c r="H161" t="s">
-        <v>2946</v>
+        <v>2942</v>
       </c>
       <c r="I161" t="s">
-        <v>2947</v>
+        <v>2943</v>
       </c>
       <c r="J161" s="1">
         <v>1</v>
@@ -21406,22 +21416,22 @@
         <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>466</v>
+        <v>36</v>
       </c>
       <c r="E162" t="s">
-        <v>2948</v>
+        <v>2944</v>
       </c>
       <c r="F162" t="s">
         <v>17</v>
       </c>
       <c r="G162" t="s">
-        <v>2949</v>
+        <v>2945</v>
       </c>
       <c r="H162" t="s">
-        <v>2950</v>
+        <v>2946</v>
       </c>
       <c r="I162" t="s">
-        <v>2951</v>
+        <v>2947</v>
       </c>
       <c r="J162" s="1">
         <v>1</v>
@@ -21447,22 +21457,22 @@
         <v>14</v>
       </c>
       <c r="D163" t="s">
-        <v>622</v>
+        <v>466</v>
       </c>
       <c r="E163" t="s">
-        <v>2952</v>
+        <v>2948</v>
       </c>
       <c r="F163" t="s">
         <v>17</v>
       </c>
       <c r="G163" t="s">
-        <v>2953</v>
+        <v>2949</v>
       </c>
       <c r="H163" t="s">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="I163" t="s">
-        <v>2955</v>
+        <v>2951</v>
       </c>
       <c r="J163" s="1">
         <v>1</v>
@@ -21488,22 +21498,22 @@
         <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>466</v>
+        <v>622</v>
       </c>
       <c r="E164" t="s">
-        <v>2956</v>
+        <v>2952</v>
       </c>
       <c r="F164" t="s">
         <v>17</v>
       </c>
       <c r="G164" t="s">
-        <v>2957</v>
+        <v>2953</v>
       </c>
       <c r="H164" t="s">
-        <v>2958</v>
+        <v>2954</v>
       </c>
       <c r="I164" t="s">
-        <v>2959</v>
+        <v>2955</v>
       </c>
       <c r="J164" s="1">
         <v>1</v>
@@ -21529,31 +21539,31 @@
         <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E165" t="s">
-        <v>2960</v>
+        <v>2956</v>
       </c>
       <c r="F165" t="s">
         <v>17</v>
       </c>
       <c r="G165" t="s">
-        <v>2961</v>
+        <v>2957</v>
       </c>
       <c r="H165" t="s">
-        <v>2962</v>
+        <v>2958</v>
       </c>
       <c r="I165" t="s">
-        <v>2963</v>
+        <v>2959</v>
       </c>
       <c r="J165" s="1">
         <v>1</v>
       </c>
       <c r="K165" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L165" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M165" t="s">
         <v>22</v>
@@ -21573,19 +21583,19 @@
         <v>461</v>
       </c>
       <c r="E166" t="s">
-        <v>2964</v>
+        <v>2960</v>
       </c>
       <c r="F166" t="s">
         <v>17</v>
       </c>
       <c r="G166" t="s">
-        <v>2965</v>
+        <v>2961</v>
       </c>
       <c r="H166" t="s">
-        <v>2966</v>
+        <v>2962</v>
       </c>
       <c r="I166" t="s">
-        <v>2967</v>
+        <v>2963</v>
       </c>
       <c r="J166" s="1">
         <v>1</v>
@@ -21614,19 +21624,19 @@
         <v>461</v>
       </c>
       <c r="E167" t="s">
-        <v>2968</v>
+        <v>2964</v>
       </c>
       <c r="F167" t="s">
         <v>17</v>
       </c>
       <c r="G167" t="s">
-        <v>2969</v>
+        <v>2965</v>
       </c>
       <c r="H167" t="s">
-        <v>2970</v>
+        <v>2966</v>
       </c>
       <c r="I167" t="s">
-        <v>2971</v>
+        <v>2967</v>
       </c>
       <c r="J167" s="1">
         <v>1</v>
@@ -21652,31 +21662,31 @@
         <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>627</v>
+        <v>461</v>
       </c>
       <c r="E168" t="s">
-        <v>2972</v>
+        <v>2968</v>
       </c>
       <c r="F168" t="s">
         <v>17</v>
       </c>
       <c r="G168" t="s">
-        <v>2973</v>
+        <v>2969</v>
       </c>
       <c r="H168" t="s">
-        <v>2974</v>
+        <v>2970</v>
       </c>
       <c r="I168" t="s">
-        <v>2975</v>
+        <v>2971</v>
       </c>
       <c r="J168" s="1">
         <v>1</v>
       </c>
       <c r="K168" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L168" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M168" t="s">
         <v>22</v>
@@ -21693,22 +21703,22 @@
         <v>14</v>
       </c>
       <c r="D169" t="s">
-        <v>56</v>
+        <v>627</v>
       </c>
       <c r="E169" t="s">
-        <v>2976</v>
+        <v>2972</v>
       </c>
       <c r="F169" t="s">
         <v>17</v>
       </c>
       <c r="G169" t="s">
-        <v>2977</v>
+        <v>2973</v>
       </c>
       <c r="H169" t="s">
-        <v>2978</v>
+        <v>2974</v>
       </c>
       <c r="I169" t="s">
-        <v>2979</v>
+        <v>2975</v>
       </c>
       <c r="J169" s="1">
         <v>1</v>
@@ -21734,22 +21744,22 @@
         <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="E170" t="s">
-        <v>2980</v>
+        <v>2976</v>
       </c>
       <c r="F170" t="s">
         <v>17</v>
       </c>
       <c r="G170" t="s">
-        <v>2981</v>
+        <v>2977</v>
       </c>
       <c r="H170" t="s">
-        <v>2982</v>
+        <v>2978</v>
       </c>
       <c r="I170" t="s">
-        <v>2983</v>
+        <v>2979</v>
       </c>
       <c r="J170" s="1">
         <v>1</v>
@@ -21775,22 +21785,22 @@
         <v>14</v>
       </c>
       <c r="D171" t="s">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="E171" t="s">
-        <v>2984</v>
+        <v>2980</v>
       </c>
       <c r="F171" t="s">
         <v>17</v>
       </c>
       <c r="G171" t="s">
-        <v>2985</v>
+        <v>2981</v>
       </c>
       <c r="H171" t="s">
-        <v>2986</v>
+        <v>2982</v>
       </c>
       <c r="I171" t="s">
-        <v>2987</v>
+        <v>2983</v>
       </c>
       <c r="J171" s="1">
         <v>1</v>
@@ -21819,19 +21829,19 @@
         <v>300</v>
       </c>
       <c r="E172" t="s">
-        <v>2988</v>
+        <v>2984</v>
       </c>
       <c r="F172" t="s">
         <v>17</v>
       </c>
       <c r="G172" t="s">
-        <v>2989</v>
+        <v>2985</v>
       </c>
       <c r="H172" t="s">
-        <v>2990</v>
+        <v>2986</v>
       </c>
       <c r="I172" t="s">
-        <v>2991</v>
+        <v>2987</v>
       </c>
       <c r="J172" s="1">
         <v>1</v>
@@ -21857,22 +21867,22 @@
         <v>14</v>
       </c>
       <c r="D173" t="s">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="E173" t="s">
-        <v>2996</v>
+        <v>2988</v>
       </c>
       <c r="F173" t="s">
         <v>17</v>
       </c>
       <c r="G173" t="s">
-        <v>2997</v>
+        <v>2989</v>
       </c>
       <c r="H173" t="s">
-        <v>2998</v>
+        <v>2990</v>
       </c>
       <c r="I173" t="s">
-        <v>2999</v>
+        <v>2991</v>
       </c>
       <c r="J173" s="1">
         <v>1</v>
@@ -21901,19 +21911,19 @@
         <v>41</v>
       </c>
       <c r="E174" t="s">
-        <v>3000</v>
+        <v>2996</v>
       </c>
       <c r="F174" t="s">
         <v>17</v>
       </c>
       <c r="G174" t="s">
-        <v>3001</v>
+        <v>2997</v>
       </c>
       <c r="H174" t="s">
-        <v>3002</v>
+        <v>2998</v>
       </c>
       <c r="I174" t="s">
-        <v>3003</v>
+        <v>2999</v>
       </c>
       <c r="J174" s="1">
         <v>1</v>
@@ -21939,22 +21949,22 @@
         <v>14</v>
       </c>
       <c r="D175" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E175" t="s">
-        <v>3004</v>
+        <v>3000</v>
       </c>
       <c r="F175" t="s">
         <v>17</v>
       </c>
       <c r="G175" t="s">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="H175" t="s">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="I175" t="s">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="J175" s="1">
         <v>1</v>
@@ -21980,22 +21990,22 @@
         <v>14</v>
       </c>
       <c r="D176" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E176" t="s">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="F176" t="s">
         <v>17</v>
       </c>
       <c r="G176" t="s">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="H176" t="s">
-        <v>3010</v>
+        <v>3006</v>
       </c>
       <c r="I176" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
       <c r="J176" s="1">
         <v>1</v>
@@ -22024,19 +22034,19 @@
         <v>15</v>
       </c>
       <c r="E177" t="s">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="F177" t="s">
         <v>17</v>
       </c>
       <c r="G177" t="s">
-        <v>3013</v>
+        <v>3009</v>
       </c>
       <c r="H177" t="s">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="I177" t="s">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="J177" s="1">
         <v>1</v>
@@ -22062,22 +22072,22 @@
         <v>14</v>
       </c>
       <c r="D178" t="s">
-        <v>605</v>
+        <v>15</v>
       </c>
       <c r="E178" t="s">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="F178" t="s">
         <v>17</v>
       </c>
       <c r="G178" t="s">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="H178" t="s">
-        <v>3018</v>
+        <v>3014</v>
       </c>
       <c r="I178" t="s">
-        <v>3019</v>
+        <v>3015</v>
       </c>
       <c r="J178" s="1">
         <v>1</v>
@@ -22103,22 +22113,22 @@
         <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>300</v>
+        <v>605</v>
       </c>
       <c r="E179" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="F179" t="s">
         <v>17</v>
       </c>
       <c r="G179" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="H179" t="s">
-        <v>3022</v>
+        <v>3018</v>
       </c>
       <c r="I179" t="s">
-        <v>3023</v>
+        <v>3019</v>
       </c>
       <c r="J179" s="1">
         <v>1</v>
@@ -22144,22 +22154,22 @@
         <v>14</v>
       </c>
       <c r="D180" t="s">
-        <v>466</v>
+        <v>300</v>
       </c>
       <c r="E180" t="s">
-        <v>3024</v>
+        <v>3020</v>
       </c>
       <c r="F180" t="s">
         <v>17</v>
       </c>
       <c r="G180" t="s">
-        <v>3025</v>
+        <v>3021</v>
       </c>
       <c r="H180" t="s">
-        <v>3026</v>
+        <v>3022</v>
       </c>
       <c r="I180" t="s">
-        <v>3027</v>
+        <v>3023</v>
       </c>
       <c r="J180" s="1">
         <v>1</v>
@@ -22185,22 +22195,22 @@
         <v>14</v>
       </c>
       <c r="D181" t="s">
-        <v>300</v>
+        <v>466</v>
       </c>
       <c r="E181" t="s">
-        <v>3028</v>
+        <v>3024</v>
       </c>
       <c r="F181" t="s">
         <v>17</v>
       </c>
       <c r="G181" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="H181" t="s">
-        <v>3030</v>
+        <v>3026</v>
       </c>
       <c r="I181" t="s">
-        <v>3031</v>
+        <v>3027</v>
       </c>
       <c r="J181" s="1">
         <v>1</v>
@@ -22226,22 +22236,22 @@
         <v>14</v>
       </c>
       <c r="D182" t="s">
-        <v>627</v>
+        <v>300</v>
       </c>
       <c r="E182" t="s">
-        <v>3032</v>
+        <v>3028</v>
       </c>
       <c r="F182" t="s">
         <v>17</v>
       </c>
       <c r="G182" t="s">
-        <v>3033</v>
+        <v>3029</v>
       </c>
       <c r="H182" t="s">
-        <v>3034</v>
+        <v>3030</v>
       </c>
       <c r="I182" t="s">
-        <v>3035</v>
+        <v>3031</v>
       </c>
       <c r="J182" s="1">
         <v>1</v>
@@ -22267,31 +22277,31 @@
         <v>14</v>
       </c>
       <c r="D183" t="s">
-        <v>461</v>
+        <v>627</v>
       </c>
       <c r="E183" t="s">
-        <v>3036</v>
+        <v>3032</v>
       </c>
       <c r="F183" t="s">
         <v>17</v>
       </c>
       <c r="G183" t="s">
-        <v>3037</v>
+        <v>3033</v>
       </c>
       <c r="H183" t="s">
-        <v>3038</v>
+        <v>3034</v>
       </c>
       <c r="I183" t="s">
-        <v>3039</v>
+        <v>3035</v>
       </c>
       <c r="J183" s="1">
         <v>1</v>
       </c>
       <c r="K183" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L183" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M183" t="s">
         <v>22</v>
@@ -22308,31 +22318,31 @@
         <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>622</v>
+        <v>461</v>
       </c>
       <c r="E184" t="s">
-        <v>3040</v>
+        <v>3036</v>
       </c>
       <c r="F184" t="s">
         <v>17</v>
       </c>
       <c r="G184" t="s">
-        <v>3041</v>
+        <v>3037</v>
       </c>
       <c r="H184" t="s">
-        <v>3042</v>
+        <v>3038</v>
       </c>
       <c r="I184" t="s">
-        <v>3043</v>
+        <v>3039</v>
       </c>
       <c r="J184" s="1">
         <v>1</v>
       </c>
       <c r="K184" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L184" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M184" t="s">
         <v>22</v>
@@ -22349,22 +22359,22 @@
         <v>14</v>
       </c>
       <c r="D185" t="s">
-        <v>300</v>
+        <v>622</v>
       </c>
       <c r="E185" t="s">
-        <v>3056</v>
+        <v>3040</v>
       </c>
       <c r="F185" t="s">
         <v>17</v>
       </c>
       <c r="G185" t="s">
-        <v>3057</v>
+        <v>3041</v>
       </c>
       <c r="H185" t="s">
-        <v>3058</v>
+        <v>3042</v>
       </c>
       <c r="I185" t="s">
-        <v>3059</v>
+        <v>3043</v>
       </c>
       <c r="J185" s="1">
         <v>1</v>
@@ -22390,22 +22400,22 @@
         <v>14</v>
       </c>
       <c r="D186" t="s">
-        <v>124</v>
+        <v>300</v>
       </c>
       <c r="E186" t="s">
-        <v>3064</v>
+        <v>3056</v>
       </c>
       <c r="F186" t="s">
         <v>17</v>
       </c>
       <c r="G186" t="s">
-        <v>3065</v>
+        <v>3057</v>
       </c>
       <c r="H186" t="s">
-        <v>3066</v>
+        <v>3058</v>
       </c>
       <c r="I186" t="s">
-        <v>3067</v>
+        <v>3059</v>
       </c>
       <c r="J186" s="1">
         <v>1</v>
@@ -22431,22 +22441,22 @@
         <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E187" t="s">
-        <v>3068</v>
+        <v>3064</v>
       </c>
       <c r="F187" t="s">
         <v>17</v>
       </c>
       <c r="G187" t="s">
-        <v>3069</v>
+        <v>3065</v>
       </c>
       <c r="H187" t="s">
-        <v>3070</v>
+        <v>3066</v>
       </c>
       <c r="I187" t="s">
-        <v>3071</v>
+        <v>3067</v>
       </c>
       <c r="J187" s="1">
         <v>1</v>
@@ -22472,22 +22482,22 @@
         <v>14</v>
       </c>
       <c r="D188" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E188" t="s">
-        <v>3072</v>
+        <v>3068</v>
       </c>
       <c r="F188" t="s">
         <v>17</v>
       </c>
       <c r="G188" t="s">
-        <v>3073</v>
+        <v>3069</v>
       </c>
       <c r="H188" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="I188" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="J188" s="1">
         <v>1</v>
@@ -22513,22 +22523,22 @@
         <v>14</v>
       </c>
       <c r="D189" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="E189" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="F189" t="s">
         <v>17</v>
       </c>
       <c r="G189" t="s">
-        <v>3077</v>
+        <v>3073</v>
       </c>
       <c r="H189" t="s">
-        <v>3078</v>
+        <v>3074</v>
       </c>
       <c r="I189" t="s">
-        <v>3079</v>
+        <v>3075</v>
       </c>
       <c r="J189" s="1">
         <v>1</v>
@@ -22557,19 +22567,19 @@
         <v>138</v>
       </c>
       <c r="E190" t="s">
-        <v>3080</v>
+        <v>3076</v>
       </c>
       <c r="F190" t="s">
         <v>17</v>
       </c>
       <c r="G190" t="s">
-        <v>3081</v>
+        <v>3077</v>
       </c>
       <c r="H190" t="s">
-        <v>3082</v>
+        <v>3078</v>
       </c>
       <c r="I190" t="s">
-        <v>3083</v>
+        <v>3079</v>
       </c>
       <c r="J190" s="1">
         <v>1</v>
@@ -22595,22 +22605,22 @@
         <v>14</v>
       </c>
       <c r="D191" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="E191" t="s">
-        <v>3084</v>
+        <v>3080</v>
       </c>
       <c r="F191" t="s">
         <v>17</v>
       </c>
       <c r="G191" t="s">
-        <v>3085</v>
+        <v>3081</v>
       </c>
       <c r="H191" t="s">
-        <v>3086</v>
+        <v>3082</v>
       </c>
       <c r="I191" t="s">
-        <v>3087</v>
+        <v>3083</v>
       </c>
       <c r="J191" s="1">
         <v>1</v>
@@ -22636,22 +22646,22 @@
         <v>14</v>
       </c>
       <c r="D192" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="E192" t="s">
-        <v>3096</v>
+        <v>3084</v>
       </c>
       <c r="F192" t="s">
         <v>17</v>
       </c>
       <c r="G192" t="s">
-        <v>3097</v>
+        <v>3085</v>
       </c>
       <c r="H192" t="s">
-        <v>3098</v>
+        <v>3086</v>
       </c>
       <c r="I192" t="s">
-        <v>3099</v>
+        <v>3087</v>
       </c>
       <c r="J192" s="1">
         <v>1</v>
@@ -22677,22 +22687,22 @@
         <v>14</v>
       </c>
       <c r="D193" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E193" t="s">
-        <v>3100</v>
+        <v>3096</v>
       </c>
       <c r="F193" t="s">
         <v>17</v>
       </c>
       <c r="G193" t="s">
-        <v>3101</v>
+        <v>3097</v>
       </c>
       <c r="H193" t="s">
-        <v>3102</v>
+        <v>3098</v>
       </c>
       <c r="I193" t="s">
-        <v>3103</v>
+        <v>3099</v>
       </c>
       <c r="J193" s="1">
         <v>1</v>
@@ -22718,22 +22728,22 @@
         <v>14</v>
       </c>
       <c r="D194" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E194" t="s">
-        <v>3104</v>
+        <v>3100</v>
       </c>
       <c r="F194" t="s">
         <v>17</v>
       </c>
       <c r="G194" t="s">
-        <v>3105</v>
+        <v>3101</v>
       </c>
       <c r="H194" t="s">
-        <v>3106</v>
+        <v>3102</v>
       </c>
       <c r="I194" t="s">
-        <v>3107</v>
+        <v>3103</v>
       </c>
       <c r="J194" s="1">
         <v>1</v>
@@ -22759,22 +22769,22 @@
         <v>14</v>
       </c>
       <c r="D195" t="s">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="E195" t="s">
-        <v>3112</v>
+        <v>3104</v>
       </c>
       <c r="F195" t="s">
         <v>17</v>
       </c>
       <c r="G195" t="s">
-        <v>3113</v>
+        <v>3105</v>
       </c>
       <c r="H195" t="s">
-        <v>3114</v>
+        <v>3106</v>
       </c>
       <c r="I195" t="s">
-        <v>3115</v>
+        <v>3107</v>
       </c>
       <c r="J195" s="1">
         <v>1</v>
@@ -22800,22 +22810,22 @@
         <v>14</v>
       </c>
       <c r="D196" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="E196" t="s">
-        <v>3116</v>
+        <v>3112</v>
       </c>
       <c r="F196" t="s">
         <v>17</v>
       </c>
       <c r="G196" t="s">
-        <v>3117</v>
+        <v>3113</v>
       </c>
       <c r="H196" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="I196" t="s">
-        <v>3119</v>
+        <v>3115</v>
       </c>
       <c r="J196" s="1">
         <v>1</v>
@@ -22841,22 +22851,22 @@
         <v>14</v>
       </c>
       <c r="D197" t="s">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="E197" t="s">
-        <v>3120</v>
+        <v>3116</v>
       </c>
       <c r="F197" t="s">
         <v>17</v>
       </c>
       <c r="G197" t="s">
-        <v>3121</v>
+        <v>3117</v>
       </c>
       <c r="H197" t="s">
-        <v>3122</v>
+        <v>3118</v>
       </c>
       <c r="I197" t="s">
-        <v>3123</v>
+        <v>3119</v>
       </c>
       <c r="J197" s="1">
         <v>1</v>
@@ -22882,22 +22892,22 @@
         <v>14</v>
       </c>
       <c r="D198" t="s">
-        <v>27</v>
+        <v>466</v>
       </c>
       <c r="E198" t="s">
-        <v>3124</v>
+        <v>3120</v>
       </c>
       <c r="F198" t="s">
         <v>17</v>
       </c>
       <c r="G198" t="s">
-        <v>3125</v>
+        <v>3121</v>
       </c>
       <c r="H198" t="s">
-        <v>3126</v>
+        <v>3122</v>
       </c>
       <c r="I198" t="s">
-        <v>3127</v>
+        <v>3123</v>
       </c>
       <c r="J198" s="1">
         <v>1</v>
@@ -22926,19 +22936,19 @@
         <v>27</v>
       </c>
       <c r="E199" t="s">
-        <v>3128</v>
+        <v>3124</v>
       </c>
       <c r="F199" t="s">
         <v>17</v>
       </c>
       <c r="G199" t="s">
-        <v>3129</v>
+        <v>3125</v>
       </c>
       <c r="H199" t="s">
-        <v>3130</v>
+        <v>3126</v>
       </c>
       <c r="I199" t="s">
-        <v>3131</v>
+        <v>3127</v>
       </c>
       <c r="J199" s="1">
         <v>1</v>
@@ -22964,28 +22974,28 @@
         <v>14</v>
       </c>
       <c r="D200" t="s">
-        <v>627</v>
+        <v>27</v>
       </c>
       <c r="E200" t="s">
-        <v>3132</v>
+        <v>3128</v>
       </c>
       <c r="F200" t="s">
         <v>17</v>
       </c>
       <c r="G200" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="H200" t="s">
-        <v>3134</v>
+        <v>3130</v>
       </c>
       <c r="I200" t="s">
-        <v>3135</v>
+        <v>3131</v>
       </c>
       <c r="J200" s="1">
         <v>1</v>
       </c>
       <c r="K200" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L200" t="s">
         <v>21</v>
@@ -23005,28 +23015,28 @@
         <v>14</v>
       </c>
       <c r="D201" t="s">
-        <v>36</v>
+        <v>627</v>
       </c>
       <c r="E201" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F201" t="s">
         <v>17</v>
       </c>
       <c r="G201" t="s">
-        <v>3137</v>
+        <v>3133</v>
       </c>
       <c r="H201" t="s">
-        <v>3138</v>
+        <v>3134</v>
       </c>
       <c r="I201" t="s">
-        <v>3139</v>
+        <v>3135</v>
       </c>
       <c r="J201" s="1">
         <v>1</v>
       </c>
       <c r="K201" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L201" t="s">
         <v>21</v>
@@ -23046,22 +23056,22 @@
         <v>14</v>
       </c>
       <c r="D202" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E202" t="s">
-        <v>3140</v>
+        <v>3136</v>
       </c>
       <c r="F202" t="s">
         <v>17</v>
       </c>
       <c r="G202" t="s">
-        <v>3141</v>
+        <v>3137</v>
       </c>
       <c r="H202" t="s">
-        <v>3142</v>
+        <v>3138</v>
       </c>
       <c r="I202" t="s">
-        <v>3143</v>
+        <v>3139</v>
       </c>
       <c r="J202" s="1">
         <v>1</v>
@@ -23087,22 +23097,22 @@
         <v>14</v>
       </c>
       <c r="D203" t="s">
-        <v>622</v>
+        <v>83</v>
       </c>
       <c r="E203" t="s">
-        <v>3144</v>
+        <v>3140</v>
       </c>
       <c r="F203" t="s">
         <v>17</v>
       </c>
       <c r="G203" t="s">
-        <v>3145</v>
+        <v>3141</v>
       </c>
       <c r="H203" t="s">
-        <v>3146</v>
+        <v>3142</v>
       </c>
       <c r="I203" t="s">
-        <v>3147</v>
+        <v>3143</v>
       </c>
       <c r="J203" s="1">
         <v>1</v>
@@ -23128,22 +23138,22 @@
         <v>14</v>
       </c>
       <c r="D204" t="s">
-        <v>88</v>
+        <v>622</v>
       </c>
       <c r="E204" t="s">
-        <v>3148</v>
+        <v>3144</v>
       </c>
       <c r="F204" t="s">
         <v>17</v>
       </c>
       <c r="G204" t="s">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="H204" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="I204" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
       <c r="J204" s="1">
         <v>1</v>
@@ -23169,22 +23179,22 @@
         <v>14</v>
       </c>
       <c r="D205" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="E205" t="s">
-        <v>3152</v>
+        <v>3148</v>
       </c>
       <c r="F205" t="s">
         <v>17</v>
       </c>
       <c r="G205" t="s">
-        <v>3153</v>
+        <v>3149</v>
       </c>
       <c r="H205" t="s">
-        <v>3154</v>
+        <v>3150</v>
       </c>
       <c r="I205" t="s">
-        <v>3155</v>
+        <v>3151</v>
       </c>
       <c r="J205" s="1">
         <v>1</v>
@@ -23213,19 +23223,19 @@
         <v>179</v>
       </c>
       <c r="E206" t="s">
-        <v>3156</v>
+        <v>3152</v>
       </c>
       <c r="F206" t="s">
         <v>17</v>
       </c>
       <c r="G206" t="s">
-        <v>3157</v>
+        <v>3153</v>
       </c>
       <c r="H206" t="s">
-        <v>3158</v>
+        <v>3154</v>
       </c>
       <c r="I206" t="s">
-        <v>3159</v>
+        <v>3155</v>
       </c>
       <c r="J206" s="1">
         <v>1</v>
@@ -23254,19 +23264,19 @@
         <v>179</v>
       </c>
       <c r="E207" t="s">
-        <v>3160</v>
+        <v>3156</v>
       </c>
       <c r="F207" t="s">
         <v>17</v>
       </c>
       <c r="G207" t="s">
-        <v>3161</v>
+        <v>3157</v>
       </c>
       <c r="H207" t="s">
-        <v>3162</v>
+        <v>3158</v>
       </c>
       <c r="I207" t="s">
-        <v>3163</v>
+        <v>3159</v>
       </c>
       <c r="J207" s="1">
         <v>1</v>
@@ -23292,22 +23302,22 @@
         <v>14</v>
       </c>
       <c r="D208" t="s">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="E208" t="s">
-        <v>3164</v>
+        <v>3160</v>
       </c>
       <c r="F208" t="s">
         <v>17</v>
       </c>
       <c r="G208" t="s">
-        <v>3165</v>
+        <v>3161</v>
       </c>
       <c r="H208" t="s">
-        <v>3166</v>
+        <v>3162</v>
       </c>
       <c r="I208" t="s">
-        <v>3167</v>
+        <v>3163</v>
       </c>
       <c r="J208" s="1">
         <v>1</v>
@@ -23333,22 +23343,22 @@
         <v>14</v>
       </c>
       <c r="D209" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="E209" t="s">
-        <v>3168</v>
+        <v>3164</v>
       </c>
       <c r="F209" t="s">
         <v>17</v>
       </c>
       <c r="G209" t="s">
-        <v>3169</v>
+        <v>3165</v>
       </c>
       <c r="H209" t="s">
-        <v>3170</v>
+        <v>3166</v>
       </c>
       <c r="I209" t="s">
-        <v>3171</v>
+        <v>3167</v>
       </c>
       <c r="J209" s="1">
         <v>1</v>
@@ -23374,22 +23384,22 @@
         <v>14</v>
       </c>
       <c r="D210" t="s">
-        <v>300</v>
+        <v>88</v>
       </c>
       <c r="E210" t="s">
-        <v>3172</v>
+        <v>3168</v>
       </c>
       <c r="F210" t="s">
         <v>17</v>
       </c>
       <c r="G210" t="s">
-        <v>3173</v>
+        <v>3169</v>
       </c>
       <c r="H210" t="s">
-        <v>3174</v>
+        <v>3170</v>
       </c>
       <c r="I210" t="s">
-        <v>3175</v>
+        <v>3171</v>
       </c>
       <c r="J210" s="1">
         <v>1</v>
@@ -23415,22 +23425,22 @@
         <v>14</v>
       </c>
       <c r="D211" t="s">
-        <v>466</v>
+        <v>300</v>
       </c>
       <c r="E211" t="s">
-        <v>3176</v>
+        <v>3172</v>
       </c>
       <c r="F211" t="s">
         <v>17</v>
       </c>
       <c r="G211" t="s">
-        <v>3177</v>
+        <v>3173</v>
       </c>
       <c r="H211" t="s">
-        <v>3178</v>
+        <v>3174</v>
       </c>
       <c r="I211" t="s">
-        <v>3179</v>
+        <v>3175</v>
       </c>
       <c r="J211" s="1">
         <v>1</v>
@@ -23456,22 +23466,22 @@
         <v>14</v>
       </c>
       <c r="D212" t="s">
-        <v>36</v>
+        <v>466</v>
       </c>
       <c r="E212" t="s">
-        <v>3180</v>
+        <v>3176</v>
       </c>
       <c r="F212" t="s">
         <v>17</v>
       </c>
       <c r="G212" t="s">
-        <v>3181</v>
+        <v>3177</v>
       </c>
       <c r="H212" t="s">
-        <v>3182</v>
+        <v>3178</v>
       </c>
       <c r="I212" t="s">
-        <v>3183</v>
+        <v>3179</v>
       </c>
       <c r="J212" s="1">
         <v>1</v>
@@ -23497,22 +23507,22 @@
         <v>14</v>
       </c>
       <c r="D213" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="E213" t="s">
-        <v>3184</v>
+        <v>3180</v>
       </c>
       <c r="F213" t="s">
         <v>17</v>
       </c>
       <c r="G213" t="s">
-        <v>3185</v>
+        <v>3181</v>
       </c>
       <c r="H213" t="s">
-        <v>3186</v>
+        <v>3182</v>
       </c>
       <c r="I213" t="s">
-        <v>3187</v>
+        <v>3183</v>
       </c>
       <c r="J213" s="1">
         <v>1</v>
@@ -23538,22 +23548,22 @@
         <v>14</v>
       </c>
       <c r="D214" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="E214" t="s">
-        <v>3192</v>
+        <v>3184</v>
       </c>
       <c r="F214" t="s">
         <v>17</v>
       </c>
       <c r="G214" t="s">
-        <v>3193</v>
+        <v>3185</v>
       </c>
       <c r="H214" t="s">
-        <v>3194</v>
+        <v>3186</v>
       </c>
       <c r="I214" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
       <c r="J214" s="1">
         <v>1</v>
@@ -23582,19 +23592,19 @@
         <v>83</v>
       </c>
       <c r="E215" t="s">
-        <v>3196</v>
+        <v>3192</v>
       </c>
       <c r="F215" t="s">
         <v>17</v>
       </c>
       <c r="G215" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
       <c r="H215" t="s">
-        <v>3198</v>
+        <v>3194</v>
       </c>
       <c r="I215" t="s">
-        <v>3199</v>
+        <v>3195</v>
       </c>
       <c r="J215" s="1">
         <v>1</v>
@@ -23620,22 +23630,22 @@
         <v>14</v>
       </c>
       <c r="D216" t="s">
-        <v>580</v>
+        <v>83</v>
       </c>
       <c r="E216" t="s">
-        <v>3212</v>
+        <v>3196</v>
       </c>
       <c r="F216" t="s">
         <v>17</v>
       </c>
       <c r="G216" t="s">
-        <v>3213</v>
+        <v>3197</v>
       </c>
       <c r="H216" t="s">
-        <v>3214</v>
+        <v>3198</v>
       </c>
       <c r="I216" t="s">
-        <v>3215</v>
+        <v>3199</v>
       </c>
       <c r="J216" s="1">
         <v>1</v>
@@ -23661,31 +23671,31 @@
         <v>14</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>580</v>
       </c>
       <c r="E217" t="s">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="F217" t="s">
         <v>17</v>
       </c>
       <c r="G217" t="s">
-        <v>3221</v>
+        <v>3213</v>
       </c>
       <c r="H217" t="s">
-        <v>3222</v>
+        <v>3214</v>
       </c>
       <c r="I217" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="J217" s="1">
         <v>1</v>
       </c>
       <c r="K217" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L217" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M217" t="s">
         <v>22</v>
@@ -23702,31 +23712,31 @@
         <v>14</v>
       </c>
       <c r="D218" t="s">
-        <v>124</v>
+        <v>461</v>
       </c>
       <c r="E218" t="s">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="F218" t="s">
         <v>17</v>
       </c>
       <c r="G218" t="s">
-        <v>3225</v>
+        <v>3221</v>
       </c>
       <c r="H218" t="s">
-        <v>3226</v>
+        <v>3222</v>
       </c>
       <c r="I218" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="J218" s="1">
         <v>1</v>
       </c>
       <c r="K218" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L218" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M218" t="s">
         <v>22</v>
@@ -23743,22 +23753,22 @@
         <v>14</v>
       </c>
       <c r="D219" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="E219" t="s">
-        <v>3228</v>
+        <v>3224</v>
       </c>
       <c r="F219" t="s">
         <v>17</v>
       </c>
       <c r="G219" t="s">
-        <v>3229</v>
+        <v>3225</v>
       </c>
       <c r="H219" t="s">
-        <v>3230</v>
+        <v>3226</v>
       </c>
       <c r="I219" t="s">
-        <v>3231</v>
+        <v>3227</v>
       </c>
       <c r="J219" s="1">
         <v>1</v>
@@ -23784,22 +23794,22 @@
         <v>14</v>
       </c>
       <c r="D220" t="s">
-        <v>580</v>
+        <v>88</v>
       </c>
       <c r="E220" t="s">
-        <v>3232</v>
+        <v>3228</v>
       </c>
       <c r="F220" t="s">
         <v>17</v>
       </c>
       <c r="G220" t="s">
-        <v>3233</v>
+        <v>3229</v>
       </c>
       <c r="H220" t="s">
-        <v>3234</v>
+        <v>3230</v>
       </c>
       <c r="I220" t="s">
-        <v>3235</v>
+        <v>3231</v>
       </c>
       <c r="J220" s="1">
         <v>1</v>
@@ -23825,22 +23835,22 @@
         <v>14</v>
       </c>
       <c r="D221" t="s">
-        <v>56</v>
+        <v>580</v>
       </c>
       <c r="E221" t="s">
-        <v>3236</v>
+        <v>3232</v>
       </c>
       <c r="F221" t="s">
         <v>17</v>
       </c>
       <c r="G221" t="s">
-        <v>3237</v>
+        <v>3233</v>
       </c>
       <c r="H221" t="s">
-        <v>3238</v>
+        <v>3234</v>
       </c>
       <c r="I221" t="s">
-        <v>3239</v>
+        <v>3235</v>
       </c>
       <c r="J221" s="1">
         <v>1</v>
@@ -23866,31 +23876,31 @@
         <v>14</v>
       </c>
       <c r="D222" t="s">
-        <v>461</v>
+        <v>56</v>
       </c>
       <c r="E222" t="s">
-        <v>3240</v>
+        <v>3236</v>
       </c>
       <c r="F222" t="s">
         <v>17</v>
       </c>
       <c r="G222" t="s">
-        <v>3241</v>
+        <v>3237</v>
       </c>
       <c r="H222" t="s">
-        <v>3242</v>
+        <v>3238</v>
       </c>
       <c r="I222" t="s">
-        <v>3243</v>
+        <v>3239</v>
       </c>
       <c r="J222" s="1">
         <v>1</v>
       </c>
       <c r="K222" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L222" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M222" t="s">
         <v>22</v>
@@ -23907,31 +23917,31 @@
         <v>14</v>
       </c>
       <c r="D223" t="s">
-        <v>116</v>
+        <v>461</v>
       </c>
       <c r="E223" t="s">
-        <v>3244</v>
+        <v>3240</v>
       </c>
       <c r="F223" t="s">
         <v>17</v>
       </c>
       <c r="G223" t="s">
-        <v>3245</v>
+        <v>3241</v>
       </c>
       <c r="H223" t="s">
-        <v>3246</v>
+        <v>3242</v>
       </c>
       <c r="I223" t="s">
-        <v>3247</v>
+        <v>3243</v>
       </c>
       <c r="J223" s="1">
         <v>1</v>
       </c>
       <c r="K223" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L223" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M223" t="s">
         <v>22</v>
@@ -23951,19 +23961,19 @@
         <v>116</v>
       </c>
       <c r="E224" t="s">
-        <v>3248</v>
+        <v>3244</v>
       </c>
       <c r="F224" t="s">
         <v>17</v>
       </c>
       <c r="G224" t="s">
-        <v>3249</v>
+        <v>3245</v>
       </c>
       <c r="H224" t="s">
-        <v>3250</v>
+        <v>3246</v>
       </c>
       <c r="I224" t="s">
-        <v>3251</v>
+        <v>3247</v>
       </c>
       <c r="J224" s="1">
         <v>1</v>
@@ -23989,22 +23999,22 @@
         <v>14</v>
       </c>
       <c r="D225" t="s">
-        <v>466</v>
+        <v>116</v>
       </c>
       <c r="E225" t="s">
-        <v>3252</v>
+        <v>3248</v>
       </c>
       <c r="F225" t="s">
         <v>17</v>
       </c>
       <c r="G225" t="s">
-        <v>3253</v>
+        <v>3249</v>
       </c>
       <c r="H225" t="s">
-        <v>3254</v>
+        <v>3250</v>
       </c>
       <c r="I225" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="J225" s="1">
         <v>1</v>
@@ -24033,19 +24043,19 @@
         <v>466</v>
       </c>
       <c r="E226" t="s">
-        <v>3256</v>
+        <v>3252</v>
       </c>
       <c r="F226" t="s">
         <v>17</v>
       </c>
       <c r="G226" t="s">
-        <v>3257</v>
+        <v>3253</v>
       </c>
       <c r="H226" t="s">
-        <v>3258</v>
+        <v>3254</v>
       </c>
       <c r="I226" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="J226" s="1">
         <v>1</v>
@@ -24071,22 +24081,22 @@
         <v>14</v>
       </c>
       <c r="D227" t="s">
-        <v>156</v>
+        <v>466</v>
       </c>
       <c r="E227" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="F227" t="s">
         <v>17</v>
       </c>
       <c r="G227" t="s">
-        <v>3261</v>
+        <v>3257</v>
       </c>
       <c r="H227" t="s">
-        <v>3262</v>
+        <v>3258</v>
       </c>
       <c r="I227" t="s">
-        <v>3263</v>
+        <v>3259</v>
       </c>
       <c r="J227" s="1">
         <v>1</v>
@@ -24112,22 +24122,22 @@
         <v>14</v>
       </c>
       <c r="D228" t="s">
-        <v>605</v>
+        <v>156</v>
       </c>
       <c r="E228" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="F228" t="s">
         <v>17</v>
       </c>
       <c r="G228" t="s">
-        <v>3265</v>
+        <v>3261</v>
       </c>
       <c r="H228" t="s">
-        <v>3266</v>
+        <v>3262</v>
       </c>
       <c r="I228" t="s">
-        <v>3267</v>
+        <v>3263</v>
       </c>
       <c r="J228" s="1">
         <v>1</v>
@@ -24153,22 +24163,22 @@
         <v>14</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>605</v>
       </c>
       <c r="E229" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="F229" t="s">
         <v>17</v>
       </c>
       <c r="G229" t="s">
-        <v>3269</v>
+        <v>3265</v>
       </c>
       <c r="H229" t="s">
-        <v>3270</v>
+        <v>3266</v>
       </c>
       <c r="I229" t="s">
-        <v>3271</v>
+        <v>3267</v>
       </c>
       <c r="J229" s="1">
         <v>1</v>
@@ -24194,22 +24204,22 @@
         <v>14</v>
       </c>
       <c r="D230" t="s">
-        <v>156</v>
+        <v>466</v>
       </c>
       <c r="E230" t="s">
-        <v>3272</v>
+        <v>3268</v>
       </c>
       <c r="F230" t="s">
         <v>17</v>
       </c>
       <c r="G230" t="s">
-        <v>3273</v>
+        <v>3269</v>
       </c>
       <c r="H230" t="s">
-        <v>3274</v>
+        <v>3270</v>
       </c>
       <c r="I230" t="s">
-        <v>3275</v>
+        <v>3271</v>
       </c>
       <c r="J230" s="1">
         <v>1</v>
@@ -24235,22 +24245,22 @@
         <v>14</v>
       </c>
       <c r="D231" t="s">
-        <v>605</v>
+        <v>156</v>
       </c>
       <c r="E231" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
       <c r="F231" t="s">
         <v>17</v>
       </c>
       <c r="G231" t="s">
-        <v>3277</v>
+        <v>3273</v>
       </c>
       <c r="H231" t="s">
-        <v>3278</v>
+        <v>3274</v>
       </c>
       <c r="I231" t="s">
-        <v>3279</v>
+        <v>3275</v>
       </c>
       <c r="J231" s="1">
         <v>1</v>
@@ -24279,101 +24289,101 @@
         <v>605</v>
       </c>
       <c r="E232" t="s">
+        <v>3276</v>
+      </c>
+      <c r="F232" t="s">
+        <v>17</v>
+      </c>
+      <c r="G232" t="s">
+        <v>3277</v>
+      </c>
+      <c r="H232" t="s">
+        <v>3278</v>
+      </c>
+      <c r="I232" t="s">
+        <v>3279</v>
+      </c>
+      <c r="J232" s="1">
+        <v>1</v>
+      </c>
+      <c r="K232" s="1">
+        <v>0</v>
+      </c>
+      <c r="L232" t="s">
+        <v>21</v>
+      </c>
+      <c r="M232" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>3</v>
+      </c>
+      <c r="B233" t="s">
+        <v>13</v>
+      </c>
+      <c r="C233" t="s">
+        <v>14</v>
+      </c>
+      <c r="D233" t="s">
+        <v>605</v>
+      </c>
+      <c r="E233" t="s">
         <v>3280</v>
       </c>
-      <c r="F232" t="s">
-        <v>17</v>
-      </c>
-      <c r="G232" t="s">
+      <c r="F233" t="s">
+        <v>17</v>
+      </c>
+      <c r="G233" t="s">
         <v>3281</v>
       </c>
-      <c r="H232" t="s">
+      <c r="H233" t="s">
         <v>3282</v>
       </c>
-      <c r="I232" t="s">
+      <c r="I233" t="s">
         <v>3283</v>
       </c>
-      <c r="J232" s="1">
-        <v>1</v>
-      </c>
-      <c r="K232" s="1">
-        <v>0</v>
-      </c>
-      <c r="L232" t="s">
-        <v>21</v>
-      </c>
-      <c r="M232" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A233" s="1">
-        <v>3</v>
-      </c>
-      <c r="B233" t="s">
-        <v>13</v>
-      </c>
-      <c r="C233" t="s">
-        <v>14</v>
-      </c>
-      <c r="D233" t="s">
+      <c r="J233" s="1">
+        <v>1</v>
+      </c>
+      <c r="K233" s="1">
+        <v>0</v>
+      </c>
+      <c r="L233" t="s">
+        <v>21</v>
+      </c>
+      <c r="M233" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>3</v>
+      </c>
+      <c r="B234" t="s">
+        <v>13</v>
+      </c>
+      <c r="C234" t="s">
+        <v>14</v>
+      </c>
+      <c r="D234" t="s">
         <v>2169</v>
       </c>
-      <c r="E233" t="s">
+      <c r="E234" t="s">
         <v>3284</v>
       </c>
-      <c r="F233" t="s">
+      <c r="F234" t="s">
         <v>2171</v>
       </c>
-      <c r="G233" t="s">
+      <c r="G234" t="s">
         <v>3285</v>
       </c>
-      <c r="H233" t="s">
+      <c r="H234" t="s">
         <v>3286</v>
       </c>
-      <c r="I233" t="s">
+      <c r="I234" t="s">
         <v>3287</v>
-      </c>
-      <c r="J233" s="1">
-        <v>1</v>
-      </c>
-      <c r="K233" s="1">
-        <v>0</v>
-      </c>
-      <c r="L233" t="s">
-        <v>21</v>
-      </c>
-      <c r="M233" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="1">
-        <v>3</v>
-      </c>
-      <c r="B234" t="s">
-        <v>13</v>
-      </c>
-      <c r="C234" t="s">
-        <v>14</v>
-      </c>
-      <c r="D234" t="s">
-        <v>138</v>
-      </c>
-      <c r="E234" t="s">
-        <v>3288</v>
-      </c>
-      <c r="F234" t="s">
-        <v>17</v>
-      </c>
-      <c r="G234" t="s">
-        <v>3289</v>
-      </c>
-      <c r="H234" t="s">
-        <v>3290</v>
-      </c>
-      <c r="I234" t="s">
-        <v>3291</v>
       </c>
       <c r="J234" s="1">
         <v>1</v>
@@ -24399,31 +24409,31 @@
         <v>14</v>
       </c>
       <c r="D235" t="s">
-        <v>461</v>
+        <v>138</v>
       </c>
       <c r="E235" t="s">
-        <v>3296</v>
+        <v>3288</v>
       </c>
       <c r="F235" t="s">
         <v>17</v>
       </c>
       <c r="G235" t="s">
-        <v>3297</v>
+        <v>3289</v>
       </c>
       <c r="H235" t="s">
-        <v>3298</v>
+        <v>3290</v>
       </c>
       <c r="I235" t="s">
-        <v>3299</v>
+        <v>3291</v>
       </c>
       <c r="J235" s="1">
         <v>1</v>
       </c>
       <c r="K235" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L235" t="s">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="M235" t="s">
         <v>22</v>
@@ -24440,31 +24450,31 @@
         <v>14</v>
       </c>
       <c r="D236" t="s">
-        <v>627</v>
+        <v>461</v>
       </c>
       <c r="E236" t="s">
-        <v>3300</v>
+        <v>3296</v>
       </c>
       <c r="F236" t="s">
         <v>17</v>
       </c>
       <c r="G236" t="s">
-        <v>3301</v>
+        <v>3297</v>
       </c>
       <c r="H236" t="s">
-        <v>3302</v>
+        <v>3298</v>
       </c>
       <c r="I236" t="s">
-        <v>3303</v>
+        <v>3299</v>
       </c>
       <c r="J236" s="1">
         <v>1</v>
       </c>
       <c r="K236" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L236" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="M236" t="s">
         <v>22</v>
@@ -24481,22 +24491,22 @@
         <v>14</v>
       </c>
       <c r="D237" t="s">
-        <v>580</v>
+        <v>627</v>
       </c>
       <c r="E237" t="s">
-        <v>3308</v>
+        <v>3300</v>
       </c>
       <c r="F237" t="s">
         <v>17</v>
       </c>
       <c r="G237" t="s">
-        <v>3309</v>
+        <v>3301</v>
       </c>
       <c r="H237" t="s">
-        <v>3310</v>
+        <v>3302</v>
       </c>
       <c r="I237" t="s">
-        <v>3311</v>
+        <v>3303</v>
       </c>
       <c r="J237" s="1">
         <v>1</v>
@@ -24522,22 +24532,22 @@
         <v>14</v>
       </c>
       <c r="D238" t="s">
-        <v>156</v>
+        <v>580</v>
       </c>
       <c r="E238" t="s">
-        <v>3312</v>
+        <v>3308</v>
       </c>
       <c r="F238" t="s">
         <v>17</v>
       </c>
       <c r="G238" t="s">
-        <v>3313</v>
+        <v>3309</v>
       </c>
       <c r="H238" t="s">
-        <v>3314</v>
+        <v>3310</v>
       </c>
       <c r="I238" t="s">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="J238" s="1">
         <v>1</v>
@@ -24566,19 +24576,19 @@
         <v>156</v>
       </c>
       <c r="E239" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="F239" t="s">
         <v>17</v>
       </c>
       <c r="G239" t="s">
-        <v>3317</v>
+        <v>3313</v>
       </c>
       <c r="H239" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="I239" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="J239" s="1">
         <v>1</v>
@@ -24604,22 +24614,22 @@
         <v>14</v>
       </c>
       <c r="D240" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="E240" t="s">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="F240" t="s">
         <v>17</v>
       </c>
       <c r="G240" t="s">
-        <v>3325</v>
+        <v>3317</v>
       </c>
       <c r="H240" t="s">
-        <v>3326</v>
+        <v>3318</v>
       </c>
       <c r="I240" t="s">
-        <v>3327</v>
+        <v>3319</v>
       </c>
       <c r="J240" s="1">
         <v>1</v>
@@ -24645,22 +24655,22 @@
         <v>14</v>
       </c>
       <c r="D241" t="s">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="E241" t="s">
-        <v>3328</v>
+        <v>3324</v>
       </c>
       <c r="F241" t="s">
         <v>17</v>
       </c>
       <c r="G241" t="s">
-        <v>3329</v>
+        <v>3325</v>
       </c>
       <c r="H241" t="s">
-        <v>3330</v>
+        <v>3326</v>
       </c>
       <c r="I241" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="J241" s="1">
         <v>1</v>
@@ -24689,19 +24699,19 @@
         <v>300</v>
       </c>
       <c r="E242" t="s">
-        <v>3332</v>
+        <v>3328</v>
       </c>
       <c r="F242" t="s">
         <v>17</v>
       </c>
       <c r="G242" t="s">
-        <v>3333</v>
+        <v>3329</v>
       </c>
       <c r="H242" t="s">
-        <v>3334</v>
+        <v>3330</v>
       </c>
       <c r="I242" t="s">
-        <v>3335</v>
+        <v>3331</v>
       </c>
       <c r="J242" s="1">
         <v>1</v>
@@ -24727,22 +24737,22 @@
         <v>14</v>
       </c>
       <c r="D243" t="s">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="E243" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="F243" t="s">
         <v>17</v>
       </c>
       <c r="G243" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="H243" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="I243" t="s">
-        <v>3339</v>
+        <v>3335</v>
       </c>
       <c r="J243" s="1">
         <v>1</v>
@@ -24768,22 +24778,22 @@
         <v>14</v>
       </c>
       <c r="D244" t="s">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="E244" t="s">
-        <v>3340</v>
+        <v>3336</v>
       </c>
       <c r="F244" t="s">
         <v>17</v>
       </c>
       <c r="G244" t="s">
-        <v>3341</v>
+        <v>3337</v>
       </c>
       <c r="H244" t="s">
-        <v>3342</v>
+        <v>3338</v>
       </c>
       <c r="I244" t="s">
-        <v>3343</v>
+        <v>3339</v>
       </c>
       <c r="J244" s="1">
         <v>1</v>
@@ -24809,22 +24819,22 @@
         <v>14</v>
       </c>
       <c r="D245" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="E245" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="F245" t="s">
         <v>17</v>
       </c>
       <c r="G245" t="s">
-        <v>3345</v>
+        <v>3341</v>
       </c>
       <c r="H245" t="s">
-        <v>3346</v>
+        <v>3342</v>
       </c>
       <c r="I245" t="s">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="J245" s="1">
         <v>1</v>
@@ -24850,22 +24860,22 @@
         <v>14</v>
       </c>
       <c r="D246" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E246" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="F246" t="s">
         <v>17</v>
       </c>
       <c r="G246" t="s">
-        <v>3349</v>
+        <v>3345</v>
       </c>
       <c r="H246" t="s">
-        <v>3350</v>
+        <v>3346</v>
       </c>
       <c r="I246" t="s">
-        <v>3351</v>
+        <v>3347</v>
       </c>
       <c r="J246" s="1">
         <v>1</v>
@@ -24891,22 +24901,22 @@
         <v>14</v>
       </c>
       <c r="D247" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="E247" t="s">
-        <v>3356</v>
+        <v>3348</v>
       </c>
       <c r="F247" t="s">
         <v>17</v>
       </c>
       <c r="G247" t="s">
-        <v>3357</v>
+        <v>3349</v>
       </c>
       <c r="H247" t="s">
-        <v>3358</v>
+        <v>3350</v>
       </c>
       <c r="I247" t="s">
-        <v>3359</v>
+        <v>3351</v>
       </c>
       <c r="J247" s="1">
         <v>1</v>
@@ -24932,22 +24942,22 @@
         <v>14</v>
       </c>
       <c r="D248" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="E248" t="s">
-        <v>3360</v>
+        <v>3356</v>
       </c>
       <c r="F248" t="s">
         <v>17</v>
       </c>
       <c r="G248" t="s">
-        <v>3361</v>
+        <v>3357</v>
       </c>
       <c r="H248" t="s">
-        <v>3362</v>
+        <v>3358</v>
       </c>
       <c r="I248" t="s">
-        <v>3363</v>
+        <v>3359</v>
       </c>
       <c r="J248" s="1">
         <v>1</v>
@@ -24976,19 +24986,19 @@
         <v>88</v>
       </c>
       <c r="E249" t="s">
-        <v>3364</v>
+        <v>3360</v>
       </c>
       <c r="F249" t="s">
         <v>17</v>
       </c>
       <c r="G249" t="s">
-        <v>3365</v>
+        <v>3361</v>
       </c>
       <c r="H249" t="s">
-        <v>3366</v>
+        <v>3362</v>
       </c>
       <c r="I249" t="s">
-        <v>3367</v>
+        <v>3363</v>
       </c>
       <c r="J249" s="1">
         <v>1</v>
@@ -25017,19 +25027,19 @@
         <v>88</v>
       </c>
       <c r="E250" t="s">
-        <v>3368</v>
+        <v>3364</v>
       </c>
       <c r="F250" t="s">
         <v>17</v>
       </c>
       <c r="G250" t="s">
-        <v>3369</v>
+        <v>3365</v>
       </c>
       <c r="H250" t="s">
-        <v>3370</v>
+        <v>3366</v>
       </c>
       <c r="I250" t="s">
-        <v>3371</v>
+        <v>3367</v>
       </c>
       <c r="J250" s="1">
         <v>1</v>
@@ -25058,19 +25068,19 @@
         <v>88</v>
       </c>
       <c r="E251" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
       <c r="F251" t="s">
         <v>17</v>
       </c>
       <c r="G251" t="s">
-        <v>3373</v>
+        <v>3369</v>
       </c>
       <c r="H251" t="s">
-        <v>3374</v>
+        <v>3370</v>
       </c>
       <c r="I251" t="s">
-        <v>3375</v>
+        <v>3371</v>
       </c>
       <c r="J251" s="1">
         <v>1</v>
@@ -25096,22 +25106,22 @@
         <v>14</v>
       </c>
       <c r="D252" t="s">
-        <v>622</v>
+        <v>88</v>
       </c>
       <c r="E252" t="s">
-        <v>3376</v>
+        <v>3372</v>
       </c>
       <c r="F252" t="s">
         <v>17</v>
       </c>
       <c r="G252" t="s">
-        <v>3377</v>
+        <v>3373</v>
       </c>
       <c r="H252" t="s">
-        <v>3378</v>
+        <v>3374</v>
       </c>
       <c r="I252" t="s">
-        <v>3379</v>
+        <v>3375</v>
       </c>
       <c r="J252" s="1">
         <v>1</v>
@@ -25137,22 +25147,22 @@
         <v>14</v>
       </c>
       <c r="D253" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="E253" t="s">
-        <v>3380</v>
+        <v>3376</v>
       </c>
       <c r="F253" t="s">
         <v>17</v>
       </c>
       <c r="G253" t="s">
-        <v>3381</v>
+        <v>3377</v>
       </c>
       <c r="H253" t="s">
-        <v>3382</v>
+        <v>3378</v>
       </c>
       <c r="I253" t="s">
-        <v>3383</v>
+        <v>3379</v>
       </c>
       <c r="J253" s="1">
         <v>1</v>
@@ -25178,22 +25188,22 @@
         <v>14</v>
       </c>
       <c r="D254" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="E254" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F254" t="s">
         <v>17</v>
       </c>
       <c r="G254" t="s">
-        <v>3385</v>
+        <v>3381</v>
       </c>
       <c r="H254" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="I254" t="s">
-        <v>3387</v>
+        <v>3383</v>
       </c>
       <c r="J254" s="1">
         <v>1</v>
@@ -25219,22 +25229,22 @@
         <v>14</v>
       </c>
       <c r="D255" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="E255" t="s">
-        <v>3388</v>
+        <v>3384</v>
       </c>
       <c r="F255" t="s">
         <v>17</v>
       </c>
       <c r="G255" t="s">
-        <v>3389</v>
+        <v>3385</v>
       </c>
       <c r="H255" t="s">
-        <v>3390</v>
+        <v>3386</v>
       </c>
       <c r="I255" t="s">
-        <v>3391</v>
+        <v>3387</v>
       </c>
       <c r="J255" s="1">
         <v>1</v>
@@ -25260,22 +25270,22 @@
         <v>14</v>
       </c>
       <c r="D256" t="s">
-        <v>83</v>
+        <v>605</v>
       </c>
       <c r="E256" t="s">
-        <v>3392</v>
+        <v>3388</v>
       </c>
       <c r="F256" t="s">
         <v>17</v>
       </c>
       <c r="G256" t="s">
-        <v>3393</v>
+        <v>3389</v>
       </c>
       <c r="H256" t="s">
-        <v>3394</v>
+        <v>3390</v>
       </c>
       <c r="I256" t="s">
-        <v>3395</v>
+        <v>3391</v>
       </c>
       <c r="J256" s="1">
         <v>1</v>
@@ -25304,19 +25314,19 @@
         <v>83</v>
       </c>
       <c r="E257" t="s">
-        <v>3396</v>
+        <v>3392</v>
       </c>
       <c r="F257" t="s">
         <v>17</v>
       </c>
       <c r="G257" t="s">
-        <v>3397</v>
+        <v>3393</v>
       </c>
       <c r="H257" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="I257" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="J257" s="1">
         <v>1</v>
@@ -25342,22 +25352,22 @@
         <v>14</v>
       </c>
       <c r="D258" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="E258" t="s">
-        <v>3404</v>
+        <v>3396</v>
       </c>
       <c r="F258" t="s">
         <v>17</v>
       </c>
       <c r="G258" t="s">
-        <v>3405</v>
+        <v>3397</v>
       </c>
       <c r="H258" t="s">
-        <v>3406</v>
+        <v>3398</v>
       </c>
       <c r="I258" t="s">
-        <v>3407</v>
+        <v>3399</v>
       </c>
       <c r="J258" s="1">
         <v>1</v>
@@ -25383,22 +25393,22 @@
         <v>14</v>
       </c>
       <c r="D259" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E259" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
       <c r="F259" t="s">
         <v>17</v>
       </c>
       <c r="G259" t="s">
-        <v>3409</v>
+        <v>3405</v>
       </c>
       <c r="H259" t="s">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="I259" t="s">
-        <v>3411</v>
+        <v>3407</v>
       </c>
       <c r="J259" s="1">
         <v>1</v>
@@ -25424,22 +25434,22 @@
         <v>14</v>
       </c>
       <c r="D260" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="E260" t="s">
-        <v>3412</v>
+        <v>3408</v>
       </c>
       <c r="F260" t="s">
         <v>17</v>
       </c>
       <c r="G260" t="s">
-        <v>3413</v>
+        <v>3409</v>
       </c>
       <c r="H260" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="I260" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="J260" s="1">
         <v>1</v>
@@ -25465,76 +25475,120 @@
         <v>14</v>
       </c>
       <c r="D261" t="s">
+        <v>56</v>
+      </c>
+      <c r="E261" t="s">
+        <v>3412</v>
+      </c>
+      <c r="F261" t="s">
+        <v>17</v>
+      </c>
+      <c r="G261" t="s">
+        <v>3413</v>
+      </c>
+      <c r="H261" t="s">
+        <v>3414</v>
+      </c>
+      <c r="I261" t="s">
+        <v>3415</v>
+      </c>
+      <c r="J261" s="1">
+        <v>1</v>
+      </c>
+      <c r="K261" s="1">
+        <v>0</v>
+      </c>
+      <c r="L261" t="s">
+        <v>21</v>
+      </c>
+      <c r="M261" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>3</v>
+      </c>
+      <c r="B262" t="s">
+        <v>13</v>
+      </c>
+      <c r="C262" t="s">
+        <v>14</v>
+      </c>
+      <c r="D262" t="s">
         <v>622</v>
       </c>
-      <c r="E261" t="s">
+      <c r="E262" t="s">
         <v>3416</v>
       </c>
-      <c r="F261" t="s">
-        <v>17</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="F262" t="s">
+        <v>17</v>
+      </c>
+      <c r="G262" t="s">
         <v>3417</v>
       </c>
-      <c r="H261" t="s">
+      <c r="H262" t="s">
         <v>3418</v>
       </c>
-      <c r="I261" t="s">
+      <c r="I262" t="s">
         <v>3419</v>
       </c>
-      <c r="J261" s="1">
-        <v>1</v>
-      </c>
-      <c r="K261" s="1">
-        <v>0</v>
-      </c>
-      <c r="L261" t="s">
-        <v>21</v>
-      </c>
-      <c r="M261" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A262" s="1">
-        <v>3</v>
-      </c>
-      <c r="B262" t="s">
-        <v>13</v>
-      </c>
-      <c r="C262" t="s">
-        <v>14</v>
-      </c>
-      <c r="D262" t="s">
+      <c r="J262" s="1">
+        <v>1</v>
+      </c>
+      <c r="K262" s="1">
+        <v>0</v>
+      </c>
+      <c r="L262" t="s">
+        <v>21</v>
+      </c>
+      <c r="M262" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>3</v>
+      </c>
+      <c r="B263" t="s">
+        <v>13</v>
+      </c>
+      <c r="C263" t="s">
+        <v>14</v>
+      </c>
+      <c r="D263" t="s">
         <v>2169</v>
       </c>
-      <c r="E262" t="s">
+      <c r="E263" t="s">
         <v>3420</v>
       </c>
-      <c r="F262" t="s">
+      <c r="F263" t="s">
         <v>2171</v>
       </c>
-      <c r="G262" t="s">
+      <c r="G263" t="s">
         <v>3421</v>
       </c>
-      <c r="H262" t="s">
+      <c r="H263" t="s">
         <v>3422</v>
       </c>
-      <c r="I262" t="s">
+      <c r="I263" t="s">
         <v>3423</v>
       </c>
-      <c r="J262" s="1">
-        <v>1</v>
-      </c>
-      <c r="K262" s="1">
-        <v>0</v>
-      </c>
-      <c r="L262" t="s">
-        <v>21</v>
-      </c>
-      <c r="M262" t="s">
-        <v>22</v>
-      </c>
+      <c r="J263" s="1">
+        <v>1</v>
+      </c>
+      <c r="K263" s="1">
+        <v>0</v>
+      </c>
+      <c r="L263" t="s">
+        <v>21</v>
+      </c>
+      <c r="M263" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D273" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -25543,7 +25597,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28252536-A143-4059-BBCB-B80D7C04A816}">
-  <dimension ref="A1:M512"/>
+  <dimension ref="A1:M511"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -44380,6 +44434,47 @@
         <v>22</v>
       </c>
     </row>
+    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A460" s="1">
+        <v>11</v>
+      </c>
+      <c r="B460" t="s">
+        <v>46</v>
+      </c>
+      <c r="C460" t="s">
+        <v>14</v>
+      </c>
+      <c r="D460" t="s">
+        <v>47</v>
+      </c>
+      <c r="E460" t="s">
+        <v>457</v>
+      </c>
+      <c r="F460" t="s">
+        <v>17</v>
+      </c>
+      <c r="G460" t="s">
+        <v>458</v>
+      </c>
+      <c r="H460" t="s">
+        <v>459</v>
+      </c>
+      <c r="I460" t="s">
+        <v>460</v>
+      </c>
+      <c r="J460" s="1">
+        <v>1</v>
+      </c>
+      <c r="K460" s="1">
+        <v>0</v>
+      </c>
+      <c r="L460" t="s">
+        <v>21</v>
+      </c>
+      <c r="M460" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>11</v>
@@ -44394,19 +44489,19 @@
         <v>47</v>
       </c>
       <c r="E461" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="F461" t="s">
         <v>17</v>
       </c>
       <c r="G461" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="H461" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="I461" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="J461" s="1">
         <v>1</v>
@@ -44432,22 +44527,22 @@
         <v>14</v>
       </c>
       <c r="D462" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E462" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F462" t="s">
         <v>17</v>
       </c>
       <c r="G462" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="H462" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="I462" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="J462" s="1">
         <v>1</v>
@@ -44476,19 +44571,19 @@
         <v>174</v>
       </c>
       <c r="E463" t="s">
-        <v>487</v>
+        <v>585</v>
       </c>
       <c r="F463" t="s">
         <v>17</v>
       </c>
       <c r="G463" t="s">
-        <v>488</v>
+        <v>586</v>
       </c>
       <c r="H463" t="s">
-        <v>489</v>
+        <v>587</v>
       </c>
       <c r="I463" t="s">
-        <v>490</v>
+        <v>588</v>
       </c>
       <c r="J463" s="1">
         <v>1</v>
@@ -44517,19 +44612,19 @@
         <v>174</v>
       </c>
       <c r="E464" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F464" t="s">
         <v>17</v>
       </c>
       <c r="G464" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="H464" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="I464" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="J464" s="1">
         <v>1</v>
@@ -44558,19 +44653,19 @@
         <v>174</v>
       </c>
       <c r="E465" t="s">
-        <v>589</v>
+        <v>676</v>
       </c>
       <c r="F465" t="s">
         <v>17</v>
       </c>
       <c r="G465" t="s">
-        <v>590</v>
+        <v>677</v>
       </c>
       <c r="H465" t="s">
-        <v>591</v>
+        <v>678</v>
       </c>
       <c r="I465" t="s">
-        <v>592</v>
+        <v>679</v>
       </c>
       <c r="J465" s="1">
         <v>1</v>
@@ -44596,22 +44691,22 @@
         <v>14</v>
       </c>
       <c r="D466" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E466" t="s">
-        <v>676</v>
+        <v>728</v>
       </c>
       <c r="F466" t="s">
         <v>17</v>
       </c>
       <c r="G466" t="s">
-        <v>677</v>
+        <v>729</v>
       </c>
       <c r="H466" t="s">
-        <v>678</v>
+        <v>730</v>
       </c>
       <c r="I466" t="s">
-        <v>679</v>
+        <v>731</v>
       </c>
       <c r="J466" s="1">
         <v>1</v>
@@ -44640,19 +44735,19 @@
         <v>47</v>
       </c>
       <c r="E467" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="F467" t="s">
         <v>17</v>
       </c>
       <c r="G467" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H467" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="I467" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="J467" s="1">
         <v>1</v>
@@ -44681,19 +44776,19 @@
         <v>47</v>
       </c>
       <c r="E468" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="F468" t="s">
         <v>17</v>
       </c>
       <c r="G468" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="H468" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="I468" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="J468" s="1">
         <v>1</v>
@@ -44719,22 +44814,22 @@
         <v>14</v>
       </c>
       <c r="D469" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E469" t="s">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="F469" t="s">
         <v>17</v>
       </c>
       <c r="G469" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="H469" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="I469" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="J469" s="1">
         <v>1</v>
@@ -44760,22 +44855,22 @@
         <v>14</v>
       </c>
       <c r="D470" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E470" t="s">
-        <v>768</v>
+        <v>816</v>
       </c>
       <c r="F470" t="s">
         <v>17</v>
       </c>
       <c r="G470" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
       <c r="H470" t="s">
-        <v>770</v>
+        <v>818</v>
       </c>
       <c r="I470" t="s">
-        <v>771</v>
+        <v>819</v>
       </c>
       <c r="J470" s="1">
         <v>1</v>
@@ -44804,19 +44899,19 @@
         <v>47</v>
       </c>
       <c r="E471" t="s">
-        <v>816</v>
+        <v>895</v>
       </c>
       <c r="F471" t="s">
         <v>17</v>
       </c>
       <c r="G471" t="s">
-        <v>817</v>
+        <v>896</v>
       </c>
       <c r="H471" t="s">
-        <v>818</v>
+        <v>897</v>
       </c>
       <c r="I471" t="s">
-        <v>819</v>
+        <v>898</v>
       </c>
       <c r="J471" s="1">
         <v>1</v>
@@ -44842,22 +44937,22 @@
         <v>14</v>
       </c>
       <c r="D472" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E472" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="F472" t="s">
         <v>17</v>
       </c>
       <c r="G472" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="H472" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="I472" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="J472" s="1">
         <v>1</v>
@@ -44886,19 +44981,19 @@
         <v>174</v>
       </c>
       <c r="E473" t="s">
-        <v>899</v>
+        <v>1003</v>
       </c>
       <c r="F473" t="s">
         <v>17</v>
       </c>
       <c r="G473" t="s">
-        <v>900</v>
+        <v>1004</v>
       </c>
       <c r="H473" t="s">
-        <v>901</v>
+        <v>1005</v>
       </c>
       <c r="I473" t="s">
-        <v>902</v>
+        <v>1006</v>
       </c>
       <c r="J473" s="1">
         <v>1</v>
@@ -44924,22 +45019,22 @@
         <v>14</v>
       </c>
       <c r="D474" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E474" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="F474" t="s">
         <v>17</v>
       </c>
       <c r="G474" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="H474" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="I474" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="J474" s="1">
         <v>1</v>
@@ -44968,19 +45063,19 @@
         <v>47</v>
       </c>
       <c r="E475" t="s">
-        <v>1007</v>
+        <v>1208</v>
       </c>
       <c r="F475" t="s">
         <v>17</v>
       </c>
       <c r="G475" t="s">
-        <v>1008</v>
+        <v>1209</v>
       </c>
       <c r="H475" t="s">
-        <v>1009</v>
+        <v>1210</v>
       </c>
       <c r="I475" t="s">
-        <v>1010</v>
+        <v>1211</v>
       </c>
       <c r="J475" s="1">
         <v>1</v>
@@ -45006,22 +45101,22 @@
         <v>14</v>
       </c>
       <c r="D476" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E476" t="s">
-        <v>1208</v>
+        <v>1260</v>
       </c>
       <c r="F476" t="s">
         <v>17</v>
       </c>
       <c r="G476" t="s">
-        <v>1209</v>
+        <v>1261</v>
       </c>
       <c r="H476" t="s">
-        <v>1210</v>
+        <v>1262</v>
       </c>
       <c r="I476" t="s">
-        <v>1211</v>
+        <v>1263</v>
       </c>
       <c r="J476" s="1">
         <v>1</v>
@@ -45047,22 +45142,22 @@
         <v>14</v>
       </c>
       <c r="D477" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E477" t="s">
-        <v>1260</v>
+        <v>1292</v>
       </c>
       <c r="F477" t="s">
         <v>17</v>
       </c>
       <c r="G477" t="s">
-        <v>1261</v>
+        <v>1293</v>
       </c>
       <c r="H477" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="I477" t="s">
-        <v>1263</v>
+        <v>1295</v>
       </c>
       <c r="J477" s="1">
         <v>1</v>
@@ -45091,19 +45186,19 @@
         <v>47</v>
       </c>
       <c r="E478" t="s">
-        <v>1292</v>
+        <v>1356</v>
       </c>
       <c r="F478" t="s">
         <v>17</v>
       </c>
       <c r="G478" t="s">
-        <v>1293</v>
+        <v>1357</v>
       </c>
       <c r="H478" t="s">
-        <v>1294</v>
-      </c>
-      <c r="I478" t="s">
-        <v>1295</v>
+        <v>1358</v>
+      </c>
+      <c r="I478" s="4" t="s">
+        <v>1359</v>
       </c>
       <c r="J478" s="1">
         <v>1</v>
@@ -45129,22 +45224,22 @@
         <v>14</v>
       </c>
       <c r="D479" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E479" t="s">
-        <v>1356</v>
+        <v>1404</v>
       </c>
       <c r="F479" t="s">
         <v>17</v>
       </c>
       <c r="G479" t="s">
-        <v>1357</v>
+        <v>1405</v>
       </c>
       <c r="H479" t="s">
-        <v>1358</v>
-      </c>
-      <c r="I479" s="4" t="s">
-        <v>1359</v>
+        <v>1406</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1407</v>
       </c>
       <c r="J479" s="1">
         <v>1</v>
@@ -45173,19 +45268,19 @@
         <v>174</v>
       </c>
       <c r="E480" t="s">
-        <v>1404</v>
+        <v>1464</v>
       </c>
       <c r="F480" t="s">
         <v>17</v>
       </c>
       <c r="G480" t="s">
-        <v>1405</v>
+        <v>1465</v>
       </c>
       <c r="H480" t="s">
-        <v>1406</v>
+        <v>1466</v>
       </c>
       <c r="I480" t="s">
-        <v>1407</v>
+        <v>1467</v>
       </c>
       <c r="J480" s="1">
         <v>1</v>
@@ -45214,19 +45309,19 @@
         <v>174</v>
       </c>
       <c r="E481" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="F481" t="s">
         <v>17</v>
       </c>
       <c r="G481" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="H481" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="I481" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="J481" s="1">
         <v>1</v>
@@ -45255,19 +45350,19 @@
         <v>174</v>
       </c>
       <c r="E482" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="F482" t="s">
         <v>17</v>
       </c>
       <c r="G482" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="H482" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="I482" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="J482" s="1">
         <v>1</v>
@@ -45296,19 +45391,19 @@
         <v>174</v>
       </c>
       <c r="E483" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="F483" t="s">
         <v>17</v>
       </c>
       <c r="G483" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="H483" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="I483" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="J483" s="1">
         <v>1</v>
@@ -45334,22 +45429,22 @@
         <v>14</v>
       </c>
       <c r="D484" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E484" t="s">
-        <v>1476</v>
+        <v>1552</v>
       </c>
       <c r="F484" t="s">
         <v>17</v>
       </c>
       <c r="G484" t="s">
-        <v>1477</v>
+        <v>1553</v>
       </c>
       <c r="H484" t="s">
-        <v>1478</v>
+        <v>1554</v>
       </c>
       <c r="I484" t="s">
-        <v>1479</v>
+        <v>1555</v>
       </c>
       <c r="J484" s="1">
         <v>1</v>
@@ -45378,19 +45473,19 @@
         <v>47</v>
       </c>
       <c r="E485" t="s">
-        <v>1552</v>
+        <v>1648</v>
       </c>
       <c r="F485" t="s">
         <v>17</v>
       </c>
       <c r="G485" t="s">
-        <v>1553</v>
+        <v>1649</v>
       </c>
       <c r="H485" t="s">
-        <v>1554</v>
+        <v>1650</v>
       </c>
       <c r="I485" t="s">
-        <v>1555</v>
+        <v>1651</v>
       </c>
       <c r="J485" s="1">
         <v>1</v>
@@ -45419,19 +45514,19 @@
         <v>47</v>
       </c>
       <c r="E486" t="s">
-        <v>1648</v>
+        <v>1681</v>
       </c>
       <c r="F486" t="s">
         <v>17</v>
       </c>
       <c r="G486" t="s">
-        <v>1649</v>
+        <v>1682</v>
       </c>
       <c r="H486" t="s">
-        <v>1650</v>
+        <v>1683</v>
       </c>
       <c r="I486" t="s">
-        <v>1651</v>
+        <v>1684</v>
       </c>
       <c r="J486" s="1">
         <v>1</v>
@@ -45460,19 +45555,19 @@
         <v>47</v>
       </c>
       <c r="E487" t="s">
-        <v>1681</v>
+        <v>1721</v>
       </c>
       <c r="F487" t="s">
         <v>17</v>
       </c>
       <c r="G487" t="s">
-        <v>1682</v>
+        <v>1722</v>
       </c>
       <c r="H487" t="s">
-        <v>1683</v>
+        <v>1723</v>
       </c>
       <c r="I487" t="s">
-        <v>1684</v>
+        <v>1724</v>
       </c>
       <c r="J487" s="1">
         <v>1</v>
@@ -45501,19 +45596,19 @@
         <v>47</v>
       </c>
       <c r="E488" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="F488" t="s">
         <v>17</v>
       </c>
       <c r="G488" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="H488" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="I488" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="J488" s="1">
         <v>1</v>
@@ -45542,19 +45637,19 @@
         <v>47</v>
       </c>
       <c r="E489" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="F489" t="s">
         <v>17</v>
       </c>
       <c r="G489" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="H489" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="I489" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="J489" s="1">
         <v>1</v>
@@ -45583,19 +45678,19 @@
         <v>47</v>
       </c>
       <c r="E490" t="s">
-        <v>1729</v>
+        <v>1845</v>
       </c>
       <c r="F490" t="s">
         <v>17</v>
       </c>
       <c r="G490" t="s">
-        <v>1730</v>
+        <v>1846</v>
       </c>
       <c r="H490" t="s">
-        <v>1731</v>
+        <v>1847</v>
       </c>
       <c r="I490" t="s">
-        <v>1732</v>
+        <v>1848</v>
       </c>
       <c r="J490" s="1">
         <v>1</v>
@@ -45624,19 +45719,19 @@
         <v>47</v>
       </c>
       <c r="E491" t="s">
-        <v>1845</v>
+        <v>1877</v>
       </c>
       <c r="F491" t="s">
         <v>17</v>
       </c>
       <c r="G491" t="s">
-        <v>1846</v>
+        <v>1878</v>
       </c>
       <c r="H491" t="s">
-        <v>1847</v>
+        <v>1879</v>
       </c>
       <c r="I491" t="s">
-        <v>1848</v>
+        <v>1880</v>
       </c>
       <c r="J491" s="1">
         <v>1</v>
@@ -45665,19 +45760,19 @@
         <v>47</v>
       </c>
       <c r="E492" t="s">
-        <v>1877</v>
+        <v>1925</v>
       </c>
       <c r="F492" t="s">
         <v>17</v>
       </c>
       <c r="G492" t="s">
-        <v>1878</v>
+        <v>1926</v>
       </c>
       <c r="H492" t="s">
-        <v>1879</v>
+        <v>1927</v>
       </c>
       <c r="I492" t="s">
-        <v>1880</v>
+        <v>1928</v>
       </c>
       <c r="J492" s="1">
         <v>1</v>
@@ -45706,19 +45801,19 @@
         <v>47</v>
       </c>
       <c r="E493" t="s">
-        <v>1925</v>
+        <v>1981</v>
       </c>
       <c r="F493" t="s">
         <v>17</v>
       </c>
       <c r="G493" t="s">
-        <v>1926</v>
+        <v>1982</v>
       </c>
       <c r="H493" t="s">
-        <v>1927</v>
+        <v>1983</v>
       </c>
       <c r="I493" t="s">
-        <v>1928</v>
+        <v>1984</v>
       </c>
       <c r="J493" s="1">
         <v>1</v>
@@ -45747,19 +45842,19 @@
         <v>47</v>
       </c>
       <c r="E494" t="s">
-        <v>1981</v>
+        <v>2029</v>
       </c>
       <c r="F494" t="s">
         <v>17</v>
       </c>
       <c r="G494" t="s">
-        <v>1982</v>
+        <v>2030</v>
       </c>
       <c r="H494" t="s">
-        <v>1983</v>
+        <v>2031</v>
       </c>
       <c r="I494" t="s">
-        <v>1984</v>
+        <v>2032</v>
       </c>
       <c r="J494" s="1">
         <v>1</v>
@@ -45785,22 +45880,22 @@
         <v>14</v>
       </c>
       <c r="D495" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E495" t="s">
-        <v>2029</v>
+        <v>2049</v>
       </c>
       <c r="F495" t="s">
         <v>17</v>
       </c>
       <c r="G495" t="s">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="H495" t="s">
-        <v>2031</v>
+        <v>2051</v>
       </c>
       <c r="I495" t="s">
-        <v>2032</v>
+        <v>2052</v>
       </c>
       <c r="J495" s="1">
         <v>1</v>
@@ -45826,22 +45921,22 @@
         <v>14</v>
       </c>
       <c r="D496" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E496" t="s">
-        <v>2049</v>
+        <v>2093</v>
       </c>
       <c r="F496" t="s">
         <v>17</v>
       </c>
       <c r="G496" t="s">
-        <v>2050</v>
+        <v>2094</v>
       </c>
       <c r="H496" t="s">
-        <v>2051</v>
+        <v>2095</v>
       </c>
       <c r="I496" t="s">
-        <v>2052</v>
+        <v>2096</v>
       </c>
       <c r="J496" s="1">
         <v>1</v>
@@ -45870,19 +45965,19 @@
         <v>47</v>
       </c>
       <c r="E497" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="F497" t="s">
         <v>17</v>
       </c>
       <c r="G497" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="H497" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
       <c r="I497" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="J497" s="1">
         <v>1</v>
@@ -45908,22 +46003,22 @@
         <v>14</v>
       </c>
       <c r="D498" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E498" t="s">
-        <v>2097</v>
+        <v>2121</v>
       </c>
       <c r="F498" t="s">
         <v>17</v>
       </c>
       <c r="G498" t="s">
-        <v>2098</v>
+        <v>2122</v>
       </c>
       <c r="H498" t="s">
-        <v>2099</v>
+        <v>2123</v>
       </c>
       <c r="I498" t="s">
-        <v>2100</v>
+        <v>2124</v>
       </c>
       <c r="J498" s="1">
         <v>1</v>
@@ -45952,19 +46047,19 @@
         <v>174</v>
       </c>
       <c r="E499" t="s">
-        <v>2121</v>
+        <v>2320</v>
       </c>
       <c r="F499" t="s">
         <v>17</v>
       </c>
       <c r="G499" t="s">
-        <v>2122</v>
+        <v>2321</v>
       </c>
       <c r="H499" t="s">
-        <v>2123</v>
+        <v>2322</v>
       </c>
       <c r="I499" t="s">
-        <v>2124</v>
+        <v>2323</v>
       </c>
       <c r="J499" s="1">
         <v>1</v>
@@ -45993,19 +46088,19 @@
         <v>174</v>
       </c>
       <c r="E500" t="s">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="F500" t="s">
         <v>17</v>
       </c>
       <c r="G500" t="s">
-        <v>2321</v>
+        <v>2325</v>
       </c>
       <c r="H500" t="s">
-        <v>2322</v>
+        <v>2326</v>
       </c>
       <c r="I500" t="s">
-        <v>2323</v>
+        <v>2327</v>
       </c>
       <c r="J500" s="1">
         <v>1</v>
@@ -46034,19 +46129,19 @@
         <v>174</v>
       </c>
       <c r="E501" t="s">
-        <v>2324</v>
+        <v>2332</v>
       </c>
       <c r="F501" t="s">
         <v>17</v>
       </c>
       <c r="G501" t="s">
-        <v>2325</v>
+        <v>2333</v>
       </c>
       <c r="H501" t="s">
-        <v>2326</v>
+        <v>2334</v>
       </c>
       <c r="I501" t="s">
-        <v>2327</v>
+        <v>2335</v>
       </c>
       <c r="J501" s="1">
         <v>1</v>
@@ -46075,19 +46170,19 @@
         <v>174</v>
       </c>
       <c r="E502" t="s">
-        <v>2332</v>
+        <v>2336</v>
       </c>
       <c r="F502" t="s">
         <v>17</v>
       </c>
       <c r="G502" t="s">
-        <v>2333</v>
+        <v>2337</v>
       </c>
       <c r="H502" t="s">
-        <v>2334</v>
+        <v>2338</v>
       </c>
       <c r="I502" t="s">
-        <v>2335</v>
+        <v>2339</v>
       </c>
       <c r="J502" s="1">
         <v>1</v>
@@ -46113,22 +46208,22 @@
         <v>14</v>
       </c>
       <c r="D503" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E503" t="s">
-        <v>2336</v>
+        <v>2344</v>
       </c>
       <c r="F503" t="s">
         <v>17</v>
       </c>
       <c r="G503" t="s">
-        <v>2337</v>
+        <v>2345</v>
       </c>
       <c r="H503" t="s">
-        <v>2338</v>
+        <v>2346</v>
       </c>
       <c r="I503" t="s">
-        <v>2339</v>
+        <v>2347</v>
       </c>
       <c r="J503" s="1">
         <v>1</v>
@@ -46157,19 +46252,19 @@
         <v>47</v>
       </c>
       <c r="E504" t="s">
-        <v>2344</v>
+        <v>2376</v>
       </c>
       <c r="F504" t="s">
         <v>17</v>
       </c>
       <c r="G504" t="s">
-        <v>2345</v>
+        <v>2377</v>
       </c>
       <c r="H504" t="s">
-        <v>2346</v>
+        <v>2378</v>
       </c>
       <c r="I504" t="s">
-        <v>2347</v>
+        <v>2379</v>
       </c>
       <c r="J504" s="1">
         <v>1</v>
@@ -46198,19 +46293,19 @@
         <v>47</v>
       </c>
       <c r="E505" t="s">
-        <v>2376</v>
+        <v>2424</v>
       </c>
       <c r="F505" t="s">
         <v>17</v>
       </c>
       <c r="G505" t="s">
-        <v>2377</v>
+        <v>2425</v>
       </c>
       <c r="H505" t="s">
-        <v>2378</v>
+        <v>2426</v>
       </c>
       <c r="I505" t="s">
-        <v>2379</v>
+        <v>2427</v>
       </c>
       <c r="J505" s="1">
         <v>1</v>
@@ -46239,19 +46334,19 @@
         <v>47</v>
       </c>
       <c r="E506" t="s">
-        <v>2424</v>
+        <v>2488</v>
       </c>
       <c r="F506" t="s">
         <v>17</v>
       </c>
       <c r="G506" t="s">
-        <v>2425</v>
+        <v>2489</v>
       </c>
       <c r="H506" t="s">
-        <v>2426</v>
+        <v>2490</v>
       </c>
       <c r="I506" t="s">
-        <v>2427</v>
+        <v>2491</v>
       </c>
       <c r="J506" s="1">
         <v>1</v>
@@ -46277,22 +46372,22 @@
         <v>14</v>
       </c>
       <c r="D507" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E507" t="s">
-        <v>2488</v>
+        <v>2568</v>
       </c>
       <c r="F507" t="s">
         <v>17</v>
       </c>
       <c r="G507" t="s">
-        <v>2489</v>
+        <v>2569</v>
       </c>
       <c r="H507" t="s">
-        <v>2490</v>
+        <v>2570</v>
       </c>
       <c r="I507" t="s">
-        <v>2491</v>
+        <v>2571</v>
       </c>
       <c r="J507" s="1">
         <v>1</v>
@@ -46321,19 +46416,19 @@
         <v>174</v>
       </c>
       <c r="E508" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="F508" t="s">
         <v>17</v>
       </c>
       <c r="G508" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="H508" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="I508" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="J508" s="1">
         <v>1</v>
@@ -46359,22 +46454,22 @@
         <v>14</v>
       </c>
       <c r="D509" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E509" t="s">
-        <v>2572</v>
+        <v>2616</v>
       </c>
       <c r="F509" t="s">
         <v>17</v>
       </c>
       <c r="G509" t="s">
-        <v>2573</v>
+        <v>2617</v>
       </c>
       <c r="H509" t="s">
-        <v>2574</v>
+        <v>2618</v>
       </c>
       <c r="I509" t="s">
-        <v>2575</v>
+        <v>2619</v>
       </c>
       <c r="J509" s="1">
         <v>1</v>
@@ -46403,19 +46498,19 @@
         <v>47</v>
       </c>
       <c r="E510" t="s">
-        <v>2616</v>
+        <v>2672</v>
       </c>
       <c r="F510" t="s">
         <v>17</v>
       </c>
       <c r="G510" t="s">
-        <v>2617</v>
+        <v>2673</v>
       </c>
       <c r="H510" t="s">
-        <v>2618</v>
+        <v>2674</v>
       </c>
       <c r="I510" t="s">
-        <v>2619</v>
+        <v>2675</v>
       </c>
       <c r="J510" s="1">
         <v>1</v>
@@ -46441,22 +46536,22 @@
         <v>14</v>
       </c>
       <c r="D511" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E511" t="s">
-        <v>2672</v>
+        <v>2716</v>
       </c>
       <c r="F511" t="s">
         <v>17</v>
       </c>
       <c r="G511" t="s">
-        <v>2673</v>
+        <v>2717</v>
       </c>
       <c r="H511" t="s">
-        <v>2674</v>
+        <v>2718</v>
       </c>
       <c r="I511" t="s">
-        <v>2675</v>
+        <v>2719</v>
       </c>
       <c r="J511" s="1">
         <v>1</v>
@@ -46468,47 +46563,6 @@
         <v>21</v>
       </c>
       <c r="M511" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A512" s="1">
-        <v>11</v>
-      </c>
-      <c r="B512" t="s">
-        <v>46</v>
-      </c>
-      <c r="C512" t="s">
-        <v>14</v>
-      </c>
-      <c r="D512" t="s">
-        <v>174</v>
-      </c>
-      <c r="E512" t="s">
-        <v>2716</v>
-      </c>
-      <c r="F512" t="s">
-        <v>17</v>
-      </c>
-      <c r="G512" t="s">
-        <v>2717</v>
-      </c>
-      <c r="H512" t="s">
-        <v>2718</v>
-      </c>
-      <c r="I512" t="s">
-        <v>2719</v>
-      </c>
-      <c r="J512" s="1">
-        <v>1</v>
-      </c>
-      <c r="K512" s="1">
-        <v>0</v>
-      </c>
-      <c r="L512" t="s">
-        <v>21</v>
-      </c>
-      <c r="M512" t="s">
         <v>22</v>
       </c>
     </row>
@@ -46519,48 +46573,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36902C53-BC33-4603-BFD3-82F285A025AB}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>306</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>307</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J1" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -46574,22 +46643,22 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>829</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>830</v>
+        <v>306</v>
       </c>
       <c r="H2" t="s">
-        <v>831</v>
+        <v>307</v>
       </c>
       <c r="I2" t="s">
-        <v>832</v>
+        <v>308</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
@@ -46598,7 +46667,7 @@
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>833</v>
+        <v>115</v>
       </c>
       <c r="M2" t="s">
         <v>22</v>
@@ -46615,22 +46684,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>828</v>
       </c>
       <c r="E3" t="s">
-        <v>3208</v>
+        <v>829</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>3209</v>
+        <v>830</v>
       </c>
       <c r="H3" t="s">
-        <v>3210</v>
+        <v>831</v>
       </c>
       <c r="I3" t="s">
-        <v>3211</v>
+        <v>832</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
@@ -46639,7 +46708,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>115</v>
+        <v>833</v>
       </c>
       <c r="M3" t="s">
         <v>22</v>
@@ -46656,22 +46725,22 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>3400</v>
+        <v>3208</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>3401</v>
+        <v>3209</v>
       </c>
       <c r="H4" t="s">
-        <v>3402</v>
+        <v>3210</v>
       </c>
       <c r="I4" t="s">
-        <v>3403</v>
+        <v>3211</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
@@ -46680,7 +46749,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>833</v>
+        <v>115</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
@@ -46697,22 +46766,22 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>3505</v>
+        <v>828</v>
       </c>
       <c r="E5" t="s">
-        <v>3506</v>
+        <v>3400</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>3507</v>
+        <v>3401</v>
       </c>
       <c r="H5" t="s">
-        <v>3508</v>
+        <v>3402</v>
       </c>
       <c r="I5" t="s">
-        <v>3509</v>
+        <v>3403</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -46721,11 +46790,55 @@
         <v>2</v>
       </c>
       <c r="L5" t="s">
+        <v>833</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3505</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3506</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3507</v>
+      </c>
+      <c r="H6" t="s">
+        <v>3508</v>
+      </c>
+      <c r="I6" t="s">
+        <v>3509</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
         <v>3510</v>
       </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Base_RAs/022__alunos_com_informacao_de_parceria_2026-07-27T16_00_39.4344432-04_00.xlsx
+++ b/Base_RAs/022__alunos_com_informacao_de_parceria_2026-07-27T16_00_39.4344432-04_00.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoel.campos\Desktop\AutomatizacaoERP\totvs_sge_bot\Base_RAs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senaimt-my.sharepoint.com/personal/manoel_campos_sfiemt_ind_br/Documents/Área de Trabalho/AutomatizacaoERP/Base_RAs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E70C2C-06D4-4CB1-9971-7F151EAE9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{98E70C2C-06D4-4CB1-9971-7F151EAE9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A937BA4B-5CC5-42FD-9BB1-906FFE983325}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2460" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultado da consulta" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,15 @@
     <sheet name="PORTO" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultado da consulta'!$A$1:$M$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'JA FEITO'!$A$1:$M$595</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultado da consulta'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8724" uniqueCount="3527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8744" uniqueCount="3527">
   <si>
     <t>CodFilialSGE</t>
   </si>
@@ -10663,13 +10664,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10688,7 +10693,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -11004,7 +11009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -11074,22 +11079,22 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>2856</v>
+        <v>3523</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>2857</v>
+        <v>3524</v>
       </c>
       <c r="H2" t="s">
-        <v>2858</v>
+        <v>3525</v>
       </c>
       <c r="I2" t="s">
-        <v>2859</v>
+        <v>3526</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
@@ -11115,22 +11120,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>2916</v>
+        <v>2572</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>2917</v>
+        <v>2573</v>
       </c>
       <c r="H3" t="s">
-        <v>2918</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>2919</v>
+        <v>2574</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2575</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
@@ -11147,37 +11152,37 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>1652</v>
       </c>
       <c r="E4" t="s">
-        <v>2992</v>
+        <v>1653</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>2993</v>
+        <v>1654</v>
       </c>
       <c r="H4" t="s">
-        <v>2994</v>
+        <v>1655</v>
       </c>
       <c r="I4" t="s">
-        <v>2995</v>
+        <v>1656</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="s">
         <v>21</v>
@@ -11186,3406 +11191,44 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3048</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>3049</v>
-      </c>
-      <c r="H5" t="s">
-        <v>3050</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3051</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3060</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>3061</v>
-      </c>
-      <c r="H6" t="s">
-        <v>3062</v>
-      </c>
-      <c r="I6" t="s">
-        <v>3063</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3108</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>3109</v>
-      </c>
-      <c r="H7" t="s">
-        <v>3110</v>
-      </c>
-      <c r="I7" t="s">
-        <v>3111</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3200</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3201</v>
-      </c>
-      <c r="H8" t="s">
-        <v>3202</v>
-      </c>
-      <c r="I8" t="s">
-        <v>3203</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3204</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>3205</v>
-      </c>
-      <c r="H9" t="s">
-        <v>3206</v>
-      </c>
-      <c r="I9" t="s">
-        <v>3207</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3216</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>3217</v>
-      </c>
-      <c r="H10" t="s">
-        <v>3218</v>
-      </c>
-      <c r="I10" t="s">
-        <v>3219</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>3523</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>3524</v>
-      </c>
-      <c r="H11" t="s">
-        <v>3525</v>
-      </c>
-      <c r="I11" t="s">
-        <v>3526</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="5" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>14</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1654</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1655</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1656</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J5" s="8">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
         <v>2</v>
       </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" t="s">
-        <v>276</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" t="s">
-        <v>277</v>
-      </c>
-      <c r="H13" t="s">
-        <v>278</v>
-      </c>
-      <c r="I13" t="s">
-        <v>279</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" t="s">
-        <v>281</v>
-      </c>
-      <c r="H14" t="s">
-        <v>282</v>
-      </c>
-      <c r="I14" t="s">
-        <v>283</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" t="s">
-        <v>315</v>
-      </c>
-      <c r="H15" t="s">
-        <v>316</v>
-      </c>
-      <c r="I15" t="s">
-        <v>317</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>370</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" t="s">
-        <v>371</v>
-      </c>
-      <c r="H16" t="s">
-        <v>372</v>
-      </c>
-      <c r="I16" t="s">
-        <v>373</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" t="s">
-        <v>374</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" t="s">
-        <v>375</v>
-      </c>
-      <c r="H17" t="s">
-        <v>376</v>
-      </c>
-      <c r="I17" t="s">
-        <v>377</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s">
-        <v>382</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="s">
-        <v>383</v>
-      </c>
-      <c r="H18" t="s">
-        <v>384</v>
-      </c>
-      <c r="I18" t="s">
-        <v>385</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" t="s">
-        <v>483</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" t="s">
-        <v>484</v>
-      </c>
-      <c r="H19" t="s">
-        <v>485</v>
-      </c>
-      <c r="I19" t="s">
-        <v>486</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" t="s">
-        <v>540</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" t="s">
-        <v>541</v>
-      </c>
-      <c r="H20" t="s">
-        <v>542</v>
-      </c>
-      <c r="I20" t="s">
-        <v>543</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>544</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>545</v>
-      </c>
-      <c r="H21" t="s">
-        <v>546</v>
-      </c>
-      <c r="I21" t="s">
-        <v>547</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>644</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>645</v>
-      </c>
-      <c r="H22" t="s">
-        <v>646</v>
-      </c>
-      <c r="I22" t="s">
-        <v>647</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" t="s">
-        <v>652</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>653</v>
-      </c>
-      <c r="H23" t="s">
-        <v>654</v>
-      </c>
-      <c r="I23" t="s">
-        <v>655</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" t="s">
-        <v>656</v>
-      </c>
-      <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" t="s">
-        <v>657</v>
-      </c>
-      <c r="H24" t="s">
-        <v>658</v>
-      </c>
-      <c r="I24" t="s">
-        <v>659</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" t="s">
-        <v>800</v>
-      </c>
-      <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" t="s">
-        <v>801</v>
-      </c>
-      <c r="H25" t="s">
-        <v>802</v>
-      </c>
-      <c r="I25" t="s">
-        <v>803</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" t="s">
-        <v>804</v>
-      </c>
-      <c r="F26" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" t="s">
-        <v>805</v>
-      </c>
-      <c r="H26" t="s">
-        <v>806</v>
-      </c>
-      <c r="I26" t="s">
-        <v>807</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" t="s">
-        <v>891</v>
-      </c>
-      <c r="F27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" t="s">
-        <v>892</v>
-      </c>
-      <c r="H27" t="s">
-        <v>893</v>
-      </c>
-      <c r="I27" t="s">
-        <v>894</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" t="s">
-        <v>975</v>
-      </c>
-      <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" t="s">
-        <v>976</v>
-      </c>
-      <c r="H28" t="s">
-        <v>977</v>
-      </c>
-      <c r="I28" t="s">
-        <v>978</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1048</v>
-      </c>
-      <c r="H29" t="s">
-        <v>1049</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1050</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F30" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1060</v>
-      </c>
-      <c r="H30" t="s">
-        <v>1061</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1062</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1120</v>
-      </c>
-      <c r="F31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H31" t="s">
-        <v>1122</v>
-      </c>
-      <c r="I31" t="s">
-        <v>1123</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>129</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1152</v>
-      </c>
-      <c r="F32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1153</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1154</v>
-      </c>
-      <c r="I32" t="s">
-        <v>1155</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
-      <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1236</v>
-      </c>
-      <c r="F33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1237</v>
-      </c>
-      <c r="H33" t="s">
-        <v>1238</v>
-      </c>
-      <c r="I33" t="s">
-        <v>1239</v>
-      </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H34" t="s">
-        <v>1242</v>
-      </c>
-      <c r="I34" t="s">
-        <v>1243</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1264</v>
-      </c>
-      <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1265</v>
-      </c>
-      <c r="H35" t="s">
-        <v>1266</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1267</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1268</v>
-      </c>
-      <c r="F36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1269</v>
-      </c>
-      <c r="H36" t="s">
-        <v>1270</v>
-      </c>
-      <c r="I36" t="s">
-        <v>1271</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
-      </c>
-      <c r="L36" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1312</v>
-      </c>
-      <c r="F37" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1313</v>
-      </c>
-      <c r="H37" t="s">
-        <v>1314</v>
-      </c>
-      <c r="I37" t="s">
-        <v>1315</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
-      <c r="L37" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F38" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1317</v>
-      </c>
-      <c r="H38" t="s">
-        <v>1318</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1320</v>
-      </c>
-      <c r="F39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H39" t="s">
-        <v>1322</v>
-      </c>
-      <c r="I39" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1408</v>
-      </c>
-      <c r="F40" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1409</v>
-      </c>
-      <c r="H40" t="s">
-        <v>1410</v>
-      </c>
-      <c r="I40" t="s">
-        <v>1411</v>
-      </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
-      </c>
-      <c r="L40" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1509</v>
-      </c>
-      <c r="H41" t="s">
-        <v>1510</v>
-      </c>
-      <c r="I41" t="s">
-        <v>1511</v>
-      </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" t="s">
-        <v>21</v>
-      </c>
-      <c r="M41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F42" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" t="s">
-        <v>1541</v>
-      </c>
-      <c r="H42" t="s">
-        <v>1542</v>
-      </c>
-      <c r="I42" t="s">
-        <v>1543</v>
-      </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1544</v>
-      </c>
-      <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1545</v>
-      </c>
-      <c r="H43" t="s">
-        <v>1546</v>
-      </c>
-      <c r="I43" t="s">
-        <v>1547</v>
-      </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1">
-        <v>0</v>
-      </c>
-      <c r="L43" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1548</v>
-      </c>
-      <c r="F44" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" t="s">
-        <v>1549</v>
-      </c>
-      <c r="H44" t="s">
-        <v>1550</v>
-      </c>
-      <c r="I44" t="s">
-        <v>1551</v>
-      </c>
-      <c r="J44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" t="s">
-        <v>62</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F45" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" t="s">
-        <v>1577</v>
-      </c>
-      <c r="H45" t="s">
-        <v>1578</v>
-      </c>
-      <c r="I45" t="s">
-        <v>1579</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" t="s">
-        <v>1589</v>
-      </c>
-      <c r="H46" t="s">
-        <v>1590</v>
-      </c>
-      <c r="I46" t="s">
-        <v>1591</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>0</v>
-      </c>
-      <c r="L46" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F47" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" t="s">
-        <v>1605</v>
-      </c>
-      <c r="H47" t="s">
-        <v>1606</v>
-      </c>
-      <c r="I47" t="s">
-        <v>1607</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0</v>
-      </c>
-      <c r="L47" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1609</v>
-      </c>
-      <c r="H48" t="s">
-        <v>1610</v>
-      </c>
-      <c r="I48" t="s">
-        <v>1611</v>
-      </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>0</v>
-      </c>
-      <c r="L48" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" t="s">
-        <v>165</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1677</v>
-      </c>
-      <c r="F49" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" t="s">
-        <v>1678</v>
-      </c>
-      <c r="H49" t="s">
-        <v>1679</v>
-      </c>
-      <c r="I49" t="s">
-        <v>1680</v>
-      </c>
-      <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
-      <c r="L49" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1689</v>
-      </c>
-      <c r="F50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" t="s">
-        <v>1690</v>
-      </c>
-      <c r="H50" t="s">
-        <v>1691</v>
-      </c>
-      <c r="I50" t="s">
-        <v>1692</v>
-      </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1693</v>
-      </c>
-      <c r="F51" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" t="s">
-        <v>1694</v>
-      </c>
-      <c r="H51" t="s">
-        <v>1695</v>
-      </c>
-      <c r="I51" t="s">
-        <v>1696</v>
-      </c>
-      <c r="J51" s="1">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-      <c r="L51" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F52" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" t="s">
-        <v>1698</v>
-      </c>
-      <c r="H52" t="s">
-        <v>1699</v>
-      </c>
-      <c r="I52" t="s">
-        <v>1700</v>
-      </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
-      </c>
-      <c r="L52" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F53" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1798</v>
-      </c>
-      <c r="H53" t="s">
-        <v>1799</v>
-      </c>
-      <c r="I53" t="s">
-        <v>1800</v>
-      </c>
-      <c r="J53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>0</v>
-      </c>
-      <c r="L53" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" t="s">
-        <v>129</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F54" t="s">
-        <v>17</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1826</v>
-      </c>
-      <c r="H54" t="s">
-        <v>1827</v>
-      </c>
-      <c r="I54" t="s">
-        <v>1828</v>
-      </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>0</v>
-      </c>
-      <c r="L54" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F55" t="s">
-        <v>17</v>
-      </c>
-      <c r="G55" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H55" t="s">
-        <v>1831</v>
-      </c>
-      <c r="I55" t="s">
-        <v>1832</v>
-      </c>
-      <c r="J55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>0</v>
-      </c>
-      <c r="L55" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" t="s">
-        <v>165</v>
-      </c>
-      <c r="E56" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F56" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" t="s">
-        <v>1918</v>
-      </c>
-      <c r="H56" t="s">
-        <v>1919</v>
-      </c>
-      <c r="I56" t="s">
-        <v>1920</v>
-      </c>
-      <c r="J56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E57" t="s">
-        <v>1921</v>
-      </c>
-      <c r="F57" t="s">
-        <v>17</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1922</v>
-      </c>
-      <c r="H57" t="s">
-        <v>1923</v>
-      </c>
-      <c r="I57" t="s">
-        <v>1924</v>
-      </c>
-      <c r="J57" s="1">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
-      <c r="L57" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" t="s">
-        <v>129</v>
-      </c>
-      <c r="E58" t="s">
-        <v>2017</v>
-      </c>
-      <c r="F58" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" t="s">
-        <v>2018</v>
-      </c>
-      <c r="H58" t="s">
-        <v>2019</v>
-      </c>
-      <c r="I58" t="s">
-        <v>2020</v>
-      </c>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
-      <c r="L58" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E59" t="s">
-        <v>2021</v>
-      </c>
-      <c r="F59" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" t="s">
-        <v>2022</v>
-      </c>
-      <c r="H59" t="s">
-        <v>2023</v>
-      </c>
-      <c r="I59" t="s">
-        <v>2024</v>
-      </c>
-      <c r="J59" s="1">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>0</v>
-      </c>
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>14</v>
-      </c>
-      <c r="D60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E60" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F60" t="s">
-        <v>17</v>
-      </c>
-      <c r="G60" t="s">
-        <v>2026</v>
-      </c>
-      <c r="H60" t="s">
-        <v>2027</v>
-      </c>
-      <c r="I60" t="s">
-        <v>2028</v>
-      </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
-      <c r="L60" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>129</v>
-      </c>
-      <c r="E61" t="s">
-        <v>2069</v>
-      </c>
-      <c r="F61" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" t="s">
-        <v>2070</v>
-      </c>
-      <c r="H61" t="s">
-        <v>2071</v>
-      </c>
-      <c r="I61" t="s">
-        <v>2072</v>
-      </c>
-      <c r="J61" s="1">
-        <v>1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>61</v>
-      </c>
-      <c r="C62" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" t="s">
-        <v>165</v>
-      </c>
-      <c r="E62" t="s">
-        <v>2101</v>
-      </c>
-      <c r="F62" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" t="s">
-        <v>2102</v>
-      </c>
-      <c r="H62" t="s">
-        <v>2103</v>
-      </c>
-      <c r="I62" t="s">
-        <v>2104</v>
-      </c>
-      <c r="J62" s="1">
-        <v>1</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
-      <c r="L62" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" t="s">
-        <v>2161</v>
-      </c>
-      <c r="F63" t="s">
-        <v>17</v>
-      </c>
-      <c r="G63" t="s">
-        <v>2162</v>
-      </c>
-      <c r="H63" t="s">
-        <v>2163</v>
-      </c>
-      <c r="I63" t="s">
-        <v>2164</v>
-      </c>
-      <c r="J63" s="1">
-        <v>1</v>
-      </c>
-      <c r="K63" s="1">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
-        <v>21</v>
-      </c>
-      <c r="M63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" t="s">
-        <v>14</v>
-      </c>
-      <c r="D64" t="s">
-        <v>62</v>
-      </c>
-      <c r="E64" t="s">
-        <v>2200</v>
-      </c>
-      <c r="F64" t="s">
-        <v>17</v>
-      </c>
-      <c r="G64" t="s">
-        <v>2201</v>
-      </c>
-      <c r="H64" t="s">
-        <v>2202</v>
-      </c>
-      <c r="I64" t="s">
-        <v>2203</v>
-      </c>
-      <c r="J64" s="1">
-        <v>1</v>
-      </c>
-      <c r="K64" s="1">
-        <v>2</v>
-      </c>
-      <c r="L64" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65" t="s">
-        <v>14</v>
-      </c>
-      <c r="D65" t="s">
-        <v>62</v>
-      </c>
-      <c r="E65" t="s">
-        <v>2204</v>
-      </c>
-      <c r="F65" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" t="s">
-        <v>2205</v>
-      </c>
-      <c r="H65" t="s">
-        <v>2206</v>
-      </c>
-      <c r="I65" t="s">
-        <v>2207</v>
-      </c>
-      <c r="J65" s="1">
-        <v>1</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" t="s">
-        <v>21</v>
-      </c>
-      <c r="M65" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>62</v>
-      </c>
-      <c r="E66" t="s">
-        <v>2220</v>
-      </c>
-      <c r="F66" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" t="s">
-        <v>2221</v>
-      </c>
-      <c r="H66" t="s">
-        <v>2222</v>
-      </c>
-      <c r="I66" t="s">
-        <v>2223</v>
-      </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-      <c r="L66" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>61</v>
-      </c>
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>62</v>
-      </c>
-      <c r="E67" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F67" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" t="s">
-        <v>2225</v>
-      </c>
-      <c r="H67" t="s">
-        <v>2226</v>
-      </c>
-      <c r="I67" t="s">
-        <v>2227</v>
-      </c>
-      <c r="J67" s="1">
-        <v>1</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C68" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" t="s">
-        <v>62</v>
-      </c>
-      <c r="E68" t="s">
-        <v>2228</v>
-      </c>
-      <c r="F68" t="s">
-        <v>17</v>
-      </c>
-      <c r="G68" t="s">
-        <v>2229</v>
-      </c>
-      <c r="H68" t="s">
-        <v>2230</v>
-      </c>
-      <c r="I68" t="s">
-        <v>2231</v>
-      </c>
-      <c r="J68" s="1">
-        <v>1</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>61</v>
-      </c>
-      <c r="C69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s">
-        <v>165</v>
-      </c>
-      <c r="E69" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F69" t="s">
-        <v>17</v>
-      </c>
-      <c r="G69" t="s">
-        <v>2281</v>
-      </c>
-      <c r="H69" t="s">
-        <v>2282</v>
-      </c>
-      <c r="I69" t="s">
-        <v>2283</v>
-      </c>
-      <c r="J69" s="1">
-        <v>1</v>
-      </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
-      <c r="L69" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>61</v>
-      </c>
-      <c r="C70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" t="s">
-        <v>62</v>
-      </c>
-      <c r="E70" t="s">
-        <v>2372</v>
-      </c>
-      <c r="F70" t="s">
-        <v>17</v>
-      </c>
-      <c r="G70" t="s">
-        <v>2373</v>
-      </c>
-      <c r="H70" t="s">
-        <v>2374</v>
-      </c>
-      <c r="I70" t="s">
-        <v>2375</v>
-      </c>
-      <c r="J70" s="1">
-        <v>1</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>61</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71" t="s">
-        <v>2604</v>
-      </c>
-      <c r="F71" t="s">
-        <v>17</v>
-      </c>
-      <c r="G71" t="s">
-        <v>2605</v>
-      </c>
-      <c r="H71" t="s">
-        <v>2606</v>
-      </c>
-      <c r="I71" t="s">
-        <v>2607</v>
-      </c>
-      <c r="J71" s="1">
-        <v>1</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
-        <v>21</v>
-      </c>
-      <c r="M71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>61</v>
-      </c>
-      <c r="C72" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" t="s">
-        <v>2612</v>
-      </c>
-      <c r="F72" t="s">
-        <v>17</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2613</v>
-      </c>
-      <c r="H72" t="s">
-        <v>2614</v>
-      </c>
-      <c r="I72" t="s">
-        <v>2615</v>
-      </c>
-      <c r="J72" s="1">
-        <v>1</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0</v>
-      </c>
-      <c r="L72" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>61</v>
-      </c>
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>165</v>
-      </c>
-      <c r="E73" t="s">
-        <v>2664</v>
-      </c>
-      <c r="F73" t="s">
-        <v>17</v>
-      </c>
-      <c r="G73" t="s">
-        <v>2665</v>
-      </c>
-      <c r="H73" t="s">
-        <v>2666</v>
-      </c>
-      <c r="I73" t="s">
-        <v>2667</v>
-      </c>
-      <c r="J73" s="1">
-        <v>1</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0</v>
-      </c>
-      <c r="L73" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>61</v>
-      </c>
-      <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>129</v>
-      </c>
-      <c r="E74" t="s">
-        <v>2712</v>
-      </c>
-      <c r="F74" t="s">
-        <v>17</v>
-      </c>
-      <c r="G74" t="s">
-        <v>2713</v>
-      </c>
-      <c r="H74" t="s">
-        <v>2714</v>
-      </c>
-      <c r="I74" t="s">
-        <v>2715</v>
-      </c>
-      <c r="J74" s="1">
-        <v>1</v>
-      </c>
-      <c r="K74" s="1">
-        <v>0</v>
-      </c>
-      <c r="L74" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>61</v>
-      </c>
-      <c r="C75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" t="s">
-        <v>129</v>
-      </c>
-      <c r="E75" t="s">
-        <v>2776</v>
-      </c>
-      <c r="F75" t="s">
-        <v>17</v>
-      </c>
-      <c r="G75" t="s">
-        <v>2777</v>
-      </c>
-      <c r="H75" t="s">
-        <v>2778</v>
-      </c>
-      <c r="I75" t="s">
-        <v>2779</v>
-      </c>
-      <c r="J75" s="1">
-        <v>1</v>
-      </c>
-      <c r="K75" s="1">
-        <v>0</v>
-      </c>
-      <c r="L75" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>61</v>
-      </c>
-      <c r="C76" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" t="s">
-        <v>2828</v>
-      </c>
-      <c r="F76" t="s">
-        <v>17</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2829</v>
-      </c>
-      <c r="H76" t="s">
-        <v>2830</v>
-      </c>
-      <c r="I76" t="s">
-        <v>2831</v>
-      </c>
-      <c r="J76" s="1">
-        <v>1</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
-      </c>
-      <c r="L76" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>61</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>129</v>
-      </c>
-      <c r="E77" t="s">
-        <v>2880</v>
-      </c>
-      <c r="F77" t="s">
-        <v>17</v>
-      </c>
-      <c r="G77" t="s">
-        <v>2881</v>
-      </c>
-      <c r="H77" t="s">
-        <v>2882</v>
-      </c>
-      <c r="I77" t="s">
-        <v>2883</v>
-      </c>
-      <c r="J77" s="1">
-        <v>1</v>
-      </c>
-      <c r="K77" s="1">
-        <v>0</v>
-      </c>
-      <c r="L77" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>61</v>
-      </c>
-      <c r="C78" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" t="s">
-        <v>129</v>
-      </c>
-      <c r="E78" t="s">
-        <v>2892</v>
-      </c>
-      <c r="F78" t="s">
-        <v>17</v>
-      </c>
-      <c r="G78" t="s">
-        <v>2893</v>
-      </c>
-      <c r="H78" t="s">
-        <v>2894</v>
-      </c>
-      <c r="I78" t="s">
-        <v>2895</v>
-      </c>
-      <c r="J78" s="1">
-        <v>1</v>
-      </c>
-      <c r="K78" s="1">
-        <v>0</v>
-      </c>
-      <c r="L78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>61</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>62</v>
-      </c>
-      <c r="E79" t="s">
-        <v>3044</v>
-      </c>
-      <c r="F79" t="s">
-        <v>17</v>
-      </c>
-      <c r="G79" t="s">
-        <v>3045</v>
-      </c>
-      <c r="H79" t="s">
-        <v>3046</v>
-      </c>
-      <c r="I79" t="s">
-        <v>3047</v>
-      </c>
-      <c r="J79" s="1">
-        <v>1</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-      <c r="L79" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>61</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" t="s">
-        <v>62</v>
-      </c>
-      <c r="E80" t="s">
-        <v>3052</v>
-      </c>
-      <c r="F80" t="s">
-        <v>17</v>
-      </c>
-      <c r="G80" t="s">
-        <v>3053</v>
-      </c>
-      <c r="H80" t="s">
-        <v>3054</v>
-      </c>
-      <c r="I80" t="s">
-        <v>3055</v>
-      </c>
-      <c r="J80" s="1">
-        <v>1</v>
-      </c>
-      <c r="K80" s="1">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>61</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>165</v>
-      </c>
-      <c r="E81" t="s">
-        <v>3092</v>
-      </c>
-      <c r="F81" t="s">
-        <v>17</v>
-      </c>
-      <c r="G81" t="s">
-        <v>3093</v>
-      </c>
-      <c r="H81" t="s">
-        <v>3094</v>
-      </c>
-      <c r="I81" t="s">
-        <v>3095</v>
-      </c>
-      <c r="J81" s="1">
-        <v>1</v>
-      </c>
-      <c r="K81" s="1">
-        <v>0</v>
-      </c>
-      <c r="L81" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" t="s">
-        <v>14</v>
-      </c>
-      <c r="D82" t="s">
-        <v>129</v>
-      </c>
-      <c r="E82" t="s">
-        <v>3188</v>
-      </c>
-      <c r="F82" t="s">
-        <v>17</v>
-      </c>
-      <c r="G82" t="s">
-        <v>3189</v>
-      </c>
-      <c r="H82" t="s">
-        <v>3190</v>
-      </c>
-      <c r="I82" t="s">
-        <v>3191</v>
-      </c>
-      <c r="J82" s="1">
-        <v>1</v>
-      </c>
-      <c r="K82" s="1">
-        <v>0</v>
-      </c>
-      <c r="L82" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>61</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>129</v>
-      </c>
-      <c r="E83" t="s">
-        <v>3292</v>
-      </c>
-      <c r="F83" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" t="s">
-        <v>3293</v>
-      </c>
-      <c r="H83" t="s">
-        <v>3294</v>
-      </c>
-      <c r="I83" t="s">
-        <v>3295</v>
-      </c>
-      <c r="J83" s="1">
-        <v>1</v>
-      </c>
-      <c r="K83" s="1">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>61</v>
-      </c>
-      <c r="C84" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" t="s">
-        <v>129</v>
-      </c>
-      <c r="E84" t="s">
-        <v>3304</v>
-      </c>
-      <c r="F84" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" t="s">
-        <v>3305</v>
-      </c>
-      <c r="H84" t="s">
-        <v>3306</v>
-      </c>
-      <c r="I84" t="s">
-        <v>3307</v>
-      </c>
-      <c r="J84" s="1">
-        <v>1</v>
-      </c>
-      <c r="K84" s="1">
-        <v>0</v>
-      </c>
-      <c r="L84" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>61</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>129</v>
-      </c>
-      <c r="E85" t="s">
-        <v>3320</v>
-      </c>
-      <c r="F85" t="s">
-        <v>17</v>
-      </c>
-      <c r="G85" t="s">
-        <v>3321</v>
-      </c>
-      <c r="H85" t="s">
-        <v>3322</v>
-      </c>
-      <c r="I85" t="s">
-        <v>3323</v>
-      </c>
-      <c r="J85" s="1">
-        <v>1</v>
-      </c>
-      <c r="K85" s="1">
-        <v>0</v>
-      </c>
-      <c r="L85" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>61</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>165</v>
-      </c>
-      <c r="E86" t="s">
-        <v>3352</v>
-      </c>
-      <c r="F86" t="s">
-        <v>17</v>
-      </c>
-      <c r="G86" t="s">
-        <v>3353</v>
-      </c>
-      <c r="H86" t="s">
-        <v>3354</v>
-      </c>
-      <c r="I86" t="s">
-        <v>3355</v>
-      </c>
-      <c r="J86" s="1">
-        <v>1</v>
-      </c>
-      <c r="K86" s="1">
-        <v>0</v>
-      </c>
-      <c r="L86" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>61</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>62</v>
-      </c>
-      <c r="E87" t="s">
-        <v>3489</v>
-      </c>
-      <c r="F87" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" t="s">
-        <v>3490</v>
-      </c>
-      <c r="H87" t="s">
-        <v>3491</v>
-      </c>
-      <c r="I87" t="s">
-        <v>3492</v>
-      </c>
-      <c r="J87" s="1">
-        <v>1</v>
-      </c>
-      <c r="K87" s="1">
-        <v>2</v>
-      </c>
-      <c r="L87" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" t="s">
+      <c r="L5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -25597,7 +22240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28252536-A143-4059-BBCB-B80D7C04A816}">
-  <dimension ref="A1:M511"/>
+  <dimension ref="A1:M595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -46563,6 +43206,3450 @@
         <v>21</v>
       </c>
       <c r="M511" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
+        <v>11</v>
+      </c>
+      <c r="B512" t="s">
+        <v>46</v>
+      </c>
+      <c r="C512" t="s">
+        <v>14</v>
+      </c>
+      <c r="D512" t="s">
+        <v>174</v>
+      </c>
+      <c r="E512" t="s">
+        <v>2856</v>
+      </c>
+      <c r="F512" t="s">
+        <v>17</v>
+      </c>
+      <c r="G512" t="s">
+        <v>2857</v>
+      </c>
+      <c r="H512" t="s">
+        <v>2858</v>
+      </c>
+      <c r="I512" t="s">
+        <v>2859</v>
+      </c>
+      <c r="J512" s="1">
+        <v>1</v>
+      </c>
+      <c r="K512" s="1">
+        <v>0</v>
+      </c>
+      <c r="L512" t="s">
+        <v>21</v>
+      </c>
+      <c r="M512" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
+        <v>11</v>
+      </c>
+      <c r="B513" t="s">
+        <v>46</v>
+      </c>
+      <c r="C513" t="s">
+        <v>14</v>
+      </c>
+      <c r="D513" t="s">
+        <v>47</v>
+      </c>
+      <c r="E513" t="s">
+        <v>2916</v>
+      </c>
+      <c r="F513" t="s">
+        <v>17</v>
+      </c>
+      <c r="G513" t="s">
+        <v>2917</v>
+      </c>
+      <c r="H513" t="s">
+        <v>2918</v>
+      </c>
+      <c r="I513" s="5" t="s">
+        <v>2919</v>
+      </c>
+      <c r="J513" s="1">
+        <v>1</v>
+      </c>
+      <c r="K513" s="1">
+        <v>0</v>
+      </c>
+      <c r="L513" t="s">
+        <v>21</v>
+      </c>
+      <c r="M513" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
+        <v>11</v>
+      </c>
+      <c r="B514" t="s">
+        <v>46</v>
+      </c>
+      <c r="C514" t="s">
+        <v>14</v>
+      </c>
+      <c r="D514" t="s">
+        <v>174</v>
+      </c>
+      <c r="E514" t="s">
+        <v>2992</v>
+      </c>
+      <c r="F514" t="s">
+        <v>17</v>
+      </c>
+      <c r="G514" t="s">
+        <v>2993</v>
+      </c>
+      <c r="H514" t="s">
+        <v>2994</v>
+      </c>
+      <c r="I514" t="s">
+        <v>2995</v>
+      </c>
+      <c r="J514" s="1">
+        <v>1</v>
+      </c>
+      <c r="K514" s="1">
+        <v>0</v>
+      </c>
+      <c r="L514" t="s">
+        <v>21</v>
+      </c>
+      <c r="M514" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
+        <v>11</v>
+      </c>
+      <c r="B515" t="s">
+        <v>46</v>
+      </c>
+      <c r="C515" t="s">
+        <v>14</v>
+      </c>
+      <c r="D515" t="s">
+        <v>47</v>
+      </c>
+      <c r="E515" t="s">
+        <v>3048</v>
+      </c>
+      <c r="F515" t="s">
+        <v>17</v>
+      </c>
+      <c r="G515" t="s">
+        <v>3049</v>
+      </c>
+      <c r="H515" t="s">
+        <v>3050</v>
+      </c>
+      <c r="I515" t="s">
+        <v>3051</v>
+      </c>
+      <c r="J515" s="1">
+        <v>1</v>
+      </c>
+      <c r="K515" s="1">
+        <v>0</v>
+      </c>
+      <c r="L515" t="s">
+        <v>21</v>
+      </c>
+      <c r="M515" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
+        <v>11</v>
+      </c>
+      <c r="B516" t="s">
+        <v>46</v>
+      </c>
+      <c r="C516" t="s">
+        <v>14</v>
+      </c>
+      <c r="D516" t="s">
+        <v>47</v>
+      </c>
+      <c r="E516" t="s">
+        <v>3060</v>
+      </c>
+      <c r="F516" t="s">
+        <v>17</v>
+      </c>
+      <c r="G516" t="s">
+        <v>3061</v>
+      </c>
+      <c r="H516" t="s">
+        <v>3062</v>
+      </c>
+      <c r="I516" t="s">
+        <v>3063</v>
+      </c>
+      <c r="J516" s="1">
+        <v>1</v>
+      </c>
+      <c r="K516" s="1">
+        <v>0</v>
+      </c>
+      <c r="L516" t="s">
+        <v>21</v>
+      </c>
+      <c r="M516" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A517" s="1">
+        <v>11</v>
+      </c>
+      <c r="B517" t="s">
+        <v>46</v>
+      </c>
+      <c r="C517" t="s">
+        <v>14</v>
+      </c>
+      <c r="D517" t="s">
+        <v>47</v>
+      </c>
+      <c r="E517" t="s">
+        <v>3108</v>
+      </c>
+      <c r="F517" t="s">
+        <v>17</v>
+      </c>
+      <c r="G517" t="s">
+        <v>3109</v>
+      </c>
+      <c r="H517" t="s">
+        <v>3110</v>
+      </c>
+      <c r="I517" t="s">
+        <v>3111</v>
+      </c>
+      <c r="J517" s="1">
+        <v>1</v>
+      </c>
+      <c r="K517" s="1">
+        <v>0</v>
+      </c>
+      <c r="L517" t="s">
+        <v>21</v>
+      </c>
+      <c r="M517" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A518" s="1">
+        <v>11</v>
+      </c>
+      <c r="B518" t="s">
+        <v>46</v>
+      </c>
+      <c r="C518" t="s">
+        <v>14</v>
+      </c>
+      <c r="D518" t="s">
+        <v>174</v>
+      </c>
+      <c r="E518" t="s">
+        <v>3200</v>
+      </c>
+      <c r="F518" t="s">
+        <v>17</v>
+      </c>
+      <c r="G518" t="s">
+        <v>3201</v>
+      </c>
+      <c r="H518" t="s">
+        <v>3202</v>
+      </c>
+      <c r="I518" t="s">
+        <v>3203</v>
+      </c>
+      <c r="J518" s="1">
+        <v>1</v>
+      </c>
+      <c r="K518" s="1">
+        <v>0</v>
+      </c>
+      <c r="L518" t="s">
+        <v>21</v>
+      </c>
+      <c r="M518" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A519" s="1">
+        <v>11</v>
+      </c>
+      <c r="B519" t="s">
+        <v>46</v>
+      </c>
+      <c r="C519" t="s">
+        <v>14</v>
+      </c>
+      <c r="D519" t="s">
+        <v>174</v>
+      </c>
+      <c r="E519" t="s">
+        <v>3204</v>
+      </c>
+      <c r="F519" t="s">
+        <v>17</v>
+      </c>
+      <c r="G519" t="s">
+        <v>3205</v>
+      </c>
+      <c r="H519" t="s">
+        <v>3206</v>
+      </c>
+      <c r="I519" t="s">
+        <v>3207</v>
+      </c>
+      <c r="J519" s="1">
+        <v>1</v>
+      </c>
+      <c r="K519" s="1">
+        <v>0</v>
+      </c>
+      <c r="L519" t="s">
+        <v>21</v>
+      </c>
+      <c r="M519" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A520" s="1">
+        <v>11</v>
+      </c>
+      <c r="B520" t="s">
+        <v>46</v>
+      </c>
+      <c r="C520" t="s">
+        <v>14</v>
+      </c>
+      <c r="D520" t="s">
+        <v>47</v>
+      </c>
+      <c r="E520" t="s">
+        <v>3216</v>
+      </c>
+      <c r="F520" t="s">
+        <v>17</v>
+      </c>
+      <c r="G520" t="s">
+        <v>3217</v>
+      </c>
+      <c r="H520" t="s">
+        <v>3218</v>
+      </c>
+      <c r="I520" t="s">
+        <v>3219</v>
+      </c>
+      <c r="J520" s="1">
+        <v>1</v>
+      </c>
+      <c r="K520" s="1">
+        <v>0</v>
+      </c>
+      <c r="L520" t="s">
+        <v>21</v>
+      </c>
+      <c r="M520" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="521" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="6">
+        <v>15</v>
+      </c>
+      <c r="B521" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C521" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D521" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E521" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F521" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G521" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H521" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="I521" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="J521" s="6">
+        <v>1</v>
+      </c>
+      <c r="K521" s="6">
+        <v>1</v>
+      </c>
+      <c r="L521" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M521" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="522" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="6">
+        <v>15</v>
+      </c>
+      <c r="B522" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C522" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D522" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E522" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F522" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G522" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="H522" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="I522" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="J522" s="6">
+        <v>1</v>
+      </c>
+      <c r="K522" s="6">
+        <v>0</v>
+      </c>
+      <c r="L522" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M522" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="523" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="6">
+        <v>15</v>
+      </c>
+      <c r="B523" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C523" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D523" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E523" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F523" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G523" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="H523" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="I523" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="J523" s="6">
+        <v>1</v>
+      </c>
+      <c r="K523" s="6">
+        <v>0</v>
+      </c>
+      <c r="L523" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M523" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="6">
+        <v>15</v>
+      </c>
+      <c r="B524" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C524" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D524" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E524" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="F524" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G524" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="H524" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I524" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="J524" s="6">
+        <v>1</v>
+      </c>
+      <c r="K524" s="6">
+        <v>0</v>
+      </c>
+      <c r="L524" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M524" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="525" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="6">
+        <v>15</v>
+      </c>
+      <c r="B525" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C525" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D525" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E525" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F525" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G525" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H525" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I525" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J525" s="6">
+        <v>1</v>
+      </c>
+      <c r="K525" s="6">
+        <v>0</v>
+      </c>
+      <c r="L525" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M525" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="6">
+        <v>15</v>
+      </c>
+      <c r="B526" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C526" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D526" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E526" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F526" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G526" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="H526" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="I526" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="J526" s="6">
+        <v>1</v>
+      </c>
+      <c r="K526" s="6">
+        <v>0</v>
+      </c>
+      <c r="L526" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M526" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="6">
+        <v>15</v>
+      </c>
+      <c r="B527" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C527" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D527" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E527" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="F527" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G527" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="H527" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="I527" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="J527" s="6">
+        <v>1</v>
+      </c>
+      <c r="K527" s="6">
+        <v>0</v>
+      </c>
+      <c r="L527" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M527" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="6">
+        <v>15</v>
+      </c>
+      <c r="B528" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C528" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D528" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E528" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="F528" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G528" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="H528" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="I528" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="J528" s="6">
+        <v>1</v>
+      </c>
+      <c r="K528" s="6">
+        <v>0</v>
+      </c>
+      <c r="L528" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M528" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="6">
+        <v>15</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C529" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D529" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E529" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="F529" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G529" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="H529" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="I529" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="J529" s="6">
+        <v>1</v>
+      </c>
+      <c r="K529" s="6">
+        <v>0</v>
+      </c>
+      <c r="L529" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M529" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="6">
+        <v>15</v>
+      </c>
+      <c r="B530" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C530" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D530" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E530" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="F530" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G530" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="H530" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="I530" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="J530" s="6">
+        <v>1</v>
+      </c>
+      <c r="K530" s="6">
+        <v>0</v>
+      </c>
+      <c r="L530" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M530" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="6">
+        <v>15</v>
+      </c>
+      <c r="B531" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C531" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D531" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E531" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="F531" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G531" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="H531" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="I531" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="J531" s="6">
+        <v>1</v>
+      </c>
+      <c r="K531" s="6">
+        <v>0</v>
+      </c>
+      <c r="L531" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M531" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="6">
+        <v>15</v>
+      </c>
+      <c r="B532" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C532" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D532" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E532" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="F532" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G532" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="H532" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="I532" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="J532" s="6">
+        <v>1</v>
+      </c>
+      <c r="K532" s="6">
+        <v>0</v>
+      </c>
+      <c r="L532" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M532" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="6">
+        <v>15</v>
+      </c>
+      <c r="B533" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C533" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D533" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E533" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="F533" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G533" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="H533" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="I533" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="J533" s="6">
+        <v>1</v>
+      </c>
+      <c r="K533" s="6">
+        <v>0</v>
+      </c>
+      <c r="L533" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M533" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="6">
+        <v>15</v>
+      </c>
+      <c r="B534" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C534" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D534" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E534" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="F534" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G534" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="H534" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="I534" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="J534" s="6">
+        <v>1</v>
+      </c>
+      <c r="K534" s="6">
+        <v>0</v>
+      </c>
+      <c r="L534" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M534" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="6">
+        <v>15</v>
+      </c>
+      <c r="B535" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C535" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D535" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E535" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="F535" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G535" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="H535" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="I535" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="J535" s="6">
+        <v>1</v>
+      </c>
+      <c r="K535" s="6">
+        <v>0</v>
+      </c>
+      <c r="L535" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M535" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="6">
+        <v>15</v>
+      </c>
+      <c r="B536" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C536" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D536" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E536" s="7" t="s">
+        <v>975</v>
+      </c>
+      <c r="F536" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G536" s="7" t="s">
+        <v>976</v>
+      </c>
+      <c r="H536" s="7" t="s">
+        <v>977</v>
+      </c>
+      <c r="I536" s="7" t="s">
+        <v>978</v>
+      </c>
+      <c r="J536" s="6">
+        <v>1</v>
+      </c>
+      <c r="K536" s="6">
+        <v>0</v>
+      </c>
+      <c r="L536" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M536" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="537" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="6">
+        <v>15</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C537" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D537" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E537" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F537" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G537" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H537" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I537" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J537" s="6">
+        <v>1</v>
+      </c>
+      <c r="K537" s="6">
+        <v>0</v>
+      </c>
+      <c r="L537" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M537" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="6">
+        <v>15</v>
+      </c>
+      <c r="B538" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C538" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D538" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E538" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F538" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G538" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H538" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I538" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J538" s="6">
+        <v>1</v>
+      </c>
+      <c r="K538" s="6">
+        <v>0</v>
+      </c>
+      <c r="L538" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M538" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="6">
+        <v>15</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C539" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D539" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E539" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F539" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G539" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H539" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I539" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="J539" s="6">
+        <v>1</v>
+      </c>
+      <c r="K539" s="6">
+        <v>0</v>
+      </c>
+      <c r="L539" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M539" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="6">
+        <v>15</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C540" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D540" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E540" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F540" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G540" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H540" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I540" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="J540" s="6">
+        <v>1</v>
+      </c>
+      <c r="K540" s="6">
+        <v>0</v>
+      </c>
+      <c r="L540" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M540" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="6">
+        <v>15</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C541" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D541" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E541" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F541" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G541" s="7" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H541" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I541" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J541" s="6">
+        <v>1</v>
+      </c>
+      <c r="K541" s="6">
+        <v>0</v>
+      </c>
+      <c r="L541" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M541" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="6">
+        <v>15</v>
+      </c>
+      <c r="B542" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C542" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D542" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E542" s="7" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F542" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G542" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H542" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="I542" s="7" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J542" s="6">
+        <v>1</v>
+      </c>
+      <c r="K542" s="6">
+        <v>0</v>
+      </c>
+      <c r="L542" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M542" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="6">
+        <v>15</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C543" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D543" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E543" s="7" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F543" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G543" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H543" s="7" t="s">
+        <v>1266</v>
+      </c>
+      <c r="I543" s="7" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J543" s="6">
+        <v>1</v>
+      </c>
+      <c r="K543" s="6">
+        <v>0</v>
+      </c>
+      <c r="L543" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M543" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="6">
+        <v>15</v>
+      </c>
+      <c r="B544" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C544" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D544" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E544" s="7" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F544" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G544" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H544" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I544" s="7" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J544" s="6">
+        <v>1</v>
+      </c>
+      <c r="K544" s="6">
+        <v>0</v>
+      </c>
+      <c r="L544" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M544" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="6">
+        <v>15</v>
+      </c>
+      <c r="B545" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C545" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D545" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E545" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F545" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G545" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H545" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I545" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J545" s="6">
+        <v>1</v>
+      </c>
+      <c r="K545" s="6">
+        <v>0</v>
+      </c>
+      <c r="L545" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M545" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="6">
+        <v>15</v>
+      </c>
+      <c r="B546" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C546" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D546" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E546" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F546" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G546" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H546" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I546" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J546" s="6">
+        <v>1</v>
+      </c>
+      <c r="K546" s="6">
+        <v>0</v>
+      </c>
+      <c r="L546" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M546" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="6">
+        <v>15</v>
+      </c>
+      <c r="B547" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C547" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D547" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E547" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F547" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G547" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H547" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="I547" s="7" t="s">
+        <v>1323</v>
+      </c>
+      <c r="J547" s="6">
+        <v>1</v>
+      </c>
+      <c r="K547" s="6">
+        <v>0</v>
+      </c>
+      <c r="L547" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M547" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A548" s="6">
+        <v>15</v>
+      </c>
+      <c r="B548" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C548" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D548" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E548" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F548" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G548" s="7" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H548" s="7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="I548" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J548" s="6">
+        <v>1</v>
+      </c>
+      <c r="K548" s="6">
+        <v>0</v>
+      </c>
+      <c r="L548" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M548" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A549" s="6">
+        <v>15</v>
+      </c>
+      <c r="B549" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C549" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D549" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E549" s="7" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F549" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G549" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="H549" s="7" t="s">
+        <v>1510</v>
+      </c>
+      <c r="I549" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="J549" s="6">
+        <v>1</v>
+      </c>
+      <c r="K549" s="6">
+        <v>0</v>
+      </c>
+      <c r="L549" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M549" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A550" s="6">
+        <v>15</v>
+      </c>
+      <c r="B550" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C550" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D550" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E550" s="7" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F550" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G550" s="7" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H550" s="7" t="s">
+        <v>1542</v>
+      </c>
+      <c r="I550" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="J550" s="6">
+        <v>1</v>
+      </c>
+      <c r="K550" s="6">
+        <v>0</v>
+      </c>
+      <c r="L550" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M550" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A551" s="6">
+        <v>15</v>
+      </c>
+      <c r="B551" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C551" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D551" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E551" s="7" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F551" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G551" s="7" t="s">
+        <v>1545</v>
+      </c>
+      <c r="H551" s="7" t="s">
+        <v>1546</v>
+      </c>
+      <c r="I551" s="7" t="s">
+        <v>1547</v>
+      </c>
+      <c r="J551" s="6">
+        <v>1</v>
+      </c>
+      <c r="K551" s="6">
+        <v>0</v>
+      </c>
+      <c r="L551" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M551" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A552" s="6">
+        <v>15</v>
+      </c>
+      <c r="B552" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C552" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D552" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E552" s="7" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F552" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G552" s="7" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H552" s="7" t="s">
+        <v>1550</v>
+      </c>
+      <c r="I552" s="7" t="s">
+        <v>1551</v>
+      </c>
+      <c r="J552" s="6">
+        <v>1</v>
+      </c>
+      <c r="K552" s="6">
+        <v>0</v>
+      </c>
+      <c r="L552" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M552" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A553" s="6">
+        <v>15</v>
+      </c>
+      <c r="B553" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C553" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D553" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E553" s="7" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F553" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G553" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="H553" s="7" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I553" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J553" s="6">
+        <v>1</v>
+      </c>
+      <c r="K553" s="6">
+        <v>0</v>
+      </c>
+      <c r="L553" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M553" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A554" s="6">
+        <v>15</v>
+      </c>
+      <c r="B554" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C554" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D554" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E554" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F554" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G554" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="H554" s="7" t="s">
+        <v>1590</v>
+      </c>
+      <c r="I554" s="7" t="s">
+        <v>1591</v>
+      </c>
+      <c r="J554" s="6">
+        <v>1</v>
+      </c>
+      <c r="K554" s="6">
+        <v>0</v>
+      </c>
+      <c r="L554" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M554" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A555" s="6">
+        <v>15</v>
+      </c>
+      <c r="B555" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C555" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D555" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E555" s="7" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F555" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G555" s="7" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H555" s="7" t="s">
+        <v>1606</v>
+      </c>
+      <c r="I555" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="J555" s="6">
+        <v>1</v>
+      </c>
+      <c r="K555" s="6">
+        <v>0</v>
+      </c>
+      <c r="L555" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M555" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A556" s="6">
+        <v>15</v>
+      </c>
+      <c r="B556" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C556" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D556" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E556" s="7" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F556" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G556" s="7" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H556" s="7" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I556" s="7" t="s">
+        <v>1611</v>
+      </c>
+      <c r="J556" s="6">
+        <v>1</v>
+      </c>
+      <c r="K556" s="6">
+        <v>0</v>
+      </c>
+      <c r="L556" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M556" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A557" s="6">
+        <v>15</v>
+      </c>
+      <c r="B557" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C557" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D557" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E557" s="7" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F557" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G557" s="7" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H557" s="7" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I557" s="7" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J557" s="6">
+        <v>1</v>
+      </c>
+      <c r="K557" s="6">
+        <v>0</v>
+      </c>
+      <c r="L557" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M557" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A558" s="6">
+        <v>15</v>
+      </c>
+      <c r="B558" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C558" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D558" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E558" s="7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F558" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G558" s="7" t="s">
+        <v>1690</v>
+      </c>
+      <c r="H558" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="I558" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="J558" s="6">
+        <v>1</v>
+      </c>
+      <c r="K558" s="6">
+        <v>0</v>
+      </c>
+      <c r="L558" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M558" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A559" s="6">
+        <v>15</v>
+      </c>
+      <c r="B559" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C559" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D559" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E559" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F559" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G559" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="H559" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="I559" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="J559" s="6">
+        <v>1</v>
+      </c>
+      <c r="K559" s="6">
+        <v>0</v>
+      </c>
+      <c r="L559" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M559" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A560" s="6">
+        <v>15</v>
+      </c>
+      <c r="B560" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C560" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D560" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E560" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F560" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G560" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="H560" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="I560" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="J560" s="6">
+        <v>1</v>
+      </c>
+      <c r="K560" s="6">
+        <v>0</v>
+      </c>
+      <c r="L560" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M560" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A561" s="6">
+        <v>15</v>
+      </c>
+      <c r="B561" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C561" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D561" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E561" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F561" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G561" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H561" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="I561" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="J561" s="6">
+        <v>1</v>
+      </c>
+      <c r="K561" s="6">
+        <v>0</v>
+      </c>
+      <c r="L561" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M561" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A562" s="6">
+        <v>15</v>
+      </c>
+      <c r="B562" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C562" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D562" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E562" s="7" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F562" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G562" s="7" t="s">
+        <v>1826</v>
+      </c>
+      <c r="H562" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="I562" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="J562" s="6">
+        <v>1</v>
+      </c>
+      <c r="K562" s="6">
+        <v>0</v>
+      </c>
+      <c r="L562" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M562" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A563" s="6">
+        <v>15</v>
+      </c>
+      <c r="B563" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C563" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D563" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E563" s="7" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F563" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G563" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H563" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="I563" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="J563" s="6">
+        <v>1</v>
+      </c>
+      <c r="K563" s="6">
+        <v>0</v>
+      </c>
+      <c r="L563" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M563" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A564" s="6">
+        <v>15</v>
+      </c>
+      <c r="B564" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C564" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D564" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E564" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F564" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G564" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H564" s="7" t="s">
+        <v>1919</v>
+      </c>
+      <c r="I564" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="J564" s="6">
+        <v>1</v>
+      </c>
+      <c r="K564" s="6">
+        <v>0</v>
+      </c>
+      <c r="L564" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M564" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A565" s="6">
+        <v>15</v>
+      </c>
+      <c r="B565" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C565" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D565" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E565" s="7" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F565" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G565" s="7" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H565" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="I565" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="J565" s="6">
+        <v>1</v>
+      </c>
+      <c r="K565" s="6">
+        <v>0</v>
+      </c>
+      <c r="L565" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M565" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A566" s="6">
+        <v>15</v>
+      </c>
+      <c r="B566" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C566" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D566" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E566" s="7" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F566" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G566" s="7" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H566" s="7" t="s">
+        <v>2019</v>
+      </c>
+      <c r="I566" s="7" t="s">
+        <v>2020</v>
+      </c>
+      <c r="J566" s="6">
+        <v>1</v>
+      </c>
+      <c r="K566" s="6">
+        <v>0</v>
+      </c>
+      <c r="L566" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M566" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A567" s="6">
+        <v>15</v>
+      </c>
+      <c r="B567" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C567" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D567" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E567" s="7" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F567" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G567" s="7" t="s">
+        <v>2022</v>
+      </c>
+      <c r="H567" s="7" t="s">
+        <v>2023</v>
+      </c>
+      <c r="I567" s="7" t="s">
+        <v>2024</v>
+      </c>
+      <c r="J567" s="6">
+        <v>1</v>
+      </c>
+      <c r="K567" s="6">
+        <v>0</v>
+      </c>
+      <c r="L567" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M567" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A568" s="6">
+        <v>15</v>
+      </c>
+      <c r="B568" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C568" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D568" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E568" s="7" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F568" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G568" s="7" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H568" s="7" t="s">
+        <v>2027</v>
+      </c>
+      <c r="I568" s="7" t="s">
+        <v>2028</v>
+      </c>
+      <c r="J568" s="6">
+        <v>1</v>
+      </c>
+      <c r="K568" s="6">
+        <v>0</v>
+      </c>
+      <c r="L568" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M568" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A569" s="6">
+        <v>15</v>
+      </c>
+      <c r="B569" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C569" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D569" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E569" s="7" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F569" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G569" s="7" t="s">
+        <v>2070</v>
+      </c>
+      <c r="H569" s="7" t="s">
+        <v>2071</v>
+      </c>
+      <c r="I569" s="7" t="s">
+        <v>2072</v>
+      </c>
+      <c r="J569" s="6">
+        <v>1</v>
+      </c>
+      <c r="K569" s="6">
+        <v>0</v>
+      </c>
+      <c r="L569" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M569" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A570" s="6">
+        <v>15</v>
+      </c>
+      <c r="B570" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C570" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D570" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E570" s="7" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F570" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G570" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="H570" s="7" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I570" s="7" t="s">
+        <v>2104</v>
+      </c>
+      <c r="J570" s="6">
+        <v>1</v>
+      </c>
+      <c r="K570" s="6">
+        <v>0</v>
+      </c>
+      <c r="L570" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M570" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A571" s="6">
+        <v>15</v>
+      </c>
+      <c r="B571" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C571" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D571" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E571" s="7" t="s">
+        <v>2161</v>
+      </c>
+      <c r="F571" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G571" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="H571" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I571" s="7" t="s">
+        <v>2164</v>
+      </c>
+      <c r="J571" s="6">
+        <v>1</v>
+      </c>
+      <c r="K571" s="6">
+        <v>0</v>
+      </c>
+      <c r="L571" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M571" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A572" s="6">
+        <v>15</v>
+      </c>
+      <c r="B572" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C572" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D572" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E572" s="7" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F572" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G572" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="H572" s="7" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I572" s="7" t="s">
+        <v>2203</v>
+      </c>
+      <c r="J572" s="6">
+        <v>1</v>
+      </c>
+      <c r="K572" s="6">
+        <v>2</v>
+      </c>
+      <c r="L572" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M572" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A573" s="6">
+        <v>15</v>
+      </c>
+      <c r="B573" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C573" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D573" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E573" s="7" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F573" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G573" s="7" t="s">
+        <v>2205</v>
+      </c>
+      <c r="H573" s="7" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I573" s="7" t="s">
+        <v>2207</v>
+      </c>
+      <c r="J573" s="6">
+        <v>1</v>
+      </c>
+      <c r="K573" s="6">
+        <v>0</v>
+      </c>
+      <c r="L573" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M573" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A574" s="6">
+        <v>15</v>
+      </c>
+      <c r="B574" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C574" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D574" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E574" s="7" t="s">
+        <v>2220</v>
+      </c>
+      <c r="F574" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G574" s="7" t="s">
+        <v>2221</v>
+      </c>
+      <c r="H574" s="7" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I574" s="7" t="s">
+        <v>2223</v>
+      </c>
+      <c r="J574" s="6">
+        <v>1</v>
+      </c>
+      <c r="K574" s="6">
+        <v>0</v>
+      </c>
+      <c r="L574" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M574" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A575" s="6">
+        <v>15</v>
+      </c>
+      <c r="B575" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C575" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D575" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E575" s="7" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F575" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G575" s="7" t="s">
+        <v>2225</v>
+      </c>
+      <c r="H575" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I575" s="7" t="s">
+        <v>2227</v>
+      </c>
+      <c r="J575" s="6">
+        <v>1</v>
+      </c>
+      <c r="K575" s="6">
+        <v>0</v>
+      </c>
+      <c r="L575" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M575" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A576" s="6">
+        <v>15</v>
+      </c>
+      <c r="B576" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C576" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D576" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E576" s="7" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F576" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G576" s="7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="H576" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I576" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="J576" s="6">
+        <v>1</v>
+      </c>
+      <c r="K576" s="6">
+        <v>0</v>
+      </c>
+      <c r="L576" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M576" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A577" s="6">
+        <v>15</v>
+      </c>
+      <c r="B577" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C577" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D577" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E577" s="7" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F577" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G577" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="H577" s="7" t="s">
+        <v>2282</v>
+      </c>
+      <c r="I577" s="7" t="s">
+        <v>2283</v>
+      </c>
+      <c r="J577" s="6">
+        <v>1</v>
+      </c>
+      <c r="K577" s="6">
+        <v>0</v>
+      </c>
+      <c r="L577" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M577" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A578" s="6">
+        <v>15</v>
+      </c>
+      <c r="B578" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C578" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D578" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E578" s="7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F578" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G578" s="7" t="s">
+        <v>2373</v>
+      </c>
+      <c r="H578" s="7" t="s">
+        <v>2374</v>
+      </c>
+      <c r="I578" s="7" t="s">
+        <v>2375</v>
+      </c>
+      <c r="J578" s="6">
+        <v>1</v>
+      </c>
+      <c r="K578" s="6">
+        <v>0</v>
+      </c>
+      <c r="L578" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M578" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A579" s="6">
+        <v>15</v>
+      </c>
+      <c r="B579" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C579" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D579" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E579" s="7" t="s">
+        <v>2604</v>
+      </c>
+      <c r="F579" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G579" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="H579" s="7" t="s">
+        <v>2606</v>
+      </c>
+      <c r="I579" s="7" t="s">
+        <v>2607</v>
+      </c>
+      <c r="J579" s="6">
+        <v>1</v>
+      </c>
+      <c r="K579" s="6">
+        <v>0</v>
+      </c>
+      <c r="L579" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M579" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A580" s="6">
+        <v>15</v>
+      </c>
+      <c r="B580" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C580" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D580" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E580" s="7" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F580" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G580" s="7" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H580" s="7" t="s">
+        <v>2614</v>
+      </c>
+      <c r="I580" s="7" t="s">
+        <v>2615</v>
+      </c>
+      <c r="J580" s="6">
+        <v>1</v>
+      </c>
+      <c r="K580" s="6">
+        <v>0</v>
+      </c>
+      <c r="L580" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M580" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A581" s="6">
+        <v>15</v>
+      </c>
+      <c r="B581" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C581" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D581" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E581" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="F581" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G581" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H581" s="7" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I581" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="J581" s="6">
+        <v>1</v>
+      </c>
+      <c r="K581" s="6">
+        <v>0</v>
+      </c>
+      <c r="L581" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M581" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A582" s="6">
+        <v>15</v>
+      </c>
+      <c r="B582" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C582" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D582" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E582" s="7" t="s">
+        <v>2712</v>
+      </c>
+      <c r="F582" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G582" s="7" t="s">
+        <v>2713</v>
+      </c>
+      <c r="H582" s="7" t="s">
+        <v>2714</v>
+      </c>
+      <c r="I582" s="7" t="s">
+        <v>2715</v>
+      </c>
+      <c r="J582" s="6">
+        <v>1</v>
+      </c>
+      <c r="K582" s="6">
+        <v>0</v>
+      </c>
+      <c r="L582" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M582" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A583" s="6">
+        <v>15</v>
+      </c>
+      <c r="B583" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C583" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D583" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E583" s="7" t="s">
+        <v>2776</v>
+      </c>
+      <c r="F583" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G583" s="7" t="s">
+        <v>2777</v>
+      </c>
+      <c r="H583" s="7" t="s">
+        <v>2778</v>
+      </c>
+      <c r="I583" s="7" t="s">
+        <v>2779</v>
+      </c>
+      <c r="J583" s="6">
+        <v>1</v>
+      </c>
+      <c r="K583" s="6">
+        <v>0</v>
+      </c>
+      <c r="L583" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M583" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A584" s="6">
+        <v>15</v>
+      </c>
+      <c r="B584" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C584" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D584" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E584" s="7" t="s">
+        <v>2828</v>
+      </c>
+      <c r="F584" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G584" s="7" t="s">
+        <v>2829</v>
+      </c>
+      <c r="H584" s="7" t="s">
+        <v>2830</v>
+      </c>
+      <c r="I584" s="7" t="s">
+        <v>2831</v>
+      </c>
+      <c r="J584" s="6">
+        <v>1</v>
+      </c>
+      <c r="K584" s="6">
+        <v>0</v>
+      </c>
+      <c r="L584" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M584" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A585" s="6">
+        <v>15</v>
+      </c>
+      <c r="B585" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C585" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D585" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E585" s="7" t="s">
+        <v>2880</v>
+      </c>
+      <c r="F585" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G585" s="7" t="s">
+        <v>2881</v>
+      </c>
+      <c r="H585" s="7" t="s">
+        <v>2882</v>
+      </c>
+      <c r="I585" s="7" t="s">
+        <v>2883</v>
+      </c>
+      <c r="J585" s="6">
+        <v>1</v>
+      </c>
+      <c r="K585" s="6">
+        <v>0</v>
+      </c>
+      <c r="L585" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M585" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A586" s="6">
+        <v>15</v>
+      </c>
+      <c r="B586" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C586" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D586" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E586" s="7" t="s">
+        <v>2892</v>
+      </c>
+      <c r="F586" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G586" s="7" t="s">
+        <v>2893</v>
+      </c>
+      <c r="H586" s="7" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I586" s="7" t="s">
+        <v>2895</v>
+      </c>
+      <c r="J586" s="6">
+        <v>1</v>
+      </c>
+      <c r="K586" s="6">
+        <v>0</v>
+      </c>
+      <c r="L586" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M586" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A587" s="6">
+        <v>15</v>
+      </c>
+      <c r="B587" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C587" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D587" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E587" s="7" t="s">
+        <v>3044</v>
+      </c>
+      <c r="F587" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G587" s="7" t="s">
+        <v>3045</v>
+      </c>
+      <c r="H587" s="7" t="s">
+        <v>3046</v>
+      </c>
+      <c r="I587" s="7" t="s">
+        <v>3047</v>
+      </c>
+      <c r="J587" s="6">
+        <v>1</v>
+      </c>
+      <c r="K587" s="6">
+        <v>0</v>
+      </c>
+      <c r="L587" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M587" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A588" s="6">
+        <v>15</v>
+      </c>
+      <c r="B588" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C588" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D588" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E588" s="7" t="s">
+        <v>3052</v>
+      </c>
+      <c r="F588" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G588" s="7" t="s">
+        <v>3053</v>
+      </c>
+      <c r="H588" s="7" t="s">
+        <v>3054</v>
+      </c>
+      <c r="I588" s="7" t="s">
+        <v>3055</v>
+      </c>
+      <c r="J588" s="6">
+        <v>1</v>
+      </c>
+      <c r="K588" s="6">
+        <v>0</v>
+      </c>
+      <c r="L588" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M588" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A589" s="6">
+        <v>15</v>
+      </c>
+      <c r="B589" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C589" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D589" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E589" s="7" t="s">
+        <v>3092</v>
+      </c>
+      <c r="F589" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G589" s="7" t="s">
+        <v>3093</v>
+      </c>
+      <c r="H589" s="7" t="s">
+        <v>3094</v>
+      </c>
+      <c r="I589" s="7" t="s">
+        <v>3095</v>
+      </c>
+      <c r="J589" s="6">
+        <v>1</v>
+      </c>
+      <c r="K589" s="6">
+        <v>0</v>
+      </c>
+      <c r="L589" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M589" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A590" s="6">
+        <v>15</v>
+      </c>
+      <c r="B590" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C590" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D590" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E590" s="7" t="s">
+        <v>3188</v>
+      </c>
+      <c r="F590" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G590" s="7" t="s">
+        <v>3189</v>
+      </c>
+      <c r="H590" s="7" t="s">
+        <v>3190</v>
+      </c>
+      <c r="I590" s="7" t="s">
+        <v>3191</v>
+      </c>
+      <c r="J590" s="6">
+        <v>1</v>
+      </c>
+      <c r="K590" s="6">
+        <v>0</v>
+      </c>
+      <c r="L590" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M590" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="6">
+        <v>15</v>
+      </c>
+      <c r="B591" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C591" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D591" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E591" s="7" t="s">
+        <v>3292</v>
+      </c>
+      <c r="F591" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G591" s="7" t="s">
+        <v>3293</v>
+      </c>
+      <c r="H591" s="7" t="s">
+        <v>3294</v>
+      </c>
+      <c r="I591" s="7" t="s">
+        <v>3295</v>
+      </c>
+      <c r="J591" s="6">
+        <v>1</v>
+      </c>
+      <c r="K591" s="6">
+        <v>0</v>
+      </c>
+      <c r="L591" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M591" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="6">
+        <v>15</v>
+      </c>
+      <c r="B592" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C592" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D592" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E592" s="7" t="s">
+        <v>3304</v>
+      </c>
+      <c r="F592" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G592" s="7" t="s">
+        <v>3305</v>
+      </c>
+      <c r="H592" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="I592" s="7" t="s">
+        <v>3307</v>
+      </c>
+      <c r="J592" s="6">
+        <v>1</v>
+      </c>
+      <c r="K592" s="6">
+        <v>0</v>
+      </c>
+      <c r="L592" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M592" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="6">
+        <v>15</v>
+      </c>
+      <c r="B593" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C593" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D593" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E593" s="7" t="s">
+        <v>3320</v>
+      </c>
+      <c r="F593" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G593" s="7" t="s">
+        <v>3321</v>
+      </c>
+      <c r="H593" s="7" t="s">
+        <v>3322</v>
+      </c>
+      <c r="I593" s="7" t="s">
+        <v>3323</v>
+      </c>
+      <c r="J593" s="6">
+        <v>1</v>
+      </c>
+      <c r="K593" s="6">
+        <v>0</v>
+      </c>
+      <c r="L593" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M593" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="6">
+        <v>15</v>
+      </c>
+      <c r="B594" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C594" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D594" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E594" s="7" t="s">
+        <v>3352</v>
+      </c>
+      <c r="F594" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G594" s="7" t="s">
+        <v>3353</v>
+      </c>
+      <c r="H594" s="7" t="s">
+        <v>3354</v>
+      </c>
+      <c r="I594" s="7" t="s">
+        <v>3355</v>
+      </c>
+      <c r="J594" s="6">
+        <v>1</v>
+      </c>
+      <c r="K594" s="6">
+        <v>0</v>
+      </c>
+      <c r="L594" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M594" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A595" s="6">
+        <v>15</v>
+      </c>
+      <c r="B595" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C595" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D595" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E595" s="7" t="s">
+        <v>3489</v>
+      </c>
+      <c r="F595" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G595" s="7" t="s">
+        <v>3490</v>
+      </c>
+      <c r="H595" s="7" t="s">
+        <v>3491</v>
+      </c>
+      <c r="I595" s="7" t="s">
+        <v>3492</v>
+      </c>
+      <c r="J595" s="6">
+        <v>1</v>
+      </c>
+      <c r="K595" s="6">
+        <v>2</v>
+      </c>
+      <c r="L595" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M595" s="7" t="s">
         <v>22</v>
       </c>
     </row>
